--- a/Unity/Assets/Config/Excel/ItemConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ItemConfig.xlsx
@@ -282,13 +282,13 @@
     <t>联盟贡献度可以在联盟商店中兑换商品</t>
   </si>
   <si>
-    <t>红色技能随机宝箱</t>
+    <t>红将碎片随机宝箱</t>
   </si>
   <si>
     <t>打开后从以下红色技能中随机获取一件</t>
   </si>
   <si>
-    <t>红色技能自选宝箱</t>
+    <t>红将碎片自选宝箱</t>
   </si>
   <si>
     <t>打开后从以下红色技能中自选一件</t>
@@ -570,16 +570,16 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="微软雅黑"/>
       <charset val="134"/>

--- a/Unity/Assets/Config/Excel/ItemConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ItemConfig.xlsx
@@ -99,8 +99,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-1.消耗型道具
-2.材料
+1.消耗品
 3.装备
 4.英雄碎片</t>
         </r>
@@ -138,11 +137,9 @@
 2 获得经验值
 3 随机宝箱
 4 自选宝箱
-5 碎片
-6 使用后永久增加属性
-7 抽奖券
-8 加速升级吞噬等阶
-9 副本入场券
+5 使用后永久增加属性
+6 抽奖券
+7 副本入场券
 </t>
         </r>
         <r>
@@ -160,9 +157,8 @@
 6 戒指
 7 手镯
 8 项链
-9 护肤
-10 饰品
-11 武器</t>
+9 饰品
+10 武器</t>
         </r>
       </text>
     </comment>
@@ -193,7 +189,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="57">
   <si>
     <t>Id</t>
   </si>
@@ -282,25 +278,19 @@
     <t>联盟贡献度可以在联盟商店中兑换商品</t>
   </si>
   <si>
-    <t>红将碎片随机宝箱</t>
+    <t>随机红将碎片</t>
   </si>
   <si>
     <t>打开后从以下红色技能中随机获取一件</t>
   </si>
   <si>
-    <t>红将碎片自选宝箱</t>
+    <t>自选红将碎片</t>
   </si>
   <si>
     <t>打开后从以下红色技能中自选一件</t>
   </si>
   <si>
-    <t>技能召唤券</t>
-  </si>
-  <si>
-    <t>可以在招募中心抽取强力的技能</t>
-  </si>
-  <si>
-    <t>随从召唤券</t>
+    <t>英雄召唤券</t>
   </si>
   <si>
     <t>可以在招募中心召唤随从</t>
@@ -330,12 +320,6 @@
     <t>使用后永久增加闪避资质</t>
   </si>
   <si>
-    <t>时间胶囊</t>
-  </si>
-  <si>
-    <t>减少吞噬等阶的升级时间</t>
-  </si>
-  <si>
     <t>入场券</t>
   </si>
   <si>
@@ -370,9 +354,6 @@
   </si>
   <si>
     <t>一个项链</t>
-  </si>
-  <si>
-    <t>一个护符</t>
   </si>
   <si>
     <t>一个饰品</t>
@@ -1451,7 +1432,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="10.875" style="5" customWidth="1"/>
@@ -1775,7 +1756,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I13" s="2">
         <v>99</v>
@@ -1806,7 +1787,7 @@
         <v>1</v>
       </c>
       <c r="H14" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I14" s="2">
         <v>99</v>
@@ -1837,7 +1818,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I15" s="2">
         <v>99</v>
@@ -1868,7 +1849,7 @@
         <v>1</v>
       </c>
       <c r="H16" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I16" s="2">
         <v>99</v>
@@ -1899,7 +1880,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I17" s="2">
         <v>99</v>
@@ -1924,13 +1905,13 @@
         <v>10000008</v>
       </c>
       <c r="F18" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
       </c>
       <c r="H18" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I18" s="2">
         <v>99</v>
@@ -1942,82 +1923,82 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="1:11">
+    <row r="19" s="3" customFormat="1" customHeight="1" spans="1:11">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
-      <c r="C19" s="2">
-        <v>10000109</v>
-      </c>
-      <c r="D19" s="2" t="s">
+      <c r="C19" s="3">
+        <v>11000001</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E19" s="2">
-        <v>10000009</v>
-      </c>
-      <c r="F19" s="2">
-        <v>5</v>
-      </c>
-      <c r="G19" s="2">
-        <v>1</v>
-      </c>
-      <c r="H19" s="2">
-        <v>8</v>
-      </c>
-      <c r="I19" s="2">
-        <v>99</v>
-      </c>
-      <c r="J19" s="2">
-        <v>0</v>
-      </c>
-      <c r="K19" s="2" t="s">
+      <c r="E19" s="3">
+        <v>10000010</v>
+      </c>
+      <c r="F19" s="3">
+        <v>2</v>
+      </c>
+      <c r="G19" s="3">
+        <v>4</v>
+      </c>
+      <c r="H19" s="3">
+        <v>4</v>
+      </c>
+      <c r="I19" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J19" s="3">
+        <v>0</v>
+      </c>
+      <c r="K19" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="20" s="2" customFormat="1" customHeight="1" spans="1:11">
+    <row r="20" s="3" customFormat="1" customHeight="1" spans="1:11">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
-      <c r="C20" s="2">
-        <v>10000110</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E20" s="2">
-        <v>10000010</v>
-      </c>
-      <c r="F20" s="2">
-        <v>3</v>
-      </c>
-      <c r="G20" s="2">
-        <v>1</v>
-      </c>
-      <c r="H20" s="2">
-        <v>9</v>
-      </c>
-      <c r="I20" s="2">
-        <v>99</v>
-      </c>
-      <c r="J20" s="2">
-        <v>0</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>48</v>
+      <c r="C20" s="3">
+        <v>11000002</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E20" s="3">
+        <v>10000011</v>
+      </c>
+      <c r="F20" s="3">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3">
+        <v>4</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="21" s="3" customFormat="1" customHeight="1" spans="1:11">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="3">
-        <v>11000001</v>
+        <v>11000003</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E21" s="3">
-        <v>10000011</v>
+        <v>10000012</v>
       </c>
       <c r="F21" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G21" s="3">
         <v>4</v>
@@ -2032,23 +2013,23 @@
         <v>0</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" s="3" customFormat="1" customHeight="1" spans="1:11">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="3">
-        <v>11000002</v>
+        <v>11000004</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E22" s="3">
-        <v>10000012</v>
+        <v>10000013</v>
       </c>
       <c r="F22" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G22" s="3">
         <v>4</v>
@@ -2063,23 +2044,23 @@
         <v>0</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23" s="3" customFormat="1" customHeight="1" spans="1:11">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="3">
-        <v>11000003</v>
+        <v>11000005</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E23" s="3">
-        <v>10000013</v>
+        <v>10000014</v>
       </c>
       <c r="F23" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G23" s="3">
         <v>4</v>
@@ -2094,82 +2075,76 @@
         <v>0</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24" s="3" customFormat="1" customHeight="1" spans="1:11">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
-      <c r="C24" s="3">
-        <v>11000004</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E24" s="3">
-        <v>10000014</v>
-      </c>
-      <c r="F24" s="3">
-        <v>5</v>
-      </c>
-      <c r="G24" s="3">
-        <v>4</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>99999999</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="25" s="3" customFormat="1" customHeight="1" spans="1:11">
+      <c r="C24" s="4">
+        <v>12000001</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E24" s="4">
+        <v>10000001</v>
+      </c>
+      <c r="F24" s="4">
+        <v>3</v>
+      </c>
+      <c r="G24" s="4">
+        <v>3</v>
+      </c>
+      <c r="H24" s="4">
+        <v>1</v>
+      </c>
+      <c r="I24" s="4">
+        <v>1</v>
+      </c>
+      <c r="J24" s="4">
+        <v>12000001</v>
+      </c>
+    </row>
+    <row r="25" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
-      <c r="C25" s="3">
-        <v>11000005</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E25" s="3">
-        <v>10000015</v>
-      </c>
-      <c r="F25" s="3">
-        <v>6</v>
-      </c>
-      <c r="G25" s="3">
-        <v>4</v>
-      </c>
-      <c r="H25" s="3">
-        <v>0</v>
-      </c>
-      <c r="I25" s="3">
-        <v>99999999</v>
-      </c>
-      <c r="J25" s="3">
-        <v>0</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>50</v>
+      <c r="C25" s="4">
+        <v>12000002</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E25" s="4">
+        <v>10000002</v>
+      </c>
+      <c r="F25" s="4">
+        <v>3</v>
+      </c>
+      <c r="G25" s="4">
+        <v>3</v>
+      </c>
+      <c r="H25" s="4">
+        <v>2</v>
+      </c>
+      <c r="I25" s="4">
+        <v>1</v>
+      </c>
+      <c r="J25" s="4">
+        <v>12000002</v>
       </c>
     </row>
     <row r="26" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="4">
-        <v>12000001</v>
+        <v>12000003</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E26" s="4">
-        <v>10000001</v>
+        <v>10000003</v>
       </c>
       <c r="F26" s="4">
         <v>3</v>
@@ -2178,26 +2153,26 @@
         <v>3</v>
       </c>
       <c r="H26" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I26" s="4">
         <v>1</v>
       </c>
       <c r="J26" s="4">
-        <v>12000001</v>
+        <v>12000003</v>
       </c>
     </row>
     <row r="27" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="4">
-        <v>12000002</v>
+        <v>12000004</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E27" s="4">
-        <v>10000002</v>
+        <v>10000004</v>
       </c>
       <c r="F27" s="4">
         <v>3</v>
@@ -2206,26 +2181,26 @@
         <v>3</v>
       </c>
       <c r="H27" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I27" s="4">
         <v>1</v>
       </c>
       <c r="J27" s="4">
-        <v>12000002</v>
+        <v>12000004</v>
       </c>
     </row>
     <row r="28" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="4">
-        <v>12000003</v>
+        <v>12000005</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E28" s="4">
-        <v>10000003</v>
+        <v>10000005</v>
       </c>
       <c r="F28" s="4">
         <v>3</v>
@@ -2234,26 +2209,26 @@
         <v>3</v>
       </c>
       <c r="H28" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I28" s="4">
         <v>1</v>
       </c>
       <c r="J28" s="4">
-        <v>12000003</v>
+        <v>12000005</v>
       </c>
     </row>
     <row r="29" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="4">
-        <v>12000004</v>
+        <v>12000006</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E29" s="4">
-        <v>10000004</v>
+        <v>10000006</v>
       </c>
       <c r="F29" s="4">
         <v>3</v>
@@ -2262,26 +2237,26 @@
         <v>3</v>
       </c>
       <c r="H29" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I29" s="4">
         <v>1</v>
       </c>
       <c r="J29" s="4">
-        <v>12000004</v>
+        <v>12000006</v>
       </c>
     </row>
     <row r="30" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="4">
-        <v>12000005</v>
+        <v>12000007</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E30" s="4">
-        <v>10000005</v>
+        <v>10000007</v>
       </c>
       <c r="F30" s="4">
         <v>3</v>
@@ -2290,26 +2265,26 @@
         <v>3</v>
       </c>
       <c r="H30" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I30" s="4">
         <v>1</v>
       </c>
       <c r="J30" s="4">
-        <v>12000005</v>
+        <v>12000007</v>
       </c>
     </row>
     <row r="31" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
       <c r="C31" s="4">
-        <v>12000006</v>
+        <v>12000008</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E31" s="4">
-        <v>10000006</v>
+        <v>10000008</v>
       </c>
       <c r="F31" s="4">
         <v>3</v>
@@ -2318,26 +2293,26 @@
         <v>3</v>
       </c>
       <c r="H31" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I31" s="4">
         <v>1</v>
       </c>
       <c r="J31" s="4">
-        <v>12000006</v>
+        <v>12000008</v>
       </c>
     </row>
     <row r="32" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A32" s="5"/>
       <c r="B32" s="5"/>
       <c r="C32" s="4">
-        <v>12000007</v>
+        <v>12000009</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E32" s="4">
-        <v>10000007</v>
+        <v>10000009</v>
       </c>
       <c r="F32" s="4">
         <v>3</v>
@@ -2346,26 +2321,26 @@
         <v>3</v>
       </c>
       <c r="H32" s="4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I32" s="4">
         <v>1</v>
       </c>
       <c r="J32" s="4">
-        <v>12000007</v>
+        <v>12000009</v>
       </c>
     </row>
     <row r="33" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A33" s="5"/>
       <c r="B33" s="5"/>
       <c r="C33" s="4">
-        <v>12000008</v>
+        <v>12000010</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E33" s="4">
-        <v>10000008</v>
+        <v>10000010</v>
       </c>
       <c r="F33" s="4">
         <v>3</v>
@@ -2374,97 +2349,13 @@
         <v>3</v>
       </c>
       <c r="H33" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I33" s="4">
         <v>1</v>
       </c>
       <c r="J33" s="4">
-        <v>12000008</v>
-      </c>
-    </row>
-    <row r="34" s="4" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A34" s="5"/>
-      <c r="B34" s="5"/>
-      <c r="C34" s="4">
-        <v>12000009</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E34" s="4">
-        <v>10000009</v>
-      </c>
-      <c r="F34" s="4">
-        <v>3</v>
-      </c>
-      <c r="G34" s="4">
-        <v>3</v>
-      </c>
-      <c r="H34" s="4">
-        <v>9</v>
-      </c>
-      <c r="I34" s="4">
-        <v>1</v>
-      </c>
-      <c r="J34" s="4">
-        <v>12000009</v>
-      </c>
-    </row>
-    <row r="35" s="4" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A35" s="5"/>
-      <c r="B35" s="5"/>
-      <c r="C35" s="4">
         <v>12000010</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E35" s="4">
-        <v>10000010</v>
-      </c>
-      <c r="F35" s="4">
-        <v>3</v>
-      </c>
-      <c r="G35" s="4">
-        <v>3</v>
-      </c>
-      <c r="H35" s="4">
-        <v>10</v>
-      </c>
-      <c r="I35" s="4">
-        <v>1</v>
-      </c>
-      <c r="J35" s="4">
-        <v>12000010</v>
-      </c>
-    </row>
-    <row r="36" s="4" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A36" s="5"/>
-      <c r="B36" s="5"/>
-      <c r="C36" s="4">
-        <v>12000011</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E36" s="4">
-        <v>10000011</v>
-      </c>
-      <c r="F36" s="4">
-        <v>3</v>
-      </c>
-      <c r="G36" s="4">
-        <v>3</v>
-      </c>
-      <c r="H36" s="4">
-        <v>11</v>
-      </c>
-      <c r="I36" s="4">
-        <v>1</v>
-      </c>
-      <c r="J36" s="4">
-        <v>12000011</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/ItemConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ItemConfig.xlsx
@@ -100,6 +100,7 @@
           </rPr>
           <t xml:space="preserve">
 1.消耗品
+2.材料
 3.装备
 4.英雄碎片</t>
         </r>
@@ -189,7 +190,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="69">
   <si>
     <t>Id</t>
   </si>
@@ -360,6 +361,42 @@
   </si>
   <si>
     <t>一个武器</t>
+  </si>
+  <si>
+    <t>材料1</t>
+  </si>
+  <si>
+    <t>一种材料1</t>
+  </si>
+  <si>
+    <t>材料2</t>
+  </si>
+  <si>
+    <t>一种材料2</t>
+  </si>
+  <si>
+    <t>材料3</t>
+  </si>
+  <si>
+    <t>一种材料3</t>
+  </si>
+  <si>
+    <t>材料4</t>
+  </si>
+  <si>
+    <t>一种材料4</t>
+  </si>
+  <si>
+    <t>材料5</t>
+  </si>
+  <si>
+    <t>一种材料5</t>
+  </si>
+  <si>
+    <t>材料6</t>
+  </si>
+  <si>
+    <t>一种材料6</t>
   </si>
 </sst>
 </file>
@@ -551,16 +588,16 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -1432,7 +1469,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="10.875" style="5" customWidth="1"/>
@@ -1933,7 +1970,7 @@
         <v>45</v>
       </c>
       <c r="E19" s="3">
-        <v>10000010</v>
+        <v>10000009</v>
       </c>
       <c r="F19" s="3">
         <v>2</v>
@@ -1964,7 +2001,7 @@
         <v>45</v>
       </c>
       <c r="E20" s="3">
-        <v>10000011</v>
+        <v>10000010</v>
       </c>
       <c r="F20" s="3">
         <v>3</v>
@@ -1995,7 +2032,7 @@
         <v>45</v>
       </c>
       <c r="E21" s="3">
-        <v>10000012</v>
+        <v>10000011</v>
       </c>
       <c r="F21" s="3">
         <v>4</v>
@@ -2026,7 +2063,7 @@
         <v>45</v>
       </c>
       <c r="E22" s="3">
-        <v>10000013</v>
+        <v>10000012</v>
       </c>
       <c r="F22" s="3">
         <v>5</v>
@@ -2057,7 +2094,7 @@
         <v>45</v>
       </c>
       <c r="E23" s="3">
-        <v>10000014</v>
+        <v>10000013</v>
       </c>
       <c r="F23" s="3">
         <v>6</v>
@@ -2356,6 +2393,180 @@
       </c>
       <c r="J33" s="4">
         <v>12000010</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:11">
+      <c r="C34" s="5">
+        <v>13000001</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E34" s="5">
+        <v>10000001</v>
+      </c>
+      <c r="F34" s="5">
+        <v>1</v>
+      </c>
+      <c r="G34" s="5">
+        <v>2</v>
+      </c>
+      <c r="H34" s="5">
+        <v>0</v>
+      </c>
+      <c r="I34" s="5">
+        <v>999</v>
+      </c>
+      <c r="J34" s="5">
+        <v>0</v>
+      </c>
+      <c r="K34" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:11">
+      <c r="C35" s="5">
+        <v>13000002</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E35" s="5">
+        <v>10000002</v>
+      </c>
+      <c r="F35" s="5">
+        <v>2</v>
+      </c>
+      <c r="G35" s="5">
+        <v>2</v>
+      </c>
+      <c r="H35" s="5">
+        <v>0</v>
+      </c>
+      <c r="I35" s="5">
+        <v>999</v>
+      </c>
+      <c r="J35" s="5">
+        <v>0</v>
+      </c>
+      <c r="K35" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:11">
+      <c r="C36" s="5">
+        <v>13000003</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E36" s="5">
+        <v>10000003</v>
+      </c>
+      <c r="F36" s="5">
+        <v>3</v>
+      </c>
+      <c r="G36" s="5">
+        <v>2</v>
+      </c>
+      <c r="H36" s="5">
+        <v>0</v>
+      </c>
+      <c r="I36" s="5">
+        <v>999</v>
+      </c>
+      <c r="J36" s="5">
+        <v>0</v>
+      </c>
+      <c r="K36" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:11">
+      <c r="C37" s="5">
+        <v>13000004</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E37" s="5">
+        <v>10000004</v>
+      </c>
+      <c r="F37" s="5">
+        <v>4</v>
+      </c>
+      <c r="G37" s="5">
+        <v>2</v>
+      </c>
+      <c r="H37" s="5">
+        <v>0</v>
+      </c>
+      <c r="I37" s="5">
+        <v>999</v>
+      </c>
+      <c r="J37" s="5">
+        <v>0</v>
+      </c>
+      <c r="K37" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:11">
+      <c r="C38" s="5">
+        <v>13000005</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E38" s="5">
+        <v>10000005</v>
+      </c>
+      <c r="F38" s="5">
+        <v>5</v>
+      </c>
+      <c r="G38" s="5">
+        <v>2</v>
+      </c>
+      <c r="H38" s="5">
+        <v>0</v>
+      </c>
+      <c r="I38" s="5">
+        <v>999</v>
+      </c>
+      <c r="J38" s="5">
+        <v>0</v>
+      </c>
+      <c r="K38" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:11">
+      <c r="C39" s="5">
+        <v>13000006</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E39" s="5">
+        <v>10000006</v>
+      </c>
+      <c r="F39" s="5">
+        <v>6</v>
+      </c>
+      <c r="G39" s="5">
+        <v>2</v>
+      </c>
+      <c r="H39" s="5">
+        <v>0</v>
+      </c>
+      <c r="I39" s="5">
+        <v>999</v>
+      </c>
+      <c r="J39" s="5">
+        <v>0</v>
+      </c>
+      <c r="K39" s="5" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/ItemConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ItemConfig.xlsx
@@ -102,7 +102,7 @@
 1.消耗品
 2.材料
 3.装备
-4.英雄碎片</t>
+</t>
         </r>
       </text>
     </comment>
@@ -190,7 +190,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="65">
   <si>
     <t>Id</t>
   </si>
@@ -330,7 +330,43 @@
     <t>大熊猫碎片</t>
   </si>
   <si>
-    <t>英雄碎片，八个合成</t>
+    <t>英雄碎片，合成英雄</t>
+  </si>
+  <si>
+    <t>材料1</t>
+  </si>
+  <si>
+    <t>一种材料1</t>
+  </si>
+  <si>
+    <t>材料2</t>
+  </si>
+  <si>
+    <t>一种材料2</t>
+  </si>
+  <si>
+    <t>材料3</t>
+  </si>
+  <si>
+    <t>一种材料3</t>
+  </si>
+  <si>
+    <t>材料4</t>
+  </si>
+  <si>
+    <t>一种材料4</t>
+  </si>
+  <si>
+    <t>材料5</t>
+  </si>
+  <si>
+    <t>一种材料5</t>
+  </si>
+  <si>
+    <t>材料6</t>
+  </si>
+  <si>
+    <t>一种材料6</t>
   </si>
   <si>
     <t>一个头盔</t>
@@ -339,64 +375,16 @@
     <t>一个衣服</t>
   </si>
   <si>
-    <t>一个腰带</t>
-  </si>
-  <si>
     <t>一个裤子</t>
   </si>
   <si>
     <t>一个鞋子</t>
   </si>
   <si>
-    <t>一个戒指</t>
-  </si>
-  <si>
-    <t>一个手镯</t>
-  </si>
-  <si>
     <t>一个项链</t>
   </si>
   <si>
-    <t>一个饰品</t>
-  </si>
-  <si>
     <t>一个武器</t>
-  </si>
-  <si>
-    <t>材料1</t>
-  </si>
-  <si>
-    <t>一种材料1</t>
-  </si>
-  <si>
-    <t>材料2</t>
-  </si>
-  <si>
-    <t>一种材料2</t>
-  </si>
-  <si>
-    <t>材料3</t>
-  </si>
-  <si>
-    <t>一种材料3</t>
-  </si>
-  <si>
-    <t>材料4</t>
-  </si>
-  <si>
-    <t>一种材料4</t>
-  </si>
-  <si>
-    <t>材料5</t>
-  </si>
-  <si>
-    <t>一种材料5</t>
-  </si>
-  <si>
-    <t>材料6</t>
-  </si>
-  <si>
-    <t>一种材料6</t>
   </si>
 </sst>
 </file>
@@ -1469,7 +1457,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="10.875" style="5" customWidth="1"/>
@@ -1716,7 +1704,7 @@
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="2">
-        <v>10000101</v>
+        <v>10001001</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>29</v>
@@ -1747,7 +1735,7 @@
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="2">
-        <v>10000102</v>
+        <v>10001002</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>31</v>
@@ -1778,7 +1766,7 @@
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="2">
-        <v>10000103</v>
+        <v>10001003</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>33</v>
@@ -1809,7 +1797,7 @@
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="2">
-        <v>10000104</v>
+        <v>10001004</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>35</v>
@@ -1840,7 +1828,7 @@
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="2">
-        <v>10000105</v>
+        <v>10001005</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>37</v>
@@ -1871,7 +1859,7 @@
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="2">
-        <v>10000106</v>
+        <v>10001006</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>39</v>
@@ -1902,7 +1890,7 @@
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="2">
-        <v>10000107</v>
+        <v>10001007</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>41</v>
@@ -1933,7 +1921,7 @@
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="2">
-        <v>10000108</v>
+        <v>10001008</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>43</v>
@@ -1964,7 +1952,7 @@
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="3">
-        <v>11000001</v>
+        <v>10002001</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>45</v>
@@ -1976,10 +1964,10 @@
         <v>2</v>
       </c>
       <c r="G19" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H19" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I19" s="3">
         <v>99999999</v>
@@ -1995,7 +1983,7 @@
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="3">
-        <v>11000002</v>
+        <v>10002002</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>45</v>
@@ -2007,7 +1995,7 @@
         <v>3</v>
       </c>
       <c r="G20" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H20" s="3">
         <v>0</v>
@@ -2026,7 +2014,7 @@
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="3">
-        <v>11000003</v>
+        <v>10002003</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>45</v>
@@ -2038,7 +2026,7 @@
         <v>4</v>
       </c>
       <c r="G21" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H21" s="3">
         <v>0</v>
@@ -2057,7 +2045,7 @@
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="3">
-        <v>11000004</v>
+        <v>10002004</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>45</v>
@@ -2069,7 +2057,7 @@
         <v>5</v>
       </c>
       <c r="G22" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H22" s="3">
         <v>0</v>
@@ -2088,7 +2076,7 @@
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="3">
-        <v>11000005</v>
+        <v>10002005</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>45</v>
@@ -2100,7 +2088,7 @@
         <v>6</v>
       </c>
       <c r="G23" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H23" s="3">
         <v>0</v>
@@ -2115,185 +2103,191 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" s="4" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="4">
-        <v>12000001</v>
-      </c>
-      <c r="D24" s="4" t="s">
+    <row r="24" customHeight="1" spans="3:11">
+      <c r="C24" s="5">
+        <v>10002006</v>
+      </c>
+      <c r="D24" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E24" s="4">
+      <c r="E24" s="5">
         <v>10000001</v>
       </c>
-      <c r="F24" s="4">
+      <c r="F24" s="5">
+        <v>1</v>
+      </c>
+      <c r="G24" s="5">
+        <v>2</v>
+      </c>
+      <c r="H24" s="5">
+        <v>0</v>
+      </c>
+      <c r="I24" s="5">
+        <v>999</v>
+      </c>
+      <c r="J24" s="5">
+        <v>0</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="3:11">
+      <c r="C25" s="5">
+        <v>10002007</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E25" s="5">
+        <v>10000002</v>
+      </c>
+      <c r="F25" s="5">
+        <v>2</v>
+      </c>
+      <c r="G25" s="5">
+        <v>2</v>
+      </c>
+      <c r="H25" s="5">
+        <v>0</v>
+      </c>
+      <c r="I25" s="5">
+        <v>999</v>
+      </c>
+      <c r="J25" s="5">
+        <v>0</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="3:11">
+      <c r="C26" s="5">
+        <v>10002008</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E26" s="5">
+        <v>10000003</v>
+      </c>
+      <c r="F26" s="5">
         <v>3</v>
       </c>
-      <c r="G24" s="4">
-        <v>3</v>
-      </c>
-      <c r="H24" s="4">
-        <v>1</v>
-      </c>
-      <c r="I24" s="4">
-        <v>1</v>
-      </c>
-      <c r="J24" s="4">
-        <v>12000001</v>
-      </c>
-    </row>
-    <row r="25" s="4" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A25" s="5"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="4">
-        <v>12000002</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E25" s="4">
-        <v>10000002</v>
-      </c>
-      <c r="F25" s="4">
-        <v>3</v>
-      </c>
-      <c r="G25" s="4">
-        <v>3</v>
-      </c>
-      <c r="H25" s="4">
+      <c r="G26" s="5">
         <v>2</v>
       </c>
-      <c r="I25" s="4">
-        <v>1</v>
-      </c>
-      <c r="J25" s="4">
-        <v>12000002</v>
-      </c>
-    </row>
-    <row r="26" s="4" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A26" s="5"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="4">
-        <v>12000003</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E26" s="4">
-        <v>10000003</v>
-      </c>
-      <c r="F26" s="4">
-        <v>3</v>
-      </c>
-      <c r="G26" s="4">
-        <v>3</v>
-      </c>
-      <c r="H26" s="4">
-        <v>3</v>
-      </c>
-      <c r="I26" s="4">
-        <v>1</v>
-      </c>
-      <c r="J26" s="4">
-        <v>12000003</v>
-      </c>
-    </row>
-    <row r="27" s="4" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A27" s="5"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="4">
-        <v>12000004</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E27" s="4">
+      <c r="H26" s="5">
+        <v>0</v>
+      </c>
+      <c r="I26" s="5">
+        <v>999</v>
+      </c>
+      <c r="J26" s="5">
+        <v>0</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="3:11">
+      <c r="C27" s="5">
+        <v>10002009</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E27" s="5">
         <v>10000004</v>
       </c>
-      <c r="F27" s="4">
-        <v>3</v>
-      </c>
-      <c r="G27" s="4">
-        <v>3</v>
-      </c>
-      <c r="H27" s="4">
+      <c r="F27" s="5">
         <v>4</v>
       </c>
-      <c r="I27" s="4">
-        <v>1</v>
-      </c>
-      <c r="J27" s="4">
-        <v>12000004</v>
-      </c>
-    </row>
-    <row r="28" s="4" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A28" s="5"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="4">
-        <v>12000005</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E28" s="4">
+      <c r="G27" s="5">
+        <v>2</v>
+      </c>
+      <c r="H27" s="5">
+        <v>0</v>
+      </c>
+      <c r="I27" s="5">
+        <v>999</v>
+      </c>
+      <c r="J27" s="5">
+        <v>0</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:11">
+      <c r="C28" s="5">
+        <v>10002010</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E28" s="5">
         <v>10000005</v>
       </c>
-      <c r="F28" s="4">
-        <v>3</v>
-      </c>
-      <c r="G28" s="4">
-        <v>3</v>
-      </c>
-      <c r="H28" s="4">
+      <c r="F28" s="5">
         <v>5</v>
       </c>
-      <c r="I28" s="4">
-        <v>1</v>
-      </c>
-      <c r="J28" s="4">
-        <v>12000005</v>
-      </c>
-    </row>
-    <row r="29" s="4" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A29" s="5"/>
-      <c r="B29" s="5"/>
-      <c r="C29" s="4">
-        <v>12000006</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E29" s="4">
+      <c r="G28" s="5">
+        <v>2</v>
+      </c>
+      <c r="H28" s="5">
+        <v>0</v>
+      </c>
+      <c r="I28" s="5">
+        <v>999</v>
+      </c>
+      <c r="J28" s="5">
+        <v>0</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:11">
+      <c r="C29" s="5">
+        <v>10002011</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E29" s="5">
         <v>10000006</v>
       </c>
-      <c r="F29" s="4">
-        <v>3</v>
-      </c>
-      <c r="G29" s="4">
-        <v>3</v>
-      </c>
-      <c r="H29" s="4">
+      <c r="F29" s="5">
         <v>6</v>
       </c>
-      <c r="I29" s="4">
-        <v>1</v>
-      </c>
-      <c r="J29" s="4">
-        <v>12000006</v>
+      <c r="G29" s="5">
+        <v>2</v>
+      </c>
+      <c r="H29" s="5">
+        <v>0</v>
+      </c>
+      <c r="I29" s="5">
+        <v>999</v>
+      </c>
+      <c r="J29" s="5">
+        <v>0</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="30" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="4">
-        <v>12000007</v>
+        <v>10003001</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E30" s="4">
-        <v>10000007</v>
+        <v>10000001</v>
       </c>
       <c r="F30" s="4">
         <v>3</v>
@@ -2302,26 +2296,26 @@
         <v>3</v>
       </c>
       <c r="H30" s="4">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I30" s="4">
         <v>1</v>
       </c>
       <c r="J30" s="4">
-        <v>12000007</v>
+        <v>12000001</v>
       </c>
     </row>
     <row r="31" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
       <c r="C31" s="4">
-        <v>12000008</v>
+        <v>10003002</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E31" s="4">
-        <v>10000008</v>
+        <v>10000002</v>
       </c>
       <c r="F31" s="4">
         <v>3</v>
@@ -2330,26 +2324,26 @@
         <v>3</v>
       </c>
       <c r="H31" s="4">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I31" s="4">
         <v>1</v>
       </c>
       <c r="J31" s="4">
-        <v>12000008</v>
+        <v>12000002</v>
       </c>
     </row>
     <row r="32" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A32" s="5"/>
       <c r="B32" s="5"/>
       <c r="C32" s="4">
-        <v>12000009</v>
+        <v>10003003</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="E32" s="4">
-        <v>10000009</v>
+        <v>10000004</v>
       </c>
       <c r="F32" s="4">
         <v>3</v>
@@ -2358,26 +2352,26 @@
         <v>3</v>
       </c>
       <c r="H32" s="4">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I32" s="4">
         <v>1</v>
       </c>
       <c r="J32" s="4">
-        <v>12000009</v>
+        <v>12000003</v>
       </c>
     </row>
     <row r="33" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A33" s="5"/>
       <c r="B33" s="5"/>
       <c r="C33" s="4">
-        <v>12000010</v>
+        <v>10003004</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E33" s="4">
-        <v>10000010</v>
+        <v>10000005</v>
       </c>
       <c r="F33" s="4">
         <v>3</v>
@@ -2386,187 +2380,69 @@
         <v>3</v>
       </c>
       <c r="H33" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I33" s="4">
         <v>1</v>
       </c>
       <c r="J33" s="4">
-        <v>12000010</v>
-      </c>
-    </row>
-    <row r="34" customHeight="1" spans="3:11">
-      <c r="C34" s="5">
-        <v>13000001</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E34" s="5">
-        <v>10000001</v>
-      </c>
-      <c r="F34" s="5">
+        <v>12000004</v>
+      </c>
+    </row>
+    <row r="34" s="4" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A34" s="5"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="4">
+        <v>10003005</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E34" s="4">
+        <v>10000008</v>
+      </c>
+      <c r="F34" s="4">
+        <v>3</v>
+      </c>
+      <c r="G34" s="4">
+        <v>3</v>
+      </c>
+      <c r="H34" s="4">
+        <v>8</v>
+      </c>
+      <c r="I34" s="4">
         <v>1</v>
       </c>
-      <c r="G34" s="5">
-        <v>2</v>
-      </c>
-      <c r="H34" s="5">
-        <v>0</v>
-      </c>
-      <c r="I34" s="5">
-        <v>999</v>
-      </c>
-      <c r="J34" s="5">
-        <v>0</v>
-      </c>
-      <c r="K34" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="35" customHeight="1" spans="3:11">
-      <c r="C35" s="5">
-        <v>13000002</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E35" s="5">
-        <v>10000002</v>
-      </c>
-      <c r="F35" s="5">
-        <v>2</v>
-      </c>
-      <c r="G35" s="5">
-        <v>2</v>
-      </c>
-      <c r="H35" s="5">
-        <v>0</v>
-      </c>
-      <c r="I35" s="5">
-        <v>999</v>
-      </c>
-      <c r="J35" s="5">
-        <v>0</v>
-      </c>
-      <c r="K35" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="36" customHeight="1" spans="3:11">
-      <c r="C36" s="5">
-        <v>13000003</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E36" s="5">
-        <v>10000003</v>
-      </c>
-      <c r="F36" s="5">
+      <c r="J34" s="4">
+        <v>12000005</v>
+      </c>
+    </row>
+    <row r="35" s="4" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A35" s="5"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="4">
+        <v>10003006</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E35" s="4">
+        <v>10000010</v>
+      </c>
+      <c r="F35" s="4">
         <v>3</v>
       </c>
-      <c r="G36" s="5">
-        <v>2</v>
-      </c>
-      <c r="H36" s="5">
-        <v>0</v>
-      </c>
-      <c r="I36" s="5">
-        <v>999</v>
-      </c>
-      <c r="J36" s="5">
-        <v>0</v>
-      </c>
-      <c r="K36" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="37" customHeight="1" spans="3:11">
-      <c r="C37" s="5">
-        <v>13000004</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E37" s="5">
-        <v>10000004</v>
-      </c>
-      <c r="F37" s="5">
-        <v>4</v>
-      </c>
-      <c r="G37" s="5">
-        <v>2</v>
-      </c>
-      <c r="H37" s="5">
-        <v>0</v>
-      </c>
-      <c r="I37" s="5">
-        <v>999</v>
-      </c>
-      <c r="J37" s="5">
-        <v>0</v>
-      </c>
-      <c r="K37" s="5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="38" customHeight="1" spans="3:11">
-      <c r="C38" s="5">
-        <v>13000005</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="E38" s="5">
-        <v>10000005</v>
-      </c>
-      <c r="F38" s="5">
-        <v>5</v>
-      </c>
-      <c r="G38" s="5">
-        <v>2</v>
-      </c>
-      <c r="H38" s="5">
-        <v>0</v>
-      </c>
-      <c r="I38" s="5">
-        <v>999</v>
-      </c>
-      <c r="J38" s="5">
-        <v>0</v>
-      </c>
-      <c r="K38" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="39" customHeight="1" spans="3:11">
-      <c r="C39" s="5">
-        <v>13000006</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E39" s="5">
-        <v>10000006</v>
-      </c>
-      <c r="F39" s="5">
-        <v>6</v>
-      </c>
-      <c r="G39" s="5">
-        <v>2</v>
-      </c>
-      <c r="H39" s="5">
-        <v>0</v>
-      </c>
-      <c r="I39" s="5">
-        <v>999</v>
-      </c>
-      <c r="J39" s="5">
-        <v>0</v>
-      </c>
-      <c r="K39" s="5" t="s">
-        <v>68</v>
+      <c r="G35" s="4">
+        <v>3</v>
+      </c>
+      <c r="H35" s="4">
+        <v>10</v>
+      </c>
+      <c r="I35" s="4">
+        <v>1</v>
+      </c>
+      <c r="J35" s="4">
+        <v>12000006</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/ItemConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ItemConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="E3" authorId="0">
+    <comment ref="D3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -54,7 +54,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F3" authorId="0">
+    <comment ref="E3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -81,7 +81,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0">
+    <comment ref="F3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -106,7 +106,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="0">
+    <comment ref="G3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -163,7 +163,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J3" authorId="0">
+    <comment ref="I3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -190,11 +190,50 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="68">
+  <si>
+    <t>##var</t>
+  </si>
   <si>
     <t>Id</t>
   </si>
   <si>
+    <t>ItemName</t>
+  </si>
+  <si>
+    <t>Icon</t>
+  </si>
+  <si>
+    <t>ItemQuality</t>
+  </si>
+  <si>
+    <t>ItemType</t>
+  </si>
+  <si>
+    <t>ItemSubType</t>
+  </si>
+  <si>
+    <t>ItemPileSum</t>
+  </si>
+  <si>
+    <t>ItemEquipID</t>
+  </si>
+  <si>
+    <t>ItemDescription</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
     <t>道具名称</t>
   </si>
   <si>
@@ -217,36 +256,6 @@
   </si>
   <si>
     <t>道具描述</t>
-  </si>
-  <si>
-    <t>ItemName</t>
-  </si>
-  <si>
-    <t>Icon</t>
-  </si>
-  <si>
-    <t>ItemQuality</t>
-  </si>
-  <si>
-    <t>ItemType</t>
-  </si>
-  <si>
-    <t>ItemSubType</t>
-  </si>
-  <si>
-    <t>ItemPileSum</t>
-  </si>
-  <si>
-    <t>ItemEquipID</t>
-  </si>
-  <si>
-    <t>ItemDescription</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
   </si>
   <si>
     <t>金币</t>
@@ -842,9 +851,7 @@
       <top style="thin">
         <color theme="0"/>
       </top>
-      <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -857,7 +864,9 @@
       <top style="thin">
         <color theme="0"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1457,991 +1466,979 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
-    <col min="1" max="2" width="10.875" style="5" customWidth="1"/>
-    <col min="3" max="10" width="17.875" style="5"/>
-    <col min="11" max="11" width="70.625" style="5" customWidth="1"/>
-    <col min="12" max="16384" width="17.875" style="5"/>
+    <col min="1" max="1" width="10.875" style="5" customWidth="1"/>
+    <col min="2" max="9" width="17.875" style="5"/>
+    <col min="10" max="10" width="70.625" style="5" customWidth="1"/>
+    <col min="11" max="16384" width="17.875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1"/>
-    <row r="2" s="1" customFormat="1" customHeight="1"/>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C3" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="7" t="s">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C4" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="8" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="8" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="B2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="D2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="B3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="D3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="E3" s="8" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C5" s="6" t="s">
+      <c r="F3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="G3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="3:11">
-      <c r="C6" s="5">
+      <c r="H3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="2:10">
+      <c r="B4" s="5">
         <v>1</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>19</v>
+      <c r="C4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="5">
+        <v>1</v>
+      </c>
+      <c r="E4" s="5">
+        <v>3</v>
+      </c>
+      <c r="F4" s="5">
+        <v>1</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>99999999</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="2:10">
+      <c r="B5" s="5">
+        <v>2</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="5">
+        <v>2</v>
+      </c>
+      <c r="E5" s="5">
+        <v>5</v>
+      </c>
+      <c r="F5" s="5">
+        <v>1</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>99999999</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="2:10">
+      <c r="B6" s="5">
+        <v>3</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="5">
+        <v>3</v>
       </c>
       <c r="E6" s="5">
+        <v>5</v>
+      </c>
+      <c r="F6" s="5">
         <v>1</v>
       </c>
-      <c r="F6" s="5">
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>99999999</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="2:10">
+      <c r="B7" s="5">
+        <v>4</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="5">
+        <v>4</v>
+      </c>
+      <c r="E7" s="5">
+        <v>5</v>
+      </c>
+      <c r="F7" s="5">
+        <v>1</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>99999999</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="2:10">
+      <c r="B8" s="5">
+        <v>5</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="5">
+        <v>5</v>
+      </c>
+      <c r="E8" s="5">
+        <v>4</v>
+      </c>
+      <c r="F8" s="5">
+        <v>1</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>99999999</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A9" s="5"/>
+      <c r="B9" s="2">
+        <v>10001001</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="2">
+        <v>10000001</v>
+      </c>
+      <c r="E9" s="2">
+        <v>6</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2">
         <v>3</v>
       </c>
-      <c r="G6" s="5">
+      <c r="H9" s="2">
+        <v>99</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" ht="19.5" customHeight="1" spans="1:10">
+      <c r="A10" s="5"/>
+      <c r="B10" s="2">
+        <v>10001002</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="2">
+        <v>10000002</v>
+      </c>
+      <c r="E10" s="2">
+        <v>6</v>
+      </c>
+      <c r="F10" s="2">
         <v>1</v>
       </c>
-      <c r="H6" s="5">
-        <v>0</v>
-      </c>
-      <c r="I6" s="5">
+      <c r="G10" s="2">
+        <v>4</v>
+      </c>
+      <c r="H10" s="2">
+        <v>99</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A11" s="5"/>
+      <c r="B11" s="2">
+        <v>10001003</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="2">
+        <v>10000003</v>
+      </c>
+      <c r="E11" s="2">
+        <v>5</v>
+      </c>
+      <c r="F11" s="2">
+        <v>1</v>
+      </c>
+      <c r="G11" s="2">
+        <v>6</v>
+      </c>
+      <c r="H11" s="2">
+        <v>99</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A12" s="5"/>
+      <c r="B12" s="2">
+        <v>10001004</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="2">
+        <v>10000004</v>
+      </c>
+      <c r="E12" s="2">
+        <v>5</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2">
+        <v>5</v>
+      </c>
+      <c r="H12" s="2">
+        <v>99</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A13" s="5"/>
+      <c r="B13" s="2">
+        <v>10001005</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="2">
+        <v>10000005</v>
+      </c>
+      <c r="E13" s="2">
+        <v>5</v>
+      </c>
+      <c r="F13" s="2">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2">
+        <v>5</v>
+      </c>
+      <c r="H13" s="2">
+        <v>99</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A14" s="5"/>
+      <c r="B14" s="2">
+        <v>10001006</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="2">
+        <v>10000006</v>
+      </c>
+      <c r="E14" s="2">
+        <v>5</v>
+      </c>
+      <c r="F14" s="2">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2">
+        <v>5</v>
+      </c>
+      <c r="H14" s="2">
+        <v>99</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A15" s="5"/>
+      <c r="B15" s="2">
+        <v>10001007</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="2">
+        <v>10000007</v>
+      </c>
+      <c r="E15" s="2">
+        <v>5</v>
+      </c>
+      <c r="F15" s="2">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2">
+        <v>5</v>
+      </c>
+      <c r="H15" s="2">
+        <v>99</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A16" s="5"/>
+      <c r="B16" s="2">
+        <v>10001008</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="2">
+        <v>10000008</v>
+      </c>
+      <c r="E16" s="2">
+        <v>3</v>
+      </c>
+      <c r="F16" s="2">
+        <v>1</v>
+      </c>
+      <c r="G16" s="2">
+        <v>7</v>
+      </c>
+      <c r="H16" s="2">
+        <v>99</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A17" s="5"/>
+      <c r="B17" s="3">
+        <v>10002001</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="3">
+        <v>10000009</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2</v>
+      </c>
+      <c r="F17" s="3">
+        <v>2</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3">
         <v>99999999</v>
       </c>
-      <c r="J6" s="5">
-        <v>0</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="3:11">
-      <c r="C7" s="5">
+      <c r="I17" s="3">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A18" s="5"/>
+      <c r="B18" s="3">
+        <v>10002002</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="3">
+        <v>10000010</v>
+      </c>
+      <c r="E18" s="3">
+        <v>3</v>
+      </c>
+      <c r="F18" s="3">
         <v>2</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="5">
-        <v>2</v>
-      </c>
-      <c r="F7" s="5">
-        <v>5</v>
-      </c>
-      <c r="G7" s="5">
-        <v>1</v>
-      </c>
-      <c r="H7" s="5">
-        <v>0</v>
-      </c>
-      <c r="I7" s="5">
+      <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3">
         <v>99999999</v>
       </c>
-      <c r="J7" s="5">
-        <v>0</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="3:11">
-      <c r="C8" s="5">
-        <v>3</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="5">
-        <v>3</v>
-      </c>
-      <c r="F8" s="5">
-        <v>5</v>
-      </c>
-      <c r="G8" s="5">
-        <v>1</v>
-      </c>
-      <c r="H8" s="5">
-        <v>0</v>
-      </c>
-      <c r="I8" s="5">
-        <v>99999999</v>
-      </c>
-      <c r="J8" s="5">
-        <v>0</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="3:11">
-      <c r="C9" s="5">
+      <c r="I18" s="3">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A19" s="5"/>
+      <c r="B19" s="3">
+        <v>10002003</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="3">
+        <v>10000011</v>
+      </c>
+      <c r="E19" s="3">
         <v>4</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="5">
-        <v>4</v>
-      </c>
-      <c r="F9" s="5">
-        <v>5</v>
-      </c>
-      <c r="G9" s="5">
-        <v>1</v>
-      </c>
-      <c r="H9" s="5">
-        <v>0</v>
-      </c>
-      <c r="I9" s="5">
-        <v>99999999</v>
-      </c>
-      <c r="J9" s="5">
-        <v>0</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="3:11">
-      <c r="C10" s="5">
-        <v>5</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="5">
-        <v>5</v>
-      </c>
-      <c r="F10" s="5">
-        <v>4</v>
-      </c>
-      <c r="G10" s="5">
-        <v>1</v>
-      </c>
-      <c r="H10" s="5">
-        <v>0</v>
-      </c>
-      <c r="I10" s="5">
-        <v>99999999</v>
-      </c>
-      <c r="J10" s="5">
-        <v>0</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="2">
-        <v>10001001</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" s="2">
-        <v>10000001</v>
-      </c>
-      <c r="F11" s="2">
-        <v>6</v>
-      </c>
-      <c r="G11" s="2">
-        <v>1</v>
-      </c>
-      <c r="H11" s="2">
-        <v>3</v>
-      </c>
-      <c r="I11" s="2">
-        <v>99</v>
-      </c>
-      <c r="J11" s="2">
-        <v>0</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" s="2" customFormat="1" ht="19.5" customHeight="1" spans="1:11">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="2">
-        <v>10001002</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" s="2">
-        <v>10000002</v>
-      </c>
-      <c r="F12" s="2">
-        <v>6</v>
-      </c>
-      <c r="G12" s="2">
-        <v>1</v>
-      </c>
-      <c r="H12" s="2">
-        <v>4</v>
-      </c>
-      <c r="I12" s="2">
-        <v>99</v>
-      </c>
-      <c r="J12" s="2">
-        <v>0</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="2">
-        <v>10001003</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13" s="2">
-        <v>10000003</v>
-      </c>
-      <c r="F13" s="2">
-        <v>5</v>
-      </c>
-      <c r="G13" s="2">
-        <v>1</v>
-      </c>
-      <c r="H13" s="2">
-        <v>6</v>
-      </c>
-      <c r="I13" s="2">
-        <v>99</v>
-      </c>
-      <c r="J13" s="2">
-        <v>0</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="2">
-        <v>10001004</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E14" s="2">
-        <v>10000004</v>
-      </c>
-      <c r="F14" s="2">
-        <v>5</v>
-      </c>
-      <c r="G14" s="2">
-        <v>1</v>
-      </c>
-      <c r="H14" s="2">
-        <v>5</v>
-      </c>
-      <c r="I14" s="2">
-        <v>99</v>
-      </c>
-      <c r="J14" s="2">
-        <v>0</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" s="2" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="2">
-        <v>10001005</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E15" s="2">
-        <v>10000005</v>
-      </c>
-      <c r="F15" s="2">
-        <v>5</v>
-      </c>
-      <c r="G15" s="2">
-        <v>1</v>
-      </c>
-      <c r="H15" s="2">
-        <v>5</v>
-      </c>
-      <c r="I15" s="2">
-        <v>99</v>
-      </c>
-      <c r="J15" s="2">
-        <v>0</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" s="2" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="2">
-        <v>10001006</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E16" s="2">
-        <v>10000006</v>
-      </c>
-      <c r="F16" s="2">
-        <v>5</v>
-      </c>
-      <c r="G16" s="2">
-        <v>1</v>
-      </c>
-      <c r="H16" s="2">
-        <v>5</v>
-      </c>
-      <c r="I16" s="2">
-        <v>99</v>
-      </c>
-      <c r="J16" s="2">
-        <v>0</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="17" s="2" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="2">
-        <v>10001007</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E17" s="2">
-        <v>10000007</v>
-      </c>
-      <c r="F17" s="2">
-        <v>5</v>
-      </c>
-      <c r="G17" s="2">
-        <v>1</v>
-      </c>
-      <c r="H17" s="2">
-        <v>5</v>
-      </c>
-      <c r="I17" s="2">
-        <v>99</v>
-      </c>
-      <c r="J17" s="2">
-        <v>0</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="18" s="2" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="2">
-        <v>10001008</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E18" s="2">
-        <v>10000008</v>
-      </c>
-      <c r="F18" s="2">
-        <v>3</v>
-      </c>
-      <c r="G18" s="2">
-        <v>1</v>
-      </c>
-      <c r="H18" s="2">
-        <v>7</v>
-      </c>
-      <c r="I18" s="2">
-        <v>99</v>
-      </c>
-      <c r="J18" s="2">
-        <v>0</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="19" s="3" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="3">
-        <v>10002001</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E19" s="3">
-        <v>10000009</v>
       </c>
       <c r="F19" s="3">
         <v>2</v>
       </c>
       <c r="G19" s="3">
+        <v>0</v>
+      </c>
+      <c r="H19" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="I19" s="3">
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A20" s="5"/>
+      <c r="B20" s="3">
+        <v>10002004</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" s="3">
+        <v>10000012</v>
+      </c>
+      <c r="E20" s="3">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3">
         <v>2</v>
       </c>
-      <c r="H19" s="3">
-        <v>0</v>
-      </c>
-      <c r="I19" s="3">
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>99999999</v>
       </c>
-      <c r="J19" s="3">
-        <v>0</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="20" s="3" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="3">
-        <v>10002002</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E20" s="3">
-        <v>10000010</v>
-      </c>
-      <c r="F20" s="3">
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A21" s="5"/>
+      <c r="B21" s="3">
+        <v>10002005</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21" s="3">
+        <v>10000013</v>
+      </c>
+      <c r="E21" s="3">
+        <v>6</v>
+      </c>
+      <c r="F21" s="3">
+        <v>2</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="2:10">
+      <c r="B22" s="5">
+        <v>10002006</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22" s="5">
+        <v>10000001</v>
+      </c>
+      <c r="E22" s="5">
+        <v>1</v>
+      </c>
+      <c r="F22" s="5">
+        <v>2</v>
+      </c>
+      <c r="G22" s="5">
+        <v>0</v>
+      </c>
+      <c r="H22" s="5">
+        <v>999</v>
+      </c>
+      <c r="I22" s="5">
+        <v>0</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="2:10">
+      <c r="B23" s="5">
+        <v>10002007</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D23" s="5">
+        <v>10000002</v>
+      </c>
+      <c r="E23" s="5">
+        <v>2</v>
+      </c>
+      <c r="F23" s="5">
+        <v>2</v>
+      </c>
+      <c r="G23" s="5">
+        <v>0</v>
+      </c>
+      <c r="H23" s="5">
+        <v>999</v>
+      </c>
+      <c r="I23" s="5">
+        <v>0</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="2:10">
+      <c r="B24" s="5">
+        <v>10002008</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" s="5">
+        <v>10000003</v>
+      </c>
+      <c r="E24" s="5">
         <v>3</v>
       </c>
-      <c r="G20" s="3">
+      <c r="F24" s="5">
         <v>2</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>99999999</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="21" s="3" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="3">
-        <v>10002003</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E21" s="3">
-        <v>10000011</v>
-      </c>
-      <c r="F21" s="3">
+      <c r="G24" s="5">
+        <v>0</v>
+      </c>
+      <c r="H24" s="5">
+        <v>999</v>
+      </c>
+      <c r="I24" s="5">
+        <v>0</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="2:10">
+      <c r="B25" s="5">
+        <v>10002009</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="5">
+        <v>10000004</v>
+      </c>
+      <c r="E25" s="5">
         <v>4</v>
-      </c>
-      <c r="G21" s="3">
-        <v>2</v>
-      </c>
-      <c r="H21" s="3">
-        <v>0</v>
-      </c>
-      <c r="I21" s="3">
-        <v>99999999</v>
-      </c>
-      <c r="J21" s="3">
-        <v>0</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="22" s="3" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="3">
-        <v>10002004</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E22" s="3">
-        <v>10000012</v>
-      </c>
-      <c r="F22" s="3">
-        <v>5</v>
-      </c>
-      <c r="G22" s="3">
-        <v>2</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>99999999</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="23" s="3" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="3">
-        <v>10002005</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E23" s="3">
-        <v>10000013</v>
-      </c>
-      <c r="F23" s="3">
-        <v>6</v>
-      </c>
-      <c r="G23" s="3">
-        <v>2</v>
-      </c>
-      <c r="H23" s="3">
-        <v>0</v>
-      </c>
-      <c r="I23" s="3">
-        <v>99999999</v>
-      </c>
-      <c r="J23" s="3">
-        <v>0</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="3:11">
-      <c r="C24" s="5">
-        <v>10002006</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E24" s="5">
-        <v>10000001</v>
-      </c>
-      <c r="F24" s="5">
-        <v>1</v>
-      </c>
-      <c r="G24" s="5">
-        <v>2</v>
-      </c>
-      <c r="H24" s="5">
-        <v>0</v>
-      </c>
-      <c r="I24" s="5">
-        <v>999</v>
-      </c>
-      <c r="J24" s="5">
-        <v>0</v>
-      </c>
-      <c r="K24" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="25" customHeight="1" spans="3:11">
-      <c r="C25" s="5">
-        <v>10002007</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E25" s="5">
-        <v>10000002</v>
       </c>
       <c r="F25" s="5">
         <v>2</v>
       </c>
       <c r="G25" s="5">
+        <v>0</v>
+      </c>
+      <c r="H25" s="5">
+        <v>999</v>
+      </c>
+      <c r="I25" s="5">
+        <v>0</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="2:10">
+      <c r="B26" s="5">
+        <v>10002010</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D26" s="5">
+        <v>10000005</v>
+      </c>
+      <c r="E26" s="5">
+        <v>5</v>
+      </c>
+      <c r="F26" s="5">
         <v>2</v>
       </c>
-      <c r="H25" s="5">
-        <v>0</v>
-      </c>
-      <c r="I25" s="5">
+      <c r="G26" s="5">
+        <v>0</v>
+      </c>
+      <c r="H26" s="5">
         <v>999</v>
       </c>
-      <c r="J25" s="5">
-        <v>0</v>
-      </c>
-      <c r="K25" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="3:11">
-      <c r="C26" s="5">
-        <v>10002008</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E26" s="5">
-        <v>10000003</v>
-      </c>
-      <c r="F26" s="5">
+      <c r="I26" s="5">
+        <v>0</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="2:10">
+      <c r="B27" s="5">
+        <v>10002011</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D27" s="5">
+        <v>10000006</v>
+      </c>
+      <c r="E27" s="5">
+        <v>6</v>
+      </c>
+      <c r="F27" s="5">
+        <v>2</v>
+      </c>
+      <c r="G27" s="5">
+        <v>0</v>
+      </c>
+      <c r="H27" s="5">
+        <v>999</v>
+      </c>
+      <c r="I27" s="5">
+        <v>0</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="28" s="4" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A28" s="5"/>
+      <c r="B28" s="4">
+        <v>10003001</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D28" s="4">
+        <v>10000001</v>
+      </c>
+      <c r="E28" s="4">
         <v>3</v>
       </c>
-      <c r="G26" s="5">
+      <c r="F28" s="4">
+        <v>3</v>
+      </c>
+      <c r="G28" s="4">
+        <v>1</v>
+      </c>
+      <c r="H28" s="4">
+        <v>1</v>
+      </c>
+      <c r="I28" s="4">
+        <v>12000001</v>
+      </c>
+    </row>
+    <row r="29" s="4" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A29" s="5"/>
+      <c r="B29" s="4">
+        <v>10003002</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D29" s="4">
+        <v>10000002</v>
+      </c>
+      <c r="E29" s="4">
+        <v>3</v>
+      </c>
+      <c r="F29" s="4">
+        <v>3</v>
+      </c>
+      <c r="G29" s="4">
         <v>2</v>
       </c>
-      <c r="H26" s="5">
-        <v>0</v>
-      </c>
-      <c r="I26" s="5">
-        <v>999</v>
-      </c>
-      <c r="J26" s="5">
-        <v>0</v>
-      </c>
-      <c r="K26" s="5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="3:11">
-      <c r="C27" s="5">
-        <v>10002009</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E27" s="5">
+      <c r="H29" s="4">
+        <v>1</v>
+      </c>
+      <c r="I29" s="4">
+        <v>12000002</v>
+      </c>
+    </row>
+    <row r="30" s="4" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A30" s="5"/>
+      <c r="B30" s="4">
+        <v>10003003</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D30" s="4">
         <v>10000004</v>
       </c>
-      <c r="F27" s="5">
-        <v>4</v>
-      </c>
-      <c r="G27" s="5">
-        <v>2</v>
-      </c>
-      <c r="H27" s="5">
-        <v>0</v>
-      </c>
-      <c r="I27" s="5">
-        <v>999</v>
-      </c>
-      <c r="J27" s="5">
-        <v>0</v>
-      </c>
-      <c r="K27" s="5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="3:11">
-      <c r="C28" s="5">
-        <v>10002010</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E28" s="5">
-        <v>10000005</v>
-      </c>
-      <c r="F28" s="5">
-        <v>5</v>
-      </c>
-      <c r="G28" s="5">
-        <v>2</v>
-      </c>
-      <c r="H28" s="5">
-        <v>0</v>
-      </c>
-      <c r="I28" s="5">
-        <v>999</v>
-      </c>
-      <c r="J28" s="5">
-        <v>0</v>
-      </c>
-      <c r="K28" s="5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="3:11">
-      <c r="C29" s="5">
-        <v>10002011</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E29" s="5">
-        <v>10000006</v>
-      </c>
-      <c r="F29" s="5">
-        <v>6</v>
-      </c>
-      <c r="G29" s="5">
-        <v>2</v>
-      </c>
-      <c r="H29" s="5">
-        <v>0</v>
-      </c>
-      <c r="I29" s="5">
-        <v>999</v>
-      </c>
-      <c r="J29" s="5">
-        <v>0</v>
-      </c>
-      <c r="K29" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="30" s="4" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A30" s="5"/>
-      <c r="B30" s="5"/>
-      <c r="C30" s="4">
-        <v>10003001</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>59</v>
-      </c>
       <c r="E30" s="4">
-        <v>10000001</v>
+        <v>3</v>
       </c>
       <c r="F30" s="4">
         <v>3</v>
       </c>
       <c r="G30" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H30" s="4">
         <v>1</v>
       </c>
       <c r="I30" s="4">
-        <v>1</v>
-      </c>
-      <c r="J30" s="4">
-        <v>12000001</v>
-      </c>
-    </row>
-    <row r="31" s="4" customFormat="1" customHeight="1" spans="1:10">
+        <v>12000003</v>
+      </c>
+    </row>
+    <row r="31" s="4" customFormat="1" customHeight="1" spans="1:9">
       <c r="A31" s="5"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="4">
-        <v>10003002</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>60</v>
+      <c r="B31" s="4">
+        <v>10003004</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D31" s="4">
+        <v>10000005</v>
       </c>
       <c r="E31" s="4">
-        <v>10000002</v>
+        <v>3</v>
       </c>
       <c r="F31" s="4">
         <v>3</v>
       </c>
       <c r="G31" s="4">
+        <v>5</v>
+      </c>
+      <c r="H31" s="4">
+        <v>1</v>
+      </c>
+      <c r="I31" s="4">
+        <v>12000004</v>
+      </c>
+    </row>
+    <row r="32" s="4" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A32" s="5"/>
+      <c r="B32" s="4">
+        <v>10003005</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D32" s="4">
+        <v>10000008</v>
+      </c>
+      <c r="E32" s="4">
         <v>3</v>
-      </c>
-      <c r="H31" s="4">
-        <v>2</v>
-      </c>
-      <c r="I31" s="4">
-        <v>1</v>
-      </c>
-      <c r="J31" s="4">
-        <v>12000002</v>
-      </c>
-    </row>
-    <row r="32" s="4" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A32" s="5"/>
-      <c r="B32" s="5"/>
-      <c r="C32" s="4">
-        <v>10003003</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E32" s="4">
-        <v>10000004</v>
       </c>
       <c r="F32" s="4">
         <v>3</v>
       </c>
       <c r="G32" s="4">
+        <v>8</v>
+      </c>
+      <c r="H32" s="4">
+        <v>1</v>
+      </c>
+      <c r="I32" s="4">
+        <v>12000005</v>
+      </c>
+    </row>
+    <row r="33" s="4" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A33" s="5"/>
+      <c r="B33" s="4">
+        <v>10003006</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D33" s="4">
+        <v>10000010</v>
+      </c>
+      <c r="E33" s="4">
         <v>3</v>
-      </c>
-      <c r="H32" s="4">
-        <v>4</v>
-      </c>
-      <c r="I32" s="4">
-        <v>1</v>
-      </c>
-      <c r="J32" s="4">
-        <v>12000003</v>
-      </c>
-    </row>
-    <row r="33" s="4" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A33" s="5"/>
-      <c r="B33" s="5"/>
-      <c r="C33" s="4">
-        <v>10003004</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E33" s="4">
-        <v>10000005</v>
       </c>
       <c r="F33" s="4">
         <v>3</v>
       </c>
       <c r="G33" s="4">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H33" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I33" s="4">
-        <v>1</v>
-      </c>
-      <c r="J33" s="4">
-        <v>12000004</v>
-      </c>
-    </row>
-    <row r="34" s="4" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A34" s="5"/>
-      <c r="B34" s="5"/>
-      <c r="C34" s="4">
-        <v>10003005</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E34" s="4">
-        <v>10000008</v>
-      </c>
-      <c r="F34" s="4">
-        <v>3</v>
-      </c>
-      <c r="G34" s="4">
-        <v>3</v>
-      </c>
-      <c r="H34" s="4">
-        <v>8</v>
-      </c>
-      <c r="I34" s="4">
-        <v>1</v>
-      </c>
-      <c r="J34" s="4">
-        <v>12000005</v>
-      </c>
-    </row>
-    <row r="35" s="4" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A35" s="5"/>
-      <c r="B35" s="5"/>
-      <c r="C35" s="4">
-        <v>10003006</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E35" s="4">
-        <v>10000010</v>
-      </c>
-      <c r="F35" s="4">
-        <v>3</v>
-      </c>
-      <c r="G35" s="4">
-        <v>3</v>
-      </c>
-      <c r="H35" s="4">
-        <v>10</v>
-      </c>
-      <c r="I35" s="4">
-        <v>1</v>
-      </c>
-      <c r="J35" s="4">
         <v>12000006</v>
       </c>
     </row>

--- a/Unity/Assets/Config/Excel/ItemConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ItemConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12795"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -152,14 +152,10 @@
           <t>当道具类型为3（装备）时该字段的意义
 1 头盔
 2 衣服
-3 腰带
-4 裤子
-5 鞋子
-6 戒指
-7 手镯
-8 项链
-9 饰品
-10 武器</t>
+3 裤子
+4 鞋子
+5 项链
+6 武器</t>
         </r>
       </text>
     </comment>

--- a/Unity/Assets/Config/Excel/ItemConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ItemConfig.xlsx
@@ -581,7 +581,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="宋体"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -592,7 +592,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="微软雅黑"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -2285,7 +2285,7 @@
         <v>62</v>
       </c>
       <c r="D28" s="4">
-        <v>10000001</v>
+        <v>10003001</v>
       </c>
       <c r="E28" s="4">
         <v>3</v>
@@ -2312,7 +2312,7 @@
         <v>63</v>
       </c>
       <c r="D29" s="4">
-        <v>10000002</v>
+        <v>10003002</v>
       </c>
       <c r="E29" s="4">
         <v>3</v>
@@ -2339,7 +2339,7 @@
         <v>64</v>
       </c>
       <c r="D30" s="4">
-        <v>10000004</v>
+        <v>10003003</v>
       </c>
       <c r="E30" s="4">
         <v>3</v>
@@ -2366,7 +2366,7 @@
         <v>65</v>
       </c>
       <c r="D31" s="4">
-        <v>10000005</v>
+        <v>10003004</v>
       </c>
       <c r="E31" s="4">
         <v>3</v>
@@ -2393,7 +2393,7 @@
         <v>66</v>
       </c>
       <c r="D32" s="4">
-        <v>10000008</v>
+        <v>10003005</v>
       </c>
       <c r="E32" s="4">
         <v>3</v>
@@ -2420,7 +2420,7 @@
         <v>67</v>
       </c>
       <c r="D33" s="4">
-        <v>10000010</v>
+        <v>10003006</v>
       </c>
       <c r="E33" s="4">
         <v>3</v>

--- a/Unity/Assets/Config/Excel/ItemConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ItemConfig.xlsx
@@ -186,7 +186,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="74">
   <si>
     <t>##var</t>
   </si>
@@ -377,19 +377,37 @@
     <t>一个头盔</t>
   </si>
   <si>
+    <t>这是一个装备1</t>
+  </si>
+  <si>
     <t>一个衣服</t>
   </si>
   <si>
+    <t>这是一个装备2</t>
+  </si>
+  <si>
     <t>一个裤子</t>
   </si>
   <si>
+    <t>这是一个装备3</t>
+  </si>
+  <si>
     <t>一个鞋子</t>
   </si>
   <si>
+    <t>这是一个装备4</t>
+  </si>
+  <si>
     <t>一个项链</t>
   </si>
   <si>
+    <t>这是一个装备5</t>
+  </si>
+  <si>
     <t>一个武器</t>
+  </si>
+  <si>
+    <t>这是一个装备6</t>
   </si>
 </sst>
 </file>
@@ -1973,7 +1991,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="3">
-        <v>99999999</v>
+        <v>999</v>
       </c>
       <c r="I17" s="3">
         <v>0</v>
@@ -2003,7 +2021,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="3">
-        <v>99999999</v>
+        <v>999</v>
       </c>
       <c r="I18" s="3">
         <v>0</v>
@@ -2033,7 +2051,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="3">
-        <v>99999999</v>
+        <v>999</v>
       </c>
       <c r="I19" s="3">
         <v>0</v>
@@ -2063,7 +2081,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>99999999</v>
+        <v>999</v>
       </c>
       <c r="I20" s="3">
         <v>0</v>
@@ -2093,7 +2111,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="3">
-        <v>99999999</v>
+        <v>999</v>
       </c>
       <c r="I21" s="3">
         <v>0</v>
@@ -2276,7 +2294,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="28" s="4" customFormat="1" customHeight="1" spans="1:9">
+    <row r="28" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A28" s="5"/>
       <c r="B28" s="4">
         <v>10003001</v>
@@ -2302,14 +2320,17 @@
       <c r="I28" s="4">
         <v>12000001</v>
       </c>
-    </row>
-    <row r="29" s="4" customFormat="1" customHeight="1" spans="1:9">
+      <c r="J28" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A29" s="5"/>
       <c r="B29" s="4">
         <v>10003002</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D29" s="4">
         <v>10003002</v>
@@ -2329,14 +2350,17 @@
       <c r="I29" s="4">
         <v>12000002</v>
       </c>
-    </row>
-    <row r="30" s="4" customFormat="1" customHeight="1" spans="1:9">
+      <c r="J29" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A30" s="5"/>
       <c r="B30" s="4">
         <v>10003003</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D30" s="4">
         <v>10003003</v>
@@ -2356,14 +2380,17 @@
       <c r="I30" s="4">
         <v>12000003</v>
       </c>
-    </row>
-    <row r="31" s="4" customFormat="1" customHeight="1" spans="1:9">
+      <c r="J30" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="31" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A31" s="5"/>
       <c r="B31" s="4">
         <v>10003004</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D31" s="4">
         <v>10003004</v>
@@ -2383,14 +2410,17 @@
       <c r="I31" s="4">
         <v>12000004</v>
       </c>
-    </row>
-    <row r="32" s="4" customFormat="1" customHeight="1" spans="1:9">
+      <c r="J31" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="32" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A32" s="5"/>
       <c r="B32" s="4">
         <v>10003005</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D32" s="4">
         <v>10003005</v>
@@ -2410,14 +2440,17 @@
       <c r="I32" s="4">
         <v>12000005</v>
       </c>
-    </row>
-    <row r="33" s="4" customFormat="1" customHeight="1" spans="1:9">
+      <c r="J32" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="33" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A33" s="5"/>
       <c r="B33" s="4">
         <v>10003006</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D33" s="4">
         <v>10003006</v>
@@ -2436,6 +2469,9 @@
       </c>
       <c r="I33" s="4">
         <v>12000006</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/ItemConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ItemConfig.xlsx
@@ -1,38 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\DreamGit\Unity\Assets\Config\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA2CB342-8C6C-44AA-9013-C193D7B3F9E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="D3" authorId="0">
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -54,7 +47,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E3" authorId="0">
+    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -81,7 +74,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F3" authorId="0">
+    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -106,7 +99,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0">
+    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -159,7 +152,33 @@
         </r>
       </text>
     </comment>
-    <comment ref="I3" authorId="0">
+    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{DA4D1309-08C8-4F8D-90F2-C6D3694F89B8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1.金币</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -186,7 +205,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="79">
   <si>
     <t>##var</t>
   </si>
@@ -408,19 +427,33 @@
   </si>
   <si>
     <t>这是一个装备6</t>
+  </si>
+  <si>
+    <t>出售货币类型</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>出售货币值</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>SellMoneyType</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>SellMoneyValue</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="27">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -448,147 +481,10 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -613,31 +509,41 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="37">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14996795556505"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -653,186 +559,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -883,254 +615,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -1139,84 +629,40 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 6" xfId="49"/>
+    <cellStyle name="常规 6" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1474,1009 +920,1217 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:J33"/>
-  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L33"/>
+  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.875" style="5" customWidth="1"/>
-    <col min="2" max="9" width="17.875" style="5"/>
-    <col min="10" max="10" width="70.625" style="5" customWidth="1"/>
-    <col min="11" max="16384" width="17.875" style="5"/>
+    <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
+    <col min="2" max="11" width="17.875" style="2"/>
+    <col min="12" max="12" width="70.625" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="17.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:10">
+    <row r="1" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="7" t="s">
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="K1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="L1" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:10">
+    <row r="2" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H2" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="K2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="L2" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:10">
+    <row r="3" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="8" t="s">
+      <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="J3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="K3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="L3" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="2:10">
-      <c r="B4" s="5">
-        <v>1</v>
-      </c>
-      <c r="C4" s="5" t="s">
+    <row r="4" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="2">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="5">
-        <v>1</v>
-      </c>
-      <c r="E4" s="5">
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2">
         <v>3</v>
       </c>
-      <c r="F4" s="5">
-        <v>1</v>
-      </c>
-      <c r="G4" s="5">
-        <v>0</v>
-      </c>
-      <c r="H4" s="5">
+      <c r="F4" s="2">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2">
+        <v>100</v>
+      </c>
+      <c r="J4" s="2">
         <v>99999999</v>
       </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5" t="s">
+      <c r="K4" s="2">
+        <v>0</v>
+      </c>
+      <c r="L4" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="2:10">
-      <c r="B5" s="5">
+    <row r="5" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="2">
         <v>2</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="2">
         <v>2</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="2">
         <v>5</v>
       </c>
-      <c r="F5" s="5">
-        <v>1</v>
-      </c>
-      <c r="G5" s="5">
-        <v>0</v>
-      </c>
-      <c r="H5" s="5">
+      <c r="F5" s="2">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2">
+        <v>1</v>
+      </c>
+      <c r="I5" s="2">
+        <f>I4+100</f>
+        <v>200</v>
+      </c>
+      <c r="J5" s="2">
         <v>99999999</v>
       </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5" t="s">
+      <c r="K5" s="2">
+        <v>0</v>
+      </c>
+      <c r="L5" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="2:10">
-      <c r="B6" s="5">
+    <row r="6" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="2">
         <v>3</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="2">
         <v>3</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="2">
         <v>5</v>
       </c>
-      <c r="F6" s="5">
-        <v>1</v>
-      </c>
-      <c r="G6" s="5">
-        <v>0</v>
-      </c>
-      <c r="H6" s="5">
+      <c r="F6" s="2">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2">
+        <f t="shared" ref="I6:I33" si="0">I5+100</f>
+        <v>300</v>
+      </c>
+      <c r="J6" s="2">
         <v>99999999</v>
       </c>
-      <c r="I6" s="5">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5" t="s">
+      <c r="K6" s="2">
+        <v>0</v>
+      </c>
+      <c r="L6" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="2:10">
-      <c r="B7" s="5">
+    <row r="7" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="2">
         <v>4</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="2">
         <v>4</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="2">
         <v>5</v>
       </c>
-      <c r="F7" s="5">
-        <v>1</v>
-      </c>
-      <c r="G7" s="5">
-        <v>0</v>
-      </c>
-      <c r="H7" s="5">
+      <c r="F7" s="2">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="J7" s="2">
         <v>99999999</v>
       </c>
-      <c r="I7" s="5">
-        <v>0</v>
-      </c>
-      <c r="J7" s="5" t="s">
+      <c r="K7" s="2">
+        <v>0</v>
+      </c>
+      <c r="L7" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="2:10">
-      <c r="B8" s="5">
+    <row r="8" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="2">
         <v>5</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="2">
         <v>5</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="2">
         <v>4</v>
       </c>
-      <c r="F8" s="5">
-        <v>1</v>
-      </c>
-      <c r="G8" s="5">
-        <v>0</v>
-      </c>
-      <c r="H8" s="5">
+      <c r="F8" s="2">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="J8" s="2">
         <v>99999999</v>
       </c>
-      <c r="I8" s="5">
-        <v>0</v>
-      </c>
-      <c r="J8" s="5" t="s">
+      <c r="K8" s="2">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A9" s="5"/>
-      <c r="B9" s="2">
+    <row r="9" spans="1:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="8">
         <v>10001001</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="8">
         <v>10000001</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="8">
         <v>6</v>
       </c>
-      <c r="F9" s="2">
-        <v>1</v>
-      </c>
-      <c r="G9" s="2">
+      <c r="F9" s="8">
+        <v>1</v>
+      </c>
+      <c r="G9" s="8">
         <v>3</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="8">
+        <v>1</v>
+      </c>
+      <c r="I9" s="2">
+        <f t="shared" si="0"/>
+        <v>600</v>
+      </c>
+      <c r="J9" s="8">
         <v>99</v>
       </c>
-      <c r="I9" s="2">
-        <v>0</v>
-      </c>
-      <c r="J9" s="2" t="s">
+      <c r="K9" s="8">
+        <v>0</v>
+      </c>
+      <c r="L9" s="8" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A10" s="5"/>
-      <c r="B10" s="2">
+    <row r="10" spans="1:12" s="8" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="8">
         <v>10001002</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="8">
         <v>10000002</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="8">
         <v>6</v>
       </c>
-      <c r="F10" s="2">
-        <v>1</v>
-      </c>
-      <c r="G10" s="2">
+      <c r="F10" s="8">
+        <v>1</v>
+      </c>
+      <c r="G10" s="8">
         <v>4</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="8">
+        <v>1</v>
+      </c>
+      <c r="I10" s="2">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="J10" s="8">
         <v>99</v>
       </c>
-      <c r="I10" s="2">
-        <v>0</v>
-      </c>
-      <c r="J10" s="2" t="s">
+      <c r="K10" s="8">
+        <v>0</v>
+      </c>
+      <c r="L10" s="8" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A11" s="5"/>
-      <c r="B11" s="2">
+    <row r="11" spans="1:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="8">
         <v>10001003</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="8">
         <v>10000003</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="8">
         <v>5</v>
       </c>
-      <c r="F11" s="2">
-        <v>1</v>
-      </c>
-      <c r="G11" s="2">
+      <c r="F11" s="8">
+        <v>1</v>
+      </c>
+      <c r="G11" s="8">
         <v>6</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="8">
+        <v>1</v>
+      </c>
+      <c r="I11" s="2">
+        <f t="shared" si="0"/>
+        <v>800</v>
+      </c>
+      <c r="J11" s="8">
         <v>99</v>
       </c>
-      <c r="I11" s="2">
-        <v>0</v>
-      </c>
-      <c r="J11" s="2" t="s">
+      <c r="K11" s="8">
+        <v>0</v>
+      </c>
+      <c r="L11" s="8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A12" s="5"/>
-      <c r="B12" s="2">
+    <row r="12" spans="1:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="8">
         <v>10001004</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="8">
         <v>10000004</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="8">
         <v>5</v>
       </c>
-      <c r="F12" s="2">
-        <v>1</v>
-      </c>
-      <c r="G12" s="2">
+      <c r="F12" s="8">
+        <v>1</v>
+      </c>
+      <c r="G12" s="8">
         <v>5</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" s="8">
+        <v>1</v>
+      </c>
+      <c r="I12" s="2">
+        <f t="shared" si="0"/>
+        <v>900</v>
+      </c>
+      <c r="J12" s="8">
         <v>99</v>
       </c>
-      <c r="I12" s="2">
-        <v>0</v>
-      </c>
-      <c r="J12" s="2" t="s">
+      <c r="K12" s="8">
+        <v>0</v>
+      </c>
+      <c r="L12" s="8" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A13" s="5"/>
-      <c r="B13" s="2">
+    <row r="13" spans="1:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="8">
         <v>10001005</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="8">
         <v>10000005</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="8">
         <v>5</v>
       </c>
-      <c r="F13" s="2">
-        <v>1</v>
-      </c>
-      <c r="G13" s="2">
+      <c r="F13" s="8">
+        <v>1</v>
+      </c>
+      <c r="G13" s="8">
         <v>5</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="8">
+        <v>1</v>
+      </c>
+      <c r="I13" s="2">
+        <f t="shared" si="0"/>
+        <v>1000</v>
+      </c>
+      <c r="J13" s="8">
         <v>99</v>
       </c>
-      <c r="I13" s="2">
-        <v>0</v>
-      </c>
-      <c r="J13" s="2" t="s">
+      <c r="K13" s="8">
+        <v>0</v>
+      </c>
+      <c r="L13" s="8" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A14" s="5"/>
-      <c r="B14" s="2">
+    <row r="14" spans="1:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="8">
         <v>10001006</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="8">
         <v>10000006</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="8">
         <v>5</v>
       </c>
-      <c r="F14" s="2">
-        <v>1</v>
-      </c>
-      <c r="G14" s="2">
+      <c r="F14" s="8">
+        <v>1</v>
+      </c>
+      <c r="G14" s="8">
         <v>5</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H14" s="8">
+        <v>1</v>
+      </c>
+      <c r="I14" s="2">
+        <f t="shared" si="0"/>
+        <v>1100</v>
+      </c>
+      <c r="J14" s="8">
         <v>99</v>
       </c>
-      <c r="I14" s="2">
-        <v>0</v>
-      </c>
-      <c r="J14" s="2" t="s">
+      <c r="K14" s="8">
+        <v>0</v>
+      </c>
+      <c r="L14" s="8" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="15" s="2" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A15" s="5"/>
-      <c r="B15" s="2">
+    <row r="15" spans="1:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="8">
         <v>10001007</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="8">
         <v>10000007</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="8">
         <v>5</v>
       </c>
-      <c r="F15" s="2">
-        <v>1</v>
-      </c>
-      <c r="G15" s="2">
+      <c r="F15" s="8">
+        <v>1</v>
+      </c>
+      <c r="G15" s="8">
         <v>5</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15" s="8">
+        <v>1</v>
+      </c>
+      <c r="I15" s="2">
+        <f t="shared" si="0"/>
+        <v>1200</v>
+      </c>
+      <c r="J15" s="8">
         <v>99</v>
       </c>
-      <c r="I15" s="2">
-        <v>0</v>
-      </c>
-      <c r="J15" s="2" t="s">
+      <c r="K15" s="8">
+        <v>0</v>
+      </c>
+      <c r="L15" s="8" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="16" s="2" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A16" s="5"/>
-      <c r="B16" s="2">
+    <row r="16" spans="1:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="8">
         <v>10001008</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="8">
         <v>10000008</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="8">
         <v>3</v>
       </c>
-      <c r="F16" s="2">
-        <v>1</v>
-      </c>
-      <c r="G16" s="2">
+      <c r="F16" s="8">
+        <v>1</v>
+      </c>
+      <c r="G16" s="8">
         <v>7</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16" s="8">
+        <v>1</v>
+      </c>
+      <c r="I16" s="2">
+        <f t="shared" si="0"/>
+        <v>1300</v>
+      </c>
+      <c r="J16" s="8">
         <v>99</v>
       </c>
-      <c r="I16" s="2">
-        <v>0</v>
-      </c>
-      <c r="J16" s="2" t="s">
+      <c r="K16" s="8">
+        <v>0</v>
+      </c>
+      <c r="L16" s="8" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="17" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A17" s="5"/>
-      <c r="B17" s="3">
+    <row r="17" spans="2:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="8">
         <v>10002001</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="8">
         <v>10000009</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="8">
         <v>2</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="8">
         <v>2</v>
       </c>
-      <c r="G17" s="3">
-        <v>0</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="G17" s="8">
+        <v>0</v>
+      </c>
+      <c r="H17" s="8">
+        <v>1</v>
+      </c>
+      <c r="I17" s="2">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="J17" s="8">
         <v>999</v>
       </c>
-      <c r="I17" s="3">
-        <v>0</v>
-      </c>
-      <c r="J17" s="3" t="s">
+      <c r="K17" s="8">
+        <v>0</v>
+      </c>
+      <c r="L17" s="8" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="18" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A18" s="5"/>
-      <c r="B18" s="3">
+    <row r="18" spans="2:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="8">
         <v>10002002</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="8">
         <v>10000010</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="8">
         <v>3</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="8">
         <v>2</v>
       </c>
-      <c r="G18" s="3">
-        <v>0</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="G18" s="8">
+        <v>0</v>
+      </c>
+      <c r="H18" s="8">
+        <v>1</v>
+      </c>
+      <c r="I18" s="2">
+        <f t="shared" si="0"/>
+        <v>1500</v>
+      </c>
+      <c r="J18" s="8">
         <v>999</v>
       </c>
-      <c r="I18" s="3">
-        <v>0</v>
-      </c>
-      <c r="J18" s="3" t="s">
+      <c r="K18" s="8">
+        <v>0</v>
+      </c>
+      <c r="L18" s="8" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="19" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A19" s="5"/>
-      <c r="B19" s="3">
+    <row r="19" spans="2:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="8">
         <v>10002003</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="8">
         <v>10000011</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="8">
         <v>4</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="8">
         <v>2</v>
       </c>
-      <c r="G19" s="3">
-        <v>0</v>
-      </c>
-      <c r="H19" s="3">
+      <c r="G19" s="8">
+        <v>0</v>
+      </c>
+      <c r="H19" s="8">
+        <v>1</v>
+      </c>
+      <c r="I19" s="2">
+        <f t="shared" si="0"/>
+        <v>1600</v>
+      </c>
+      <c r="J19" s="8">
         <v>999</v>
       </c>
-      <c r="I19" s="3">
-        <v>0</v>
-      </c>
-      <c r="J19" s="3" t="s">
+      <c r="K19" s="8">
+        <v>0</v>
+      </c>
+      <c r="L19" s="8" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="20" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A20" s="5"/>
-      <c r="B20" s="3">
+    <row r="20" spans="2:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="8">
         <v>10002004</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="8">
         <v>10000012</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="8">
         <v>5</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="8">
         <v>2</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="G20" s="8">
+        <v>0</v>
+      </c>
+      <c r="H20" s="8">
+        <v>1</v>
+      </c>
+      <c r="I20" s="2">
+        <f t="shared" si="0"/>
+        <v>1700</v>
+      </c>
+      <c r="J20" s="8">
         <v>999</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="s">
+      <c r="K20" s="8">
+        <v>0</v>
+      </c>
+      <c r="L20" s="8" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="21" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A21" s="5"/>
-      <c r="B21" s="3">
+    <row r="21" spans="2:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="8">
         <v>10002005</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="8">
         <v>10000013</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21" s="8">
         <v>6</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="8">
         <v>2</v>
       </c>
-      <c r="G21" s="3">
-        <v>0</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="G21" s="8">
+        <v>0</v>
+      </c>
+      <c r="H21" s="8">
+        <v>1</v>
+      </c>
+      <c r="I21" s="2">
+        <f t="shared" si="0"/>
+        <v>1800</v>
+      </c>
+      <c r="J21" s="8">
         <v>999</v>
       </c>
-      <c r="I21" s="3">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3" t="s">
+      <c r="K21" s="8">
+        <v>0</v>
+      </c>
+      <c r="L21" s="8" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="2:10">
-      <c r="B22" s="5">
+    <row r="22" spans="2:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="8">
         <v>10002006</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D22" s="8">
         <v>10000001</v>
       </c>
-      <c r="E22" s="5">
-        <v>1</v>
-      </c>
-      <c r="F22" s="5">
+      <c r="E22" s="8">
+        <v>1</v>
+      </c>
+      <c r="F22" s="8">
         <v>2</v>
       </c>
-      <c r="G22" s="5">
-        <v>0</v>
-      </c>
-      <c r="H22" s="5">
+      <c r="G22" s="8">
+        <v>0</v>
+      </c>
+      <c r="H22" s="8">
+        <v>1</v>
+      </c>
+      <c r="I22" s="2">
+        <f t="shared" si="0"/>
+        <v>1900</v>
+      </c>
+      <c r="J22" s="8">
         <v>999</v>
       </c>
-      <c r="I22" s="5">
-        <v>0</v>
-      </c>
-      <c r="J22" s="5" t="s">
+      <c r="K22" s="8">
+        <v>0</v>
+      </c>
+      <c r="L22" s="8" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="23" customHeight="1" spans="2:10">
-      <c r="B23" s="5">
+    <row r="23" spans="2:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="8">
         <v>10002007</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="D23" s="5">
+      <c r="D23" s="8">
         <v>10000002</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E23" s="8">
         <v>2</v>
       </c>
-      <c r="F23" s="5">
+      <c r="F23" s="8">
         <v>2</v>
       </c>
-      <c r="G23" s="5">
-        <v>0</v>
-      </c>
-      <c r="H23" s="5">
+      <c r="G23" s="8">
+        <v>0</v>
+      </c>
+      <c r="H23" s="8">
+        <v>1</v>
+      </c>
+      <c r="I23" s="2">
+        <f t="shared" si="0"/>
+        <v>2000</v>
+      </c>
+      <c r="J23" s="8">
         <v>999</v>
       </c>
-      <c r="I23" s="5">
-        <v>0</v>
-      </c>
-      <c r="J23" s="5" t="s">
+      <c r="K23" s="8">
+        <v>0</v>
+      </c>
+      <c r="L23" s="8" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="2:10">
-      <c r="B24" s="5">
+    <row r="24" spans="2:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="8">
         <v>10002008</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D24" s="5">
+      <c r="D24" s="8">
         <v>10000003</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E24" s="8">
         <v>3</v>
       </c>
-      <c r="F24" s="5">
+      <c r="F24" s="8">
         <v>2</v>
       </c>
-      <c r="G24" s="5">
-        <v>0</v>
-      </c>
-      <c r="H24" s="5">
+      <c r="G24" s="8">
+        <v>0</v>
+      </c>
+      <c r="H24" s="8">
+        <v>1</v>
+      </c>
+      <c r="I24" s="2">
+        <f t="shared" si="0"/>
+        <v>2100</v>
+      </c>
+      <c r="J24" s="8">
         <v>999</v>
       </c>
-      <c r="I24" s="5">
-        <v>0</v>
-      </c>
-      <c r="J24" s="5" t="s">
+      <c r="K24" s="8">
+        <v>0</v>
+      </c>
+      <c r="L24" s="8" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="2:10">
-      <c r="B25" s="5">
+    <row r="25" spans="2:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="8">
         <v>10002009</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D25" s="5">
+      <c r="D25" s="8">
         <v>10000004</v>
       </c>
-      <c r="E25" s="5">
+      <c r="E25" s="8">
         <v>4</v>
       </c>
-      <c r="F25" s="5">
+      <c r="F25" s="8">
         <v>2</v>
       </c>
-      <c r="G25" s="5">
-        <v>0</v>
-      </c>
-      <c r="H25" s="5">
+      <c r="G25" s="8">
+        <v>0</v>
+      </c>
+      <c r="H25" s="8">
+        <v>1</v>
+      </c>
+      <c r="I25" s="2">
+        <f t="shared" si="0"/>
+        <v>2200</v>
+      </c>
+      <c r="J25" s="8">
         <v>999</v>
       </c>
-      <c r="I25" s="5">
-        <v>0</v>
-      </c>
-      <c r="J25" s="5" t="s">
+      <c r="K25" s="8">
+        <v>0</v>
+      </c>
+      <c r="L25" s="8" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="2:10">
-      <c r="B26" s="5">
+    <row r="26" spans="2:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="8">
         <v>10002010</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="D26" s="5">
+      <c r="D26" s="8">
         <v>10000005</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E26" s="8">
         <v>5</v>
       </c>
-      <c r="F26" s="5">
+      <c r="F26" s="8">
         <v>2</v>
       </c>
-      <c r="G26" s="5">
-        <v>0</v>
-      </c>
-      <c r="H26" s="5">
+      <c r="G26" s="8">
+        <v>0</v>
+      </c>
+      <c r="H26" s="8">
+        <v>1</v>
+      </c>
+      <c r="I26" s="2">
+        <f t="shared" si="0"/>
+        <v>2300</v>
+      </c>
+      <c r="J26" s="8">
         <v>999</v>
       </c>
-      <c r="I26" s="5">
-        <v>0</v>
-      </c>
-      <c r="J26" s="5" t="s">
+      <c r="K26" s="8">
+        <v>0</v>
+      </c>
+      <c r="L26" s="8" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="27" customHeight="1" spans="2:10">
-      <c r="B27" s="5">
+    <row r="27" spans="2:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B27" s="8">
         <v>10002011</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D27" s="5">
+      <c r="D27" s="8">
         <v>10000006</v>
       </c>
-      <c r="E27" s="5">
+      <c r="E27" s="8">
         <v>6</v>
       </c>
-      <c r="F27" s="5">
+      <c r="F27" s="8">
         <v>2</v>
       </c>
-      <c r="G27" s="5">
-        <v>0</v>
-      </c>
-      <c r="H27" s="5">
+      <c r="G27" s="8">
+        <v>0</v>
+      </c>
+      <c r="H27" s="8">
+        <v>1</v>
+      </c>
+      <c r="I27" s="2">
+        <f t="shared" si="0"/>
+        <v>2400</v>
+      </c>
+      <c r="J27" s="8">
         <v>999</v>
       </c>
-      <c r="I27" s="5">
-        <v>0</v>
-      </c>
-      <c r="J27" s="5" t="s">
+      <c r="K27" s="8">
+        <v>0</v>
+      </c>
+      <c r="L27" s="8" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="28" s="4" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A28" s="5"/>
-      <c r="B28" s="4">
+    <row r="28" spans="2:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="8">
         <v>10003001</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D28" s="8">
         <v>10003001</v>
       </c>
-      <c r="E28" s="4">
+      <c r="E28" s="8">
         <v>3</v>
       </c>
-      <c r="F28" s="4">
+      <c r="F28" s="8">
         <v>3</v>
       </c>
-      <c r="G28" s="4">
-        <v>1</v>
-      </c>
-      <c r="H28" s="4">
-        <v>1</v>
-      </c>
-      <c r="I28" s="4">
+      <c r="G28" s="8">
+        <v>1</v>
+      </c>
+      <c r="H28" s="8">
+        <v>1</v>
+      </c>
+      <c r="I28" s="2">
+        <f t="shared" si="0"/>
+        <v>2500</v>
+      </c>
+      <c r="J28" s="8">
+        <v>1</v>
+      </c>
+      <c r="K28" s="8">
         <v>12000001</v>
       </c>
-      <c r="J28" s="4" t="s">
+      <c r="L28" s="8" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="29" s="4" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A29" s="5"/>
-      <c r="B29" s="4">
+    <row r="29" spans="2:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="8">
         <v>10003002</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D29" s="8">
         <v>10003002</v>
       </c>
-      <c r="E29" s="4">
+      <c r="E29" s="8">
         <v>3</v>
       </c>
-      <c r="F29" s="4">
+      <c r="F29" s="8">
         <v>3</v>
       </c>
-      <c r="G29" s="4">
+      <c r="G29" s="8">
         <v>2</v>
       </c>
-      <c r="H29" s="4">
-        <v>1</v>
-      </c>
-      <c r="I29" s="4">
+      <c r="H29" s="8">
+        <v>1</v>
+      </c>
+      <c r="I29" s="2">
+        <f t="shared" si="0"/>
+        <v>2600</v>
+      </c>
+      <c r="J29" s="8">
+        <v>1</v>
+      </c>
+      <c r="K29" s="8">
         <v>12000002</v>
       </c>
-      <c r="J29" s="4" t="s">
+      <c r="L29" s="8" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="30" s="4" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A30" s="5"/>
-      <c r="B30" s="4">
+    <row r="30" spans="2:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="8">
         <v>10003003</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="D30" s="4">
+      <c r="D30" s="8">
         <v>10003003</v>
       </c>
-      <c r="E30" s="4">
+      <c r="E30" s="8">
         <v>3</v>
       </c>
-      <c r="F30" s="4">
+      <c r="F30" s="8">
         <v>3</v>
       </c>
-      <c r="G30" s="4">
+      <c r="G30" s="8">
         <v>4</v>
       </c>
-      <c r="H30" s="4">
-        <v>1</v>
-      </c>
-      <c r="I30" s="4">
+      <c r="H30" s="8">
+        <v>1</v>
+      </c>
+      <c r="I30" s="2">
+        <f t="shared" si="0"/>
+        <v>2700</v>
+      </c>
+      <c r="J30" s="8">
+        <v>1</v>
+      </c>
+      <c r="K30" s="8">
         <v>12000003</v>
       </c>
-      <c r="J30" s="4" t="s">
+      <c r="L30" s="8" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="31" s="4" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A31" s="5"/>
-      <c r="B31" s="4">
+    <row r="31" spans="2:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="8">
         <v>10003004</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="D31" s="4">
+      <c r="D31" s="8">
         <v>10003004</v>
       </c>
-      <c r="E31" s="4">
+      <c r="E31" s="8">
         <v>3</v>
       </c>
-      <c r="F31" s="4">
+      <c r="F31" s="8">
         <v>3</v>
       </c>
-      <c r="G31" s="4">
+      <c r="G31" s="8">
         <v>5</v>
       </c>
-      <c r="H31" s="4">
-        <v>1</v>
-      </c>
-      <c r="I31" s="4">
+      <c r="H31" s="8">
+        <v>1</v>
+      </c>
+      <c r="I31" s="2">
+        <f t="shared" si="0"/>
+        <v>2800</v>
+      </c>
+      <c r="J31" s="8">
+        <v>1</v>
+      </c>
+      <c r="K31" s="8">
         <v>12000004</v>
       </c>
-      <c r="J31" s="4" t="s">
+      <c r="L31" s="8" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="32" s="4" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A32" s="5"/>
-      <c r="B32" s="4">
+    <row r="32" spans="2:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="8">
         <v>10003005</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="D32" s="4">
+      <c r="D32" s="8">
         <v>10003005</v>
       </c>
-      <c r="E32" s="4">
+      <c r="E32" s="8">
         <v>3</v>
       </c>
-      <c r="F32" s="4">
+      <c r="F32" s="8">
         <v>3</v>
       </c>
-      <c r="G32" s="4">
+      <c r="G32" s="8">
         <v>8</v>
       </c>
-      <c r="H32" s="4">
-        <v>1</v>
-      </c>
-      <c r="I32" s="4">
+      <c r="H32" s="8">
+        <v>1</v>
+      </c>
+      <c r="I32" s="2">
+        <f t="shared" si="0"/>
+        <v>2900</v>
+      </c>
+      <c r="J32" s="8">
+        <v>1</v>
+      </c>
+      <c r="K32" s="8">
         <v>12000005</v>
       </c>
-      <c r="J32" s="4" t="s">
+      <c r="L32" s="8" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="33" s="4" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A33" s="5"/>
-      <c r="B33" s="4">
+    <row r="33" spans="2:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="8">
         <v>10003006</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="D33" s="4">
+      <c r="D33" s="8">
         <v>10003006</v>
       </c>
-      <c r="E33" s="4">
+      <c r="E33" s="8">
         <v>3</v>
       </c>
-      <c r="F33" s="4">
+      <c r="F33" s="8">
         <v>3</v>
       </c>
-      <c r="G33" s="4">
+      <c r="G33" s="8">
         <v>10</v>
       </c>
-      <c r="H33" s="4">
-        <v>1</v>
-      </c>
-      <c r="I33" s="4">
+      <c r="H33" s="8">
+        <v>1</v>
+      </c>
+      <c r="I33" s="2">
+        <f t="shared" si="0"/>
+        <v>3000</v>
+      </c>
+      <c r="J33" s="8">
+        <v>1</v>
+      </c>
+      <c r="K33" s="8">
         <v>12000006</v>
       </c>
-      <c r="J33" s="4" t="s">
+      <c r="L33" s="8" t="s">
         <v>73</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Unity/Assets/Config/Excel/ItemConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ItemConfig.xlsx
@@ -1,31 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\DreamGit\Unity\Assets\Config\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA2CB342-8C6C-44AA-9013-C193D7B3F9E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="D3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -47,7 +54,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="E3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -74,7 +81,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="F3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -99,7 +106,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="G3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -152,15 +159,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{DA4D1309-08C8-4F8D-90F2-C6D3694F89B8}">
+    <comment ref="H3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
-            <color indexed="81"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -168,9 +173,7 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -178,7 +181,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="K3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -205,7 +208,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="78">
   <si>
     <t>##var</t>
   </si>
@@ -228,6 +231,12 @@
     <t>ItemSubType</t>
   </si>
   <si>
+    <t>SellMoneyType</t>
+  </si>
+  <si>
+    <t>SellMoneyValue</t>
+  </si>
+  <si>
     <t>ItemPileSum</t>
   </si>
   <si>
@@ -264,6 +273,12 @@
     <t>道具子类</t>
   </si>
   <si>
+    <t>出售货币类型</t>
+  </si>
+  <si>
+    <t>出售货币值</t>
+  </si>
+  <si>
     <t>道具堆叠最大数量</t>
   </si>
   <si>
@@ -427,33 +442,19 @@
   </si>
   <si>
     <t>这是一个装备6</t>
-  </si>
-  <si>
-    <t>出售货币类型</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>出售货币值</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>SellMoneyType</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>SellMoneyValue</t>
-    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -481,11 +482,159 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -495,7 +644,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="微软雅黑"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -504,41 +653,8 @@
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="0"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -547,6 +663,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -559,12 +681,192 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -615,12 +917,254 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -629,40 +1173,84 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 6" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 6" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -920,1217 +1508,1217 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L33"/>
-  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
-    <col min="2" max="11" width="17.875" style="2"/>
-    <col min="12" max="12" width="70.625" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="17.875" style="2"/>
+    <col min="1" max="1" width="10.875" style="3" customWidth="1"/>
+    <col min="2" max="11" width="17.875" style="3"/>
+    <col min="12" max="12" width="70.625" style="3" customWidth="1"/>
+    <col min="13" max="16384" width="17.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="J1" s="4" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="B3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="D3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="E3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="J3" s="5" t="s">
+      <c r="F3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="G3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="H3" s="8" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="2">
-        <v>1</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="I3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="2">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2">
+      <c r="J3" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="2:12">
+      <c r="B4" s="3">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3">
         <v>3</v>
       </c>
-      <c r="F4" s="2">
-        <v>1</v>
-      </c>
-      <c r="G4" s="2">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2">
-        <v>1</v>
-      </c>
-      <c r="I4" s="2">
+      <c r="F4" s="3">
+        <v>1</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3">
+        <v>1</v>
+      </c>
+      <c r="I4" s="3">
         <v>100</v>
       </c>
-      <c r="J4" s="2">
+      <c r="J4" s="3">
         <v>99999999</v>
       </c>
-      <c r="K4" s="2">
-        <v>0</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="2">
+      <c r="K4" s="3">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="2:12">
+      <c r="B5" s="3">
         <v>2</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="2">
+      <c r="C5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="3">
         <v>2</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="3">
         <v>5</v>
       </c>
-      <c r="F5" s="2">
-        <v>1</v>
-      </c>
-      <c r="G5" s="2">
-        <v>0</v>
-      </c>
-      <c r="H5" s="2">
-        <v>1</v>
-      </c>
-      <c r="I5" s="2">
+      <c r="F5" s="3">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
+        <v>1</v>
+      </c>
+      <c r="I5" s="3">
         <f>I4+100</f>
         <v>200</v>
       </c>
-      <c r="J5" s="2">
+      <c r="J5" s="3">
         <v>99999999</v>
       </c>
-      <c r="K5" s="2">
-        <v>0</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="2">
+      <c r="K5" s="3">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="2:12">
+      <c r="B6" s="3">
         <v>3</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="2">
+      <c r="C6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="3">
         <v>3</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="3">
         <v>5</v>
       </c>
-      <c r="F6" s="2">
-        <v>1</v>
-      </c>
-      <c r="G6" s="2">
-        <v>0</v>
-      </c>
-      <c r="H6" s="2">
-        <v>1</v>
-      </c>
-      <c r="I6" s="2">
+      <c r="F6" s="3">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
+        <v>1</v>
+      </c>
+      <c r="I6" s="3">
         <f t="shared" ref="I6:I33" si="0">I5+100</f>
         <v>300</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6" s="3">
         <v>99999999</v>
       </c>
-      <c r="K6" s="2">
-        <v>0</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="2">
+      <c r="K6" s="3">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="2:12">
+      <c r="B7" s="3">
         <v>4</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="2">
+      <c r="C7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="3">
         <v>4</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="3">
         <v>5</v>
       </c>
-      <c r="F7" s="2">
-        <v>1</v>
-      </c>
-      <c r="G7" s="2">
-        <v>0</v>
-      </c>
-      <c r="H7" s="2">
-        <v>1</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="F7" s="3">
+        <v>1</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3">
+        <v>1</v>
+      </c>
+      <c r="I7" s="3">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="J7" s="2">
+      <c r="J7" s="3">
         <v>99999999</v>
       </c>
-      <c r="K7" s="2">
-        <v>0</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="2">
+      <c r="K7" s="3">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="2:12">
+      <c r="B8" s="3">
         <v>5</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="2">
+      <c r="C8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="3">
         <v>5</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="3">
         <v>4</v>
       </c>
-      <c r="F8" s="2">
-        <v>1</v>
-      </c>
-      <c r="G8" s="2">
-        <v>0</v>
-      </c>
-      <c r="H8" s="2">
-        <v>1</v>
-      </c>
-      <c r="I8" s="2">
+      <c r="F8" s="3">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
+        <v>1</v>
+      </c>
+      <c r="I8" s="3">
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
-      <c r="J8" s="2">
+      <c r="J8" s="3">
         <v>99999999</v>
       </c>
-      <c r="K8" s="2">
-        <v>0</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="8">
+      <c r="K8" s="3">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B9" s="2">
         <v>10001001</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="8">
+      <c r="C9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="2">
         <v>10000001</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="2">
         <v>6</v>
       </c>
-      <c r="F9" s="8">
-        <v>1</v>
-      </c>
-      <c r="G9" s="8">
+      <c r="F9" s="2">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2">
         <v>3</v>
       </c>
-      <c r="H9" s="8">
-        <v>1</v>
-      </c>
-      <c r="I9" s="2">
+      <c r="H9" s="2">
+        <v>1</v>
+      </c>
+      <c r="I9" s="3">
         <f t="shared" si="0"/>
         <v>600</v>
       </c>
-      <c r="J9" s="8">
+      <c r="J9" s="2">
         <v>99</v>
       </c>
-      <c r="K9" s="8">
-        <v>0</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" s="8" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="8">
+      <c r="K9" s="2">
+        <v>0</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" ht="19.5" customHeight="1" spans="2:12">
+      <c r="B10" s="2">
         <v>10001002</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="8">
+      <c r="C10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="2">
         <v>10000002</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="2">
         <v>6</v>
       </c>
-      <c r="F10" s="8">
-        <v>1</v>
-      </c>
-      <c r="G10" s="8">
+      <c r="F10" s="2">
+        <v>1</v>
+      </c>
+      <c r="G10" s="2">
         <v>4</v>
       </c>
-      <c r="H10" s="8">
-        <v>1</v>
-      </c>
-      <c r="I10" s="2">
+      <c r="H10" s="2">
+        <v>1</v>
+      </c>
+      <c r="I10" s="3">
         <f t="shared" si="0"/>
         <v>700</v>
       </c>
-      <c r="J10" s="8">
+      <c r="J10" s="2">
         <v>99</v>
       </c>
-      <c r="K10" s="8">
-        <v>0</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="8">
+      <c r="K10" s="2">
+        <v>0</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B11" s="2">
         <v>10001003</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" s="8">
+      <c r="C11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="2">
         <v>10000003</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="2">
         <v>5</v>
       </c>
-      <c r="F11" s="8">
-        <v>1</v>
-      </c>
-      <c r="G11" s="8">
+      <c r="F11" s="2">
+        <v>1</v>
+      </c>
+      <c r="G11" s="2">
         <v>6</v>
       </c>
-      <c r="H11" s="8">
-        <v>1</v>
-      </c>
-      <c r="I11" s="2">
+      <c r="H11" s="2">
+        <v>1</v>
+      </c>
+      <c r="I11" s="3">
         <f t="shared" si="0"/>
         <v>800</v>
       </c>
-      <c r="J11" s="8">
+      <c r="J11" s="2">
         <v>99</v>
       </c>
-      <c r="K11" s="8">
-        <v>0</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="8">
+      <c r="K11" s="2">
+        <v>0</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B12" s="2">
         <v>10001004</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" s="8">
+      <c r="C12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="2">
         <v>10000004</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="2">
         <v>5</v>
       </c>
-      <c r="F12" s="8">
-        <v>1</v>
-      </c>
-      <c r="G12" s="8">
+      <c r="F12" s="2">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2">
         <v>5</v>
       </c>
-      <c r="H12" s="8">
-        <v>1</v>
-      </c>
-      <c r="I12" s="2">
+      <c r="H12" s="2">
+        <v>1</v>
+      </c>
+      <c r="I12" s="3">
         <f t="shared" si="0"/>
         <v>900</v>
       </c>
-      <c r="J12" s="8">
+      <c r="J12" s="2">
         <v>99</v>
       </c>
-      <c r="K12" s="8">
-        <v>0</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="8">
+      <c r="K12" s="2">
+        <v>0</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B13" s="2">
         <v>10001005</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D13" s="8">
+      <c r="C13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="2">
         <v>10000005</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="2">
         <v>5</v>
       </c>
-      <c r="F13" s="8">
-        <v>1</v>
-      </c>
-      <c r="G13" s="8">
+      <c r="F13" s="2">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2">
         <v>5</v>
       </c>
-      <c r="H13" s="8">
-        <v>1</v>
-      </c>
-      <c r="I13" s="2">
+      <c r="H13" s="2">
+        <v>1</v>
+      </c>
+      <c r="I13" s="3">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
-      <c r="J13" s="8">
+      <c r="J13" s="2">
         <v>99</v>
       </c>
-      <c r="K13" s="8">
-        <v>0</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="8">
+      <c r="K13" s="2">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B14" s="2">
         <v>10001006</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" s="8">
+      <c r="C14" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="2">
         <v>10000006</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="2">
         <v>5</v>
       </c>
-      <c r="F14" s="8">
-        <v>1</v>
-      </c>
-      <c r="G14" s="8">
+      <c r="F14" s="2">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2">
         <v>5</v>
       </c>
-      <c r="H14" s="8">
-        <v>1</v>
-      </c>
-      <c r="I14" s="2">
+      <c r="H14" s="2">
+        <v>1</v>
+      </c>
+      <c r="I14" s="3">
         <f t="shared" si="0"/>
         <v>1100</v>
       </c>
-      <c r="J14" s="8">
+      <c r="J14" s="2">
         <v>99</v>
       </c>
-      <c r="K14" s="8">
-        <v>0</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="8">
+      <c r="K14" s="2">
+        <v>0</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B15" s="2">
         <v>10001007</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" s="8">
+      <c r="C15" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="2">
         <v>10000007</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="2">
         <v>5</v>
       </c>
-      <c r="F15" s="8">
-        <v>1</v>
-      </c>
-      <c r="G15" s="8">
+      <c r="F15" s="2">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2">
         <v>5</v>
       </c>
-      <c r="H15" s="8">
-        <v>1</v>
-      </c>
-      <c r="I15" s="2">
+      <c r="H15" s="2">
+        <v>1</v>
+      </c>
+      <c r="I15" s="3">
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
-      <c r="J15" s="8">
+      <c r="J15" s="2">
         <v>99</v>
       </c>
-      <c r="K15" s="8">
-        <v>0</v>
-      </c>
-      <c r="L15" s="8" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="8">
+      <c r="K15" s="2">
+        <v>0</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B16" s="2">
         <v>10001008</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" s="8">
+      <c r="C16" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="2">
         <v>10000008</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="2">
         <v>3</v>
       </c>
-      <c r="F16" s="8">
-        <v>1</v>
-      </c>
-      <c r="G16" s="8">
+      <c r="F16" s="2">
+        <v>1</v>
+      </c>
+      <c r="G16" s="2">
         <v>7</v>
       </c>
-      <c r="H16" s="8">
-        <v>1</v>
-      </c>
-      <c r="I16" s="2">
+      <c r="H16" s="2">
+        <v>1</v>
+      </c>
+      <c r="I16" s="3">
         <f t="shared" si="0"/>
         <v>1300</v>
       </c>
-      <c r="J16" s="8">
+      <c r="J16" s="2">
         <v>99</v>
       </c>
-      <c r="K16" s="8">
-        <v>0</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="2:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="8">
+      <c r="K16" s="2">
+        <v>0</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B17" s="2">
         <v>10002001</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D17" s="8">
+      <c r="C17" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="2">
         <v>10000009</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="2">
         <v>2</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F17" s="2">
         <v>2</v>
       </c>
-      <c r="G17" s="8">
-        <v>0</v>
-      </c>
-      <c r="H17" s="8">
-        <v>1</v>
-      </c>
-      <c r="I17" s="2">
+      <c r="G17" s="2">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2">
+        <v>1</v>
+      </c>
+      <c r="I17" s="3">
         <f t="shared" si="0"/>
         <v>1400</v>
       </c>
-      <c r="J17" s="8">
+      <c r="J17" s="2">
         <v>999</v>
       </c>
-      <c r="K17" s="8">
-        <v>0</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="18" spans="2:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="8">
+      <c r="K17" s="2">
+        <v>0</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B18" s="2">
         <v>10002002</v>
       </c>
-      <c r="C18" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D18" s="8">
+      <c r="C18" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" s="2">
         <v>10000010</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="2">
         <v>3</v>
       </c>
-      <c r="F18" s="8">
+      <c r="F18" s="2">
         <v>2</v>
       </c>
-      <c r="G18" s="8">
-        <v>0</v>
-      </c>
-      <c r="H18" s="8">
-        <v>1</v>
-      </c>
-      <c r="I18" s="2">
+      <c r="G18" s="2">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2">
+        <v>1</v>
+      </c>
+      <c r="I18" s="3">
         <f t="shared" si="0"/>
         <v>1500</v>
       </c>
-      <c r="J18" s="8">
+      <c r="J18" s="2">
         <v>999</v>
       </c>
-      <c r="K18" s="8">
-        <v>0</v>
-      </c>
-      <c r="L18" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" spans="2:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="8">
+      <c r="K18" s="2">
+        <v>0</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B19" s="2">
         <v>10002003</v>
       </c>
-      <c r="C19" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D19" s="8">
+      <c r="C19" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="2">
         <v>10000011</v>
       </c>
-      <c r="E19" s="8">
+      <c r="E19" s="2">
         <v>4</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="2">
         <v>2</v>
       </c>
-      <c r="G19" s="8">
-        <v>0</v>
-      </c>
-      <c r="H19" s="8">
-        <v>1</v>
-      </c>
-      <c r="I19" s="2">
+      <c r="G19" s="2">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2">
+        <v>1</v>
+      </c>
+      <c r="I19" s="3">
         <f t="shared" si="0"/>
         <v>1600</v>
       </c>
-      <c r="J19" s="8">
+      <c r="J19" s="2">
         <v>999</v>
       </c>
-      <c r="K19" s="8">
-        <v>0</v>
-      </c>
-      <c r="L19" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="20" spans="2:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="8">
+      <c r="K19" s="2">
+        <v>0</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B20" s="2">
         <v>10002004</v>
       </c>
-      <c r="C20" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D20" s="8">
+      <c r="C20" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" s="2">
         <v>10000012</v>
       </c>
-      <c r="E20" s="8">
+      <c r="E20" s="2">
         <v>5</v>
       </c>
-      <c r="F20" s="8">
+      <c r="F20" s="2">
         <v>2</v>
       </c>
-      <c r="G20" s="8">
-        <v>0</v>
-      </c>
-      <c r="H20" s="8">
-        <v>1</v>
-      </c>
-      <c r="I20" s="2">
+      <c r="G20" s="2">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2">
+        <v>1</v>
+      </c>
+      <c r="I20" s="3">
         <f t="shared" si="0"/>
         <v>1700</v>
       </c>
-      <c r="J20" s="8">
+      <c r="J20" s="2">
         <v>999</v>
       </c>
-      <c r="K20" s="8">
-        <v>0</v>
-      </c>
-      <c r="L20" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="21" spans="2:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="8">
+      <c r="K20" s="2">
+        <v>0</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B21" s="2">
         <v>10002005</v>
       </c>
-      <c r="C21" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D21" s="8">
+      <c r="C21" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" s="2">
         <v>10000013</v>
       </c>
-      <c r="E21" s="8">
+      <c r="E21" s="2">
         <v>6</v>
       </c>
-      <c r="F21" s="8">
+      <c r="F21" s="2">
         <v>2</v>
       </c>
-      <c r="G21" s="8">
-        <v>0</v>
-      </c>
-      <c r="H21" s="8">
-        <v>1</v>
-      </c>
-      <c r="I21" s="2">
+      <c r="G21" s="2">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2">
+        <v>1</v>
+      </c>
+      <c r="I21" s="3">
         <f t="shared" si="0"/>
         <v>1800</v>
       </c>
-      <c r="J21" s="8">
+      <c r="J21" s="2">
         <v>999</v>
       </c>
-      <c r="K21" s="8">
-        <v>0</v>
-      </c>
-      <c r="L21" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="22" spans="2:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="8">
+      <c r="K21" s="2">
+        <v>0</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B22" s="2">
         <v>10002006</v>
       </c>
-      <c r="C22" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="D22" s="8">
+      <c r="C22" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" s="2">
         <v>10000001</v>
       </c>
-      <c r="E22" s="8">
-        <v>1</v>
-      </c>
-      <c r="F22" s="8">
+      <c r="E22" s="2">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
         <v>2</v>
       </c>
-      <c r="G22" s="8">
-        <v>0</v>
-      </c>
-      <c r="H22" s="8">
-        <v>1</v>
-      </c>
-      <c r="I22" s="2">
+      <c r="G22" s="2">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2">
+        <v>1</v>
+      </c>
+      <c r="I22" s="3">
         <f t="shared" si="0"/>
         <v>1900</v>
       </c>
-      <c r="J22" s="8">
+      <c r="J22" s="2">
         <v>999</v>
       </c>
-      <c r="K22" s="8">
-        <v>0</v>
-      </c>
-      <c r="L22" s="8" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="23" spans="2:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="8">
+      <c r="K22" s="2">
+        <v>0</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B23" s="2">
         <v>10002007</v>
       </c>
-      <c r="C23" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D23" s="8">
+      <c r="C23" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" s="2">
         <v>10000002</v>
       </c>
-      <c r="E23" s="8">
+      <c r="E23" s="2">
         <v>2</v>
       </c>
-      <c r="F23" s="8">
+      <c r="F23" s="2">
         <v>2</v>
       </c>
-      <c r="G23" s="8">
-        <v>0</v>
-      </c>
-      <c r="H23" s="8">
-        <v>1</v>
-      </c>
-      <c r="I23" s="2">
+      <c r="G23" s="2">
+        <v>0</v>
+      </c>
+      <c r="H23" s="2">
+        <v>1</v>
+      </c>
+      <c r="I23" s="3">
         <f t="shared" si="0"/>
         <v>2000</v>
       </c>
-      <c r="J23" s="8">
+      <c r="J23" s="2">
         <v>999</v>
       </c>
-      <c r="K23" s="8">
-        <v>0</v>
-      </c>
-      <c r="L23" s="8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="24" spans="2:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="8">
+      <c r="K23" s="2">
+        <v>0</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B24" s="2">
         <v>10002008</v>
       </c>
-      <c r="C24" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="D24" s="8">
+      <c r="C24" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" s="2">
         <v>10000003</v>
       </c>
-      <c r="E24" s="8">
+      <c r="E24" s="2">
         <v>3</v>
       </c>
-      <c r="F24" s="8">
+      <c r="F24" s="2">
         <v>2</v>
       </c>
-      <c r="G24" s="8">
-        <v>0</v>
-      </c>
-      <c r="H24" s="8">
-        <v>1</v>
-      </c>
-      <c r="I24" s="2">
+      <c r="G24" s="2">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2">
+        <v>1</v>
+      </c>
+      <c r="I24" s="3">
         <f t="shared" si="0"/>
         <v>2100</v>
       </c>
-      <c r="J24" s="8">
+      <c r="J24" s="2">
         <v>999</v>
       </c>
-      <c r="K24" s="8">
-        <v>0</v>
-      </c>
-      <c r="L24" s="8" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="25" spans="2:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="8">
+      <c r="K24" s="2">
+        <v>0</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B25" s="2">
         <v>10002009</v>
       </c>
-      <c r="C25" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D25" s="8">
+      <c r="C25" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D25" s="2">
         <v>10000004</v>
       </c>
-      <c r="E25" s="8">
+      <c r="E25" s="2">
         <v>4</v>
       </c>
-      <c r="F25" s="8">
+      <c r="F25" s="2">
         <v>2</v>
       </c>
-      <c r="G25" s="8">
-        <v>0</v>
-      </c>
-      <c r="H25" s="8">
-        <v>1</v>
-      </c>
-      <c r="I25" s="2">
+      <c r="G25" s="2">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2">
+        <v>1</v>
+      </c>
+      <c r="I25" s="3">
         <f t="shared" si="0"/>
         <v>2200</v>
       </c>
-      <c r="J25" s="8">
+      <c r="J25" s="2">
         <v>999</v>
       </c>
-      <c r="K25" s="8">
-        <v>0</v>
-      </c>
-      <c r="L25" s="8" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="26" spans="2:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="8">
+      <c r="K25" s="2">
+        <v>0</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B26" s="2">
         <v>10002010</v>
       </c>
-      <c r="C26" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="D26" s="8">
+      <c r="C26" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D26" s="2">
         <v>10000005</v>
       </c>
-      <c r="E26" s="8">
+      <c r="E26" s="2">
         <v>5</v>
       </c>
-      <c r="F26" s="8">
+      <c r="F26" s="2">
         <v>2</v>
       </c>
-      <c r="G26" s="8">
-        <v>0</v>
-      </c>
-      <c r="H26" s="8">
-        <v>1</v>
-      </c>
-      <c r="I26" s="2">
+      <c r="G26" s="2">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2">
+        <v>1</v>
+      </c>
+      <c r="I26" s="3">
         <f t="shared" si="0"/>
         <v>2300</v>
       </c>
-      <c r="J26" s="8">
+      <c r="J26" s="2">
         <v>999</v>
       </c>
-      <c r="K26" s="8">
-        <v>0</v>
-      </c>
-      <c r="L26" s="8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="27" spans="2:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="8">
+      <c r="K26" s="2">
+        <v>0</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B27" s="2">
         <v>10002011</v>
       </c>
-      <c r="C27" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="D27" s="8">
+      <c r="C27" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27" s="2">
         <v>10000006</v>
       </c>
-      <c r="E27" s="8">
+      <c r="E27" s="2">
         <v>6</v>
       </c>
-      <c r="F27" s="8">
+      <c r="F27" s="2">
         <v>2</v>
       </c>
-      <c r="G27" s="8">
-        <v>0</v>
-      </c>
-      <c r="H27" s="8">
-        <v>1</v>
-      </c>
-      <c r="I27" s="2">
+      <c r="G27" s="2">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2">
+        <v>1</v>
+      </c>
+      <c r="I27" s="3">
         <f t="shared" si="0"/>
         <v>2400</v>
       </c>
-      <c r="J27" s="8">
+      <c r="J27" s="2">
         <v>999</v>
       </c>
-      <c r="K27" s="8">
-        <v>0</v>
-      </c>
-      <c r="L27" s="8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="28" spans="2:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="8">
+      <c r="K27" s="2">
+        <v>0</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B28" s="2">
         <v>10003001</v>
       </c>
-      <c r="C28" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="D28" s="8">
+      <c r="C28" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D28" s="2">
         <v>10003001</v>
       </c>
-      <c r="E28" s="8">
+      <c r="E28" s="2">
         <v>3</v>
       </c>
-      <c r="F28" s="8">
+      <c r="F28" s="2">
         <v>3</v>
       </c>
-      <c r="G28" s="8">
-        <v>1</v>
-      </c>
-      <c r="H28" s="8">
-        <v>1</v>
-      </c>
-      <c r="I28" s="2">
+      <c r="G28" s="2">
+        <v>1</v>
+      </c>
+      <c r="H28" s="2">
+        <v>1</v>
+      </c>
+      <c r="I28" s="3">
         <f t="shared" si="0"/>
         <v>2500</v>
       </c>
-      <c r="J28" s="8">
-        <v>1</v>
-      </c>
-      <c r="K28" s="8">
+      <c r="J28" s="2">
+        <v>1</v>
+      </c>
+      <c r="K28" s="2">
         <v>12000001</v>
       </c>
-      <c r="L28" s="8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="29" spans="2:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="8">
+      <c r="L28" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B29" s="2">
         <v>10003002</v>
       </c>
-      <c r="C29" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="D29" s="8">
+      <c r="C29" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D29" s="2">
         <v>10003002</v>
       </c>
-      <c r="E29" s="8">
+      <c r="E29" s="2">
         <v>3</v>
       </c>
-      <c r="F29" s="8">
+      <c r="F29" s="2">
         <v>3</v>
       </c>
-      <c r="G29" s="8">
+      <c r="G29" s="2">
         <v>2</v>
       </c>
-      <c r="H29" s="8">
-        <v>1</v>
-      </c>
-      <c r="I29" s="2">
+      <c r="H29" s="2">
+        <v>1</v>
+      </c>
+      <c r="I29" s="3">
         <f t="shared" si="0"/>
         <v>2600</v>
       </c>
-      <c r="J29" s="8">
-        <v>1</v>
-      </c>
-      <c r="K29" s="8">
+      <c r="J29" s="2">
+        <v>1</v>
+      </c>
+      <c r="K29" s="2">
         <v>12000002</v>
       </c>
-      <c r="L29" s="8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="30" spans="2:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="8">
+      <c r="L29" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B30" s="2">
         <v>10003003</v>
       </c>
-      <c r="C30" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D30" s="8">
+      <c r="C30" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D30" s="2">
         <v>10003003</v>
       </c>
-      <c r="E30" s="8">
+      <c r="E30" s="2">
         <v>3</v>
       </c>
-      <c r="F30" s="8">
+      <c r="F30" s="2">
         <v>3</v>
       </c>
-      <c r="G30" s="8">
-        <v>4</v>
-      </c>
-      <c r="H30" s="8">
-        <v>1</v>
-      </c>
-      <c r="I30" s="2">
+      <c r="G30" s="2">
+        <v>3</v>
+      </c>
+      <c r="H30" s="2">
+        <v>1</v>
+      </c>
+      <c r="I30" s="3">
         <f t="shared" si="0"/>
         <v>2700</v>
       </c>
-      <c r="J30" s="8">
-        <v>1</v>
-      </c>
-      <c r="K30" s="8">
+      <c r="J30" s="2">
+        <v>1</v>
+      </c>
+      <c r="K30" s="2">
         <v>12000003</v>
       </c>
-      <c r="L30" s="8" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="31" spans="2:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="8">
+      <c r="L30" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B31" s="2">
         <v>10003004</v>
       </c>
-      <c r="C31" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D31" s="8">
+      <c r="C31" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D31" s="2">
         <v>10003004</v>
       </c>
-      <c r="E31" s="8">
+      <c r="E31" s="2">
         <v>3</v>
       </c>
-      <c r="F31" s="8">
+      <c r="F31" s="2">
         <v>3</v>
       </c>
-      <c r="G31" s="8">
-        <v>5</v>
-      </c>
-      <c r="H31" s="8">
-        <v>1</v>
-      </c>
-      <c r="I31" s="2">
+      <c r="G31" s="2">
+        <v>4</v>
+      </c>
+      <c r="H31" s="2">
+        <v>1</v>
+      </c>
+      <c r="I31" s="3">
         <f t="shared" si="0"/>
         <v>2800</v>
       </c>
-      <c r="J31" s="8">
-        <v>1</v>
-      </c>
-      <c r="K31" s="8">
+      <c r="J31" s="2">
+        <v>1</v>
+      </c>
+      <c r="K31" s="2">
         <v>12000004</v>
       </c>
-      <c r="L31" s="8" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="32" spans="2:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="8">
+      <c r="L31" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B32" s="2">
         <v>10003005</v>
       </c>
-      <c r="C32" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="D32" s="8">
+      <c r="C32" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D32" s="2">
         <v>10003005</v>
       </c>
-      <c r="E32" s="8">
+      <c r="E32" s="2">
         <v>3</v>
       </c>
-      <c r="F32" s="8">
+      <c r="F32" s="2">
         <v>3</v>
       </c>
-      <c r="G32" s="8">
-        <v>8</v>
-      </c>
-      <c r="H32" s="8">
-        <v>1</v>
-      </c>
-      <c r="I32" s="2">
+      <c r="G32" s="2">
+        <v>5</v>
+      </c>
+      <c r="H32" s="2">
+        <v>1</v>
+      </c>
+      <c r="I32" s="3">
         <f t="shared" si="0"/>
         <v>2900</v>
       </c>
-      <c r="J32" s="8">
-        <v>1</v>
-      </c>
-      <c r="K32" s="8">
+      <c r="J32" s="2">
+        <v>1</v>
+      </c>
+      <c r="K32" s="2">
         <v>12000005</v>
       </c>
-      <c r="L32" s="8" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="33" spans="2:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="8">
+      <c r="L32" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B33" s="2">
         <v>10003006</v>
       </c>
-      <c r="C33" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D33" s="8">
+      <c r="C33" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D33" s="2">
         <v>10003006</v>
       </c>
-      <c r="E33" s="8">
+      <c r="E33" s="2">
         <v>3</v>
       </c>
-      <c r="F33" s="8">
+      <c r="F33" s="2">
         <v>3</v>
       </c>
-      <c r="G33" s="8">
-        <v>10</v>
-      </c>
-      <c r="H33" s="8">
-        <v>1</v>
-      </c>
-      <c r="I33" s="2">
+      <c r="G33" s="2">
+        <v>6</v>
+      </c>
+      <c r="H33" s="2">
+        <v>1</v>
+      </c>
+      <c r="I33" s="3">
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
-      <c r="J33" s="8">
-        <v>1</v>
-      </c>
-      <c r="K33" s="8">
+      <c r="J33" s="2">
+        <v>1</v>
+      </c>
+      <c r="K33" s="2">
         <v>12000006</v>
       </c>
-      <c r="L33" s="8" t="s">
-        <v>73</v>
+      <c r="L33" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Unity/Assets/Config/Excel/ItemConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ItemConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12795"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -81,7 +81,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F3" authorId="0">
+    <comment ref="G3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -106,7 +106,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0">
+    <comment ref="H3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -159,7 +159,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="0">
+    <comment ref="I3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -181,7 +181,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K3" authorId="0">
+    <comment ref="L3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -208,7 +208,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="80">
   <si>
     <t>##var</t>
   </si>
@@ -225,6 +225,9 @@
     <t>ItemQuality</t>
   </si>
   <si>
+    <t>UseLv</t>
+  </si>
+  <si>
     <t>ItemType</t>
   </si>
   <si>
@@ -265,6 +268,9 @@
   </si>
   <si>
     <t>道具品质</t>
+  </si>
+  <si>
+    <t>使用等级</t>
   </si>
   <si>
     <t>道具类型</t>
@@ -454,7 +460,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -472,12 +478,6 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="0"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -632,11 +632,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
@@ -649,6 +644,11 @@
     </font>
     <font>
       <b/>
+      <sz val="9"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -1035,138 +1035,138 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1185,13 +1185,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1514,16 +1508,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.875" style="3" customWidth="1"/>
-    <col min="2" max="11" width="17.875" style="3"/>
-    <col min="12" max="12" width="70.625" style="3" customWidth="1"/>
-    <col min="13" max="16384" width="17.875" style="3"/>
+    <col min="2" max="12" width="17.875" style="3"/>
+    <col min="13" max="13" width="70.625" style="3" customWidth="1"/>
+    <col min="14" max="16384" width="17.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:12">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1545,10 +1539,10 @@
       <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="5" t="s">
@@ -1560,89 +1554,98 @@
       <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="M1" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>13</v>
-      </c>
       <c r="G2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L2" s="5" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="M2" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="G3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="H3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="I3" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="J3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="K3" s="6" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="4" customHeight="1" spans="2:12">
+      <c r="L3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="2:13">
       <c r="B4" s="3">
         <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>
@@ -1654,30 +1657,33 @@
         <v>1</v>
       </c>
       <c r="G4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" s="3">
+        <v>1</v>
+      </c>
+      <c r="J4" s="3">
         <v>100</v>
       </c>
-      <c r="J4" s="3">
+      <c r="K4" s="3">
         <v>99999999</v>
       </c>
-      <c r="K4" s="3">
-        <v>0</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" customHeight="1" spans="2:12">
+      <c r="L4" s="3">
+        <v>0</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="2:13">
       <c r="B5" s="3">
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D5" s="3">
         <v>2</v>
@@ -1686,34 +1692,37 @@
         <v>5</v>
       </c>
       <c r="F5" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" s="3">
-        <f>I4+100</f>
+        <v>1</v>
+      </c>
+      <c r="J5" s="3">
+        <f>J4+100</f>
         <v>200</v>
       </c>
-      <c r="J5" s="3">
+      <c r="K5" s="3">
         <v>99999999</v>
       </c>
-      <c r="K5" s="3">
-        <v>0</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="2:12">
+      <c r="L5" s="3">
+        <v>0</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="2:13">
       <c r="B6" s="3">
         <v>3</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D6" s="3">
         <v>3</v>
@@ -1722,34 +1731,37 @@
         <v>5</v>
       </c>
       <c r="F6" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" s="3">
-        <f t="shared" ref="I6:I33" si="0">I5+100</f>
+        <v>1</v>
+      </c>
+      <c r="J6" s="3">
+        <f t="shared" ref="J6:J33" si="0">J5+100</f>
         <v>300</v>
       </c>
-      <c r="J6" s="3">
+      <c r="K6" s="3">
         <v>99999999</v>
       </c>
-      <c r="K6" s="3">
-        <v>0</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="2:12">
+      <c r="L6" s="3">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="2:13">
       <c r="B7" s="3">
         <v>4</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D7" s="3">
         <v>4</v>
@@ -1758,34 +1770,37 @@
         <v>5</v>
       </c>
       <c r="F7" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" s="3">
+        <v>1</v>
+      </c>
+      <c r="J7" s="3">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="J7" s="3">
+      <c r="K7" s="3">
         <v>99999999</v>
       </c>
-      <c r="K7" s="3">
-        <v>0</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="2:12">
+      <c r="L7" s="3">
+        <v>0</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="2:13">
       <c r="B8" s="3">
         <v>5</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D8" s="3">
         <v>5</v>
@@ -1794,34 +1809,37 @@
         <v>4</v>
       </c>
       <c r="F8" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" s="3">
+        <v>1</v>
+      </c>
+      <c r="J8" s="3">
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>99999999</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="2:13">
       <c r="B9" s="2">
         <v>10001001</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D9" s="2">
         <v>10000001</v>
@@ -1829,35 +1847,38 @@
       <c r="E9" s="2">
         <v>6</v>
       </c>
-      <c r="F9" s="2">
-        <v>1</v>
+      <c r="F9" s="3">
+        <v>6</v>
       </c>
       <c r="G9" s="2">
+        <v>1</v>
+      </c>
+      <c r="H9" s="2">
         <v>3</v>
       </c>
-      <c r="H9" s="2">
-        <v>1</v>
-      </c>
-      <c r="I9" s="3">
+      <c r="I9" s="2">
+        <v>1</v>
+      </c>
+      <c r="J9" s="3">
         <f t="shared" si="0"/>
         <v>600</v>
       </c>
-      <c r="J9" s="2">
+      <c r="K9" s="2">
         <v>99</v>
       </c>
-      <c r="K9" s="2">
-        <v>0</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" s="2" customFormat="1" ht="19.5" customHeight="1" spans="2:12">
+      <c r="L9" s="2">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" ht="19.5" customHeight="1" spans="2:13">
       <c r="B10" s="2">
         <v>10001002</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D10" s="2">
         <v>10000002</v>
@@ -1865,35 +1886,38 @@
       <c r="E10" s="2">
         <v>6</v>
       </c>
-      <c r="F10" s="2">
-        <v>1</v>
+      <c r="F10" s="3">
+        <v>7</v>
       </c>
       <c r="G10" s="2">
+        <v>1</v>
+      </c>
+      <c r="H10" s="2">
         <v>4</v>
       </c>
-      <c r="H10" s="2">
-        <v>1</v>
-      </c>
-      <c r="I10" s="3">
+      <c r="I10" s="2">
+        <v>1</v>
+      </c>
+      <c r="J10" s="3">
         <f t="shared" si="0"/>
         <v>700</v>
       </c>
-      <c r="J10" s="2">
+      <c r="K10" s="2">
         <v>99</v>
       </c>
-      <c r="K10" s="2">
-        <v>0</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="L10" s="2">
+        <v>0</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="2:13">
       <c r="B11" s="2">
         <v>10001003</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D11" s="2">
         <v>10000003</v>
@@ -1901,35 +1925,38 @@
       <c r="E11" s="2">
         <v>5</v>
       </c>
-      <c r="F11" s="2">
-        <v>1</v>
+      <c r="F11" s="3">
+        <v>8</v>
       </c>
       <c r="G11" s="2">
+        <v>1</v>
+      </c>
+      <c r="H11" s="2">
         <v>6</v>
       </c>
-      <c r="H11" s="2">
-        <v>1</v>
-      </c>
-      <c r="I11" s="3">
+      <c r="I11" s="2">
+        <v>1</v>
+      </c>
+      <c r="J11" s="3">
         <f t="shared" si="0"/>
         <v>800</v>
       </c>
-      <c r="J11" s="2">
+      <c r="K11" s="2">
         <v>99</v>
       </c>
-      <c r="K11" s="2">
-        <v>0</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="L11" s="2">
+        <v>0</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="2:13">
       <c r="B12" s="2">
         <v>10001004</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D12" s="2">
         <v>10000004</v>
@@ -1937,35 +1964,38 @@
       <c r="E12" s="2">
         <v>5</v>
       </c>
-      <c r="F12" s="2">
-        <v>1</v>
+      <c r="F12" s="3">
+        <v>9</v>
       </c>
       <c r="G12" s="2">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2">
         <v>5</v>
       </c>
-      <c r="H12" s="2">
-        <v>1</v>
-      </c>
-      <c r="I12" s="3">
+      <c r="I12" s="2">
+        <v>1</v>
+      </c>
+      <c r="J12" s="3">
         <f t="shared" si="0"/>
         <v>900</v>
       </c>
-      <c r="J12" s="2">
+      <c r="K12" s="2">
         <v>99</v>
       </c>
-      <c r="K12" s="2">
-        <v>0</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="L12" s="2">
+        <v>0</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="2:13">
       <c r="B13" s="2">
         <v>10001005</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D13" s="2">
         <v>10000005</v>
@@ -1973,35 +2003,38 @@
       <c r="E13" s="2">
         <v>5</v>
       </c>
-      <c r="F13" s="2">
-        <v>1</v>
+      <c r="F13" s="3">
+        <v>10</v>
       </c>
       <c r="G13" s="2">
+        <v>1</v>
+      </c>
+      <c r="H13" s="2">
         <v>5</v>
       </c>
-      <c r="H13" s="2">
-        <v>1</v>
-      </c>
-      <c r="I13" s="3">
+      <c r="I13" s="2">
+        <v>1</v>
+      </c>
+      <c r="J13" s="3">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
-      <c r="J13" s="2">
+      <c r="K13" s="2">
         <v>99</v>
       </c>
-      <c r="K13" s="2">
-        <v>0</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="L13" s="2">
+        <v>0</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="2:13">
       <c r="B14" s="2">
         <v>10001006</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D14" s="2">
         <v>10000006</v>
@@ -2009,35 +2042,38 @@
       <c r="E14" s="2">
         <v>5</v>
       </c>
-      <c r="F14" s="2">
-        <v>1</v>
+      <c r="F14" s="3">
+        <v>11</v>
       </c>
       <c r="G14" s="2">
+        <v>1</v>
+      </c>
+      <c r="H14" s="2">
         <v>5</v>
       </c>
-      <c r="H14" s="2">
-        <v>1</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="I14" s="2">
+        <v>1</v>
+      </c>
+      <c r="J14" s="3">
         <f t="shared" si="0"/>
         <v>1100</v>
       </c>
-      <c r="J14" s="2">
+      <c r="K14" s="2">
         <v>99</v>
       </c>
-      <c r="K14" s="2">
-        <v>0</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="15" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="L14" s="2">
+        <v>0</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="2:13">
       <c r="B15" s="2">
         <v>10001007</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D15" s="2">
         <v>10000007</v>
@@ -2045,35 +2081,38 @@
       <c r="E15" s="2">
         <v>5</v>
       </c>
-      <c r="F15" s="2">
-        <v>1</v>
+      <c r="F15" s="3">
+        <v>12</v>
       </c>
       <c r="G15" s="2">
+        <v>1</v>
+      </c>
+      <c r="H15" s="2">
         <v>5</v>
       </c>
-      <c r="H15" s="2">
-        <v>1</v>
-      </c>
-      <c r="I15" s="3">
+      <c r="I15" s="2">
+        <v>1</v>
+      </c>
+      <c r="J15" s="3">
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
-      <c r="J15" s="2">
+      <c r="K15" s="2">
         <v>99</v>
       </c>
-      <c r="K15" s="2">
-        <v>0</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="16" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="L15" s="2">
+        <v>0</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="2:13">
       <c r="B16" s="2">
         <v>10001008</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D16" s="2">
         <v>10000008</v>
@@ -2081,35 +2120,38 @@
       <c r="E16" s="2">
         <v>3</v>
       </c>
-      <c r="F16" s="2">
-        <v>1</v>
+      <c r="F16" s="3">
+        <v>13</v>
       </c>
       <c r="G16" s="2">
+        <v>1</v>
+      </c>
+      <c r="H16" s="2">
         <v>7</v>
       </c>
-      <c r="H16" s="2">
-        <v>1</v>
-      </c>
-      <c r="I16" s="3">
+      <c r="I16" s="2">
+        <v>1</v>
+      </c>
+      <c r="J16" s="3">
         <f t="shared" si="0"/>
         <v>1300</v>
       </c>
-      <c r="J16" s="2">
+      <c r="K16" s="2">
         <v>99</v>
       </c>
-      <c r="K16" s="2">
-        <v>0</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="17" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="L16" s="2">
+        <v>0</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="2:13">
       <c r="B17" s="2">
         <v>10002001</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D17" s="2">
         <v>10000009</v>
@@ -2117,35 +2159,38 @@
       <c r="E17" s="2">
         <v>2</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="3">
+        <v>14</v>
+      </c>
+      <c r="G17" s="2">
         <v>2</v>
       </c>
-      <c r="G17" s="2">
-        <v>0</v>
-      </c>
       <c r="H17" s="2">
-        <v>1</v>
-      </c>
-      <c r="I17" s="3">
+        <v>0</v>
+      </c>
+      <c r="I17" s="2">
+        <v>1</v>
+      </c>
+      <c r="J17" s="3">
         <f t="shared" si="0"/>
         <v>1400</v>
       </c>
-      <c r="J17" s="2">
+      <c r="K17" s="2">
         <v>999</v>
       </c>
-      <c r="K17" s="2">
-        <v>0</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="18" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="L17" s="2">
+        <v>0</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="2:13">
       <c r="B18" s="2">
         <v>10002002</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D18" s="2">
         <v>10000010</v>
@@ -2153,35 +2198,38 @@
       <c r="E18" s="2">
         <v>3</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="3">
+        <v>15</v>
+      </c>
+      <c r="G18" s="2">
         <v>2</v>
       </c>
-      <c r="G18" s="2">
-        <v>0</v>
-      </c>
       <c r="H18" s="2">
-        <v>1</v>
-      </c>
-      <c r="I18" s="3">
+        <v>0</v>
+      </c>
+      <c r="I18" s="2">
+        <v>1</v>
+      </c>
+      <c r="J18" s="3">
         <f t="shared" si="0"/>
         <v>1500</v>
       </c>
-      <c r="J18" s="2">
+      <c r="K18" s="2">
         <v>999</v>
       </c>
-      <c r="K18" s="2">
-        <v>0</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="L18" s="2">
+        <v>0</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="2:13">
       <c r="B19" s="2">
         <v>10002003</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D19" s="2">
         <v>10000011</v>
@@ -2189,35 +2237,38 @@
       <c r="E19" s="2">
         <v>4</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="3">
+        <v>16</v>
+      </c>
+      <c r="G19" s="2">
         <v>2</v>
       </c>
-      <c r="G19" s="2">
-        <v>0</v>
-      </c>
       <c r="H19" s="2">
-        <v>1</v>
-      </c>
-      <c r="I19" s="3">
+        <v>0</v>
+      </c>
+      <c r="I19" s="2">
+        <v>1</v>
+      </c>
+      <c r="J19" s="3">
         <f t="shared" si="0"/>
         <v>1600</v>
       </c>
-      <c r="J19" s="2">
+      <c r="K19" s="2">
         <v>999</v>
       </c>
-      <c r="K19" s="2">
-        <v>0</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="20" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="L19" s="2">
+        <v>0</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="2:13">
       <c r="B20" s="2">
         <v>10002004</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D20" s="2">
         <v>10000012</v>
@@ -2225,35 +2276,38 @@
       <c r="E20" s="2">
         <v>5</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" s="3">
+        <v>17</v>
+      </c>
+      <c r="G20" s="2">
         <v>2</v>
       </c>
-      <c r="G20" s="2">
-        <v>0</v>
-      </c>
       <c r="H20" s="2">
-        <v>1</v>
-      </c>
-      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="2">
+        <v>1</v>
+      </c>
+      <c r="J20" s="3">
         <f t="shared" si="0"/>
         <v>1700</v>
       </c>
-      <c r="J20" s="2">
+      <c r="K20" s="2">
         <v>999</v>
       </c>
-      <c r="K20" s="2">
-        <v>0</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="21" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="L20" s="2">
+        <v>0</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="2:13">
       <c r="B21" s="2">
         <v>10002005</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D21" s="2">
         <v>10000013</v>
@@ -2261,35 +2315,38 @@
       <c r="E21" s="2">
         <v>6</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="3">
+        <v>18</v>
+      </c>
+      <c r="G21" s="2">
         <v>2</v>
       </c>
-      <c r="G21" s="2">
-        <v>0</v>
-      </c>
       <c r="H21" s="2">
-        <v>1</v>
-      </c>
-      <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="2">
+        <v>1</v>
+      </c>
+      <c r="J21" s="3">
         <f t="shared" si="0"/>
         <v>1800</v>
       </c>
-      <c r="J21" s="2">
+      <c r="K21" s="2">
         <v>999</v>
       </c>
-      <c r="K21" s="2">
-        <v>0</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="22" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="L21" s="2">
+        <v>0</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="2:13">
       <c r="B22" s="2">
         <v>10002006</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D22" s="2">
         <v>10000001</v>
@@ -2297,35 +2354,38 @@
       <c r="E22" s="2">
         <v>1</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="3">
+        <v>19</v>
+      </c>
+      <c r="G22" s="2">
         <v>2</v>
       </c>
-      <c r="G22" s="2">
-        <v>0</v>
-      </c>
       <c r="H22" s="2">
-        <v>1</v>
-      </c>
-      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="2">
+        <v>1</v>
+      </c>
+      <c r="J22" s="3">
         <f t="shared" si="0"/>
         <v>1900</v>
       </c>
-      <c r="J22" s="2">
+      <c r="K22" s="2">
         <v>999</v>
       </c>
-      <c r="K22" s="2">
-        <v>0</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="23" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="L22" s="2">
+        <v>0</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="2:13">
       <c r="B23" s="2">
         <v>10002007</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D23" s="2">
         <v>10000002</v>
@@ -2333,35 +2393,38 @@
       <c r="E23" s="2">
         <v>2</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F23" s="3">
+        <v>20</v>
+      </c>
+      <c r="G23" s="2">
         <v>2</v>
       </c>
-      <c r="G23" s="2">
-        <v>0</v>
-      </c>
       <c r="H23" s="2">
-        <v>1</v>
-      </c>
-      <c r="I23" s="3">
+        <v>0</v>
+      </c>
+      <c r="I23" s="2">
+        <v>1</v>
+      </c>
+      <c r="J23" s="3">
         <f t="shared" si="0"/>
         <v>2000</v>
       </c>
-      <c r="J23" s="2">
+      <c r="K23" s="2">
         <v>999</v>
       </c>
-      <c r="K23" s="2">
-        <v>0</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="24" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="L23" s="2">
+        <v>0</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="2:13">
       <c r="B24" s="2">
         <v>10002008</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D24" s="2">
         <v>10000003</v>
@@ -2369,35 +2432,38 @@
       <c r="E24" s="2">
         <v>3</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24" s="3">
+        <v>21</v>
+      </c>
+      <c r="G24" s="2">
         <v>2</v>
       </c>
-      <c r="G24" s="2">
-        <v>0</v>
-      </c>
       <c r="H24" s="2">
-        <v>1</v>
-      </c>
-      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="2">
+        <v>1</v>
+      </c>
+      <c r="J24" s="3">
         <f t="shared" si="0"/>
         <v>2100</v>
       </c>
-      <c r="J24" s="2">
+      <c r="K24" s="2">
         <v>999</v>
       </c>
-      <c r="K24" s="2">
-        <v>0</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="25" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="L24" s="2">
+        <v>0</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="2:13">
       <c r="B25" s="2">
         <v>10002009</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D25" s="2">
         <v>10000004</v>
@@ -2405,35 +2471,38 @@
       <c r="E25" s="2">
         <v>4</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25" s="3">
+        <v>22</v>
+      </c>
+      <c r="G25" s="2">
         <v>2</v>
       </c>
-      <c r="G25" s="2">
-        <v>0</v>
-      </c>
       <c r="H25" s="2">
-        <v>1</v>
-      </c>
-      <c r="I25" s="3">
+        <v>0</v>
+      </c>
+      <c r="I25" s="2">
+        <v>1</v>
+      </c>
+      <c r="J25" s="3">
         <f t="shared" si="0"/>
         <v>2200</v>
       </c>
-      <c r="J25" s="2">
+      <c r="K25" s="2">
         <v>999</v>
       </c>
-      <c r="K25" s="2">
-        <v>0</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="26" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="L25" s="2">
+        <v>0</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="2:13">
       <c r="B26" s="2">
         <v>10002010</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D26" s="2">
         <v>10000005</v>
@@ -2441,35 +2510,38 @@
       <c r="E26" s="2">
         <v>5</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F26" s="3">
+        <v>23</v>
+      </c>
+      <c r="G26" s="2">
         <v>2</v>
       </c>
-      <c r="G26" s="2">
-        <v>0</v>
-      </c>
       <c r="H26" s="2">
-        <v>1</v>
-      </c>
-      <c r="I26" s="3">
+        <v>0</v>
+      </c>
+      <c r="I26" s="2">
+        <v>1</v>
+      </c>
+      <c r="J26" s="3">
         <f t="shared" si="0"/>
         <v>2300</v>
       </c>
-      <c r="J26" s="2">
+      <c r="K26" s="2">
         <v>999</v>
       </c>
-      <c r="K26" s="2">
-        <v>0</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="27" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="L26" s="2">
+        <v>0</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="2:13">
       <c r="B27" s="2">
         <v>10002011</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D27" s="2">
         <v>10000006</v>
@@ -2477,35 +2549,38 @@
       <c r="E27" s="2">
         <v>6</v>
       </c>
-      <c r="F27" s="2">
+      <c r="F27" s="3">
+        <v>24</v>
+      </c>
+      <c r="G27" s="2">
         <v>2</v>
       </c>
-      <c r="G27" s="2">
-        <v>0</v>
-      </c>
       <c r="H27" s="2">
-        <v>1</v>
-      </c>
-      <c r="I27" s="3">
+        <v>0</v>
+      </c>
+      <c r="I27" s="2">
+        <v>1</v>
+      </c>
+      <c r="J27" s="3">
         <f t="shared" si="0"/>
         <v>2400</v>
       </c>
-      <c r="J27" s="2">
+      <c r="K27" s="2">
         <v>999</v>
       </c>
-      <c r="K27" s="2">
-        <v>0</v>
-      </c>
-      <c r="L27" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="28" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="L27" s="2">
+        <v>0</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="2:13">
       <c r="B28" s="2">
         <v>10003001</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D28" s="2">
         <v>10003001</v>
@@ -2513,35 +2588,38 @@
       <c r="E28" s="2">
         <v>3</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F28" s="3">
+        <v>25</v>
+      </c>
+      <c r="G28" s="2">
         <v>3</v>
       </c>
-      <c r="G28" s="2">
-        <v>1</v>
-      </c>
       <c r="H28" s="2">
         <v>1</v>
       </c>
-      <c r="I28" s="3">
+      <c r="I28" s="2">
+        <v>1</v>
+      </c>
+      <c r="J28" s="3">
         <f t="shared" si="0"/>
         <v>2500</v>
       </c>
-      <c r="J28" s="2">
-        <v>1</v>
-      </c>
       <c r="K28" s="2">
+        <v>1</v>
+      </c>
+      <c r="L28" s="2">
         <v>12000001</v>
       </c>
-      <c r="L28" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="29" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="M28" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="2:13">
       <c r="B29" s="2">
         <v>10003002</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D29" s="2">
         <v>10003002</v>
@@ -2549,35 +2627,38 @@
       <c r="E29" s="2">
         <v>3</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F29" s="3">
+        <v>26</v>
+      </c>
+      <c r="G29" s="2">
         <v>3</v>
       </c>
-      <c r="G29" s="2">
+      <c r="H29" s="2">
         <v>2</v>
       </c>
-      <c r="H29" s="2">
-        <v>1</v>
-      </c>
-      <c r="I29" s="3">
+      <c r="I29" s="2">
+        <v>1</v>
+      </c>
+      <c r="J29" s="3">
         <f t="shared" si="0"/>
         <v>2600</v>
       </c>
-      <c r="J29" s="2">
-        <v>1</v>
-      </c>
       <c r="K29" s="2">
+        <v>1</v>
+      </c>
+      <c r="L29" s="2">
         <v>12000002</v>
       </c>
-      <c r="L29" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="30" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="M29" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="2:13">
       <c r="B30" s="2">
         <v>10003003</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D30" s="2">
         <v>10003003</v>
@@ -2585,35 +2666,38 @@
       <c r="E30" s="2">
         <v>3</v>
       </c>
-      <c r="F30" s="2">
-        <v>3</v>
+      <c r="F30" s="3">
+        <v>27</v>
       </c>
       <c r="G30" s="2">
         <v>3</v>
       </c>
       <c r="H30" s="2">
-        <v>1</v>
-      </c>
-      <c r="I30" s="3">
+        <v>3</v>
+      </c>
+      <c r="I30" s="2">
+        <v>1</v>
+      </c>
+      <c r="J30" s="3">
         <f t="shared" si="0"/>
         <v>2700</v>
       </c>
-      <c r="J30" s="2">
-        <v>1</v>
-      </c>
       <c r="K30" s="2">
+        <v>1</v>
+      </c>
+      <c r="L30" s="2">
         <v>12000003</v>
       </c>
-      <c r="L30" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="31" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="M30" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" customHeight="1" spans="2:13">
       <c r="B31" s="2">
         <v>10003004</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D31" s="2">
         <v>10003004</v>
@@ -2621,35 +2705,38 @@
       <c r="E31" s="2">
         <v>3</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F31" s="3">
+        <v>28</v>
+      </c>
+      <c r="G31" s="2">
         <v>3</v>
       </c>
-      <c r="G31" s="2">
+      <c r="H31" s="2">
         <v>4</v>
       </c>
-      <c r="H31" s="2">
-        <v>1</v>
-      </c>
-      <c r="I31" s="3">
+      <c r="I31" s="2">
+        <v>1</v>
+      </c>
+      <c r="J31" s="3">
         <f t="shared" si="0"/>
         <v>2800</v>
       </c>
-      <c r="J31" s="2">
-        <v>1</v>
-      </c>
       <c r="K31" s="2">
+        <v>1</v>
+      </c>
+      <c r="L31" s="2">
         <v>12000004</v>
       </c>
-      <c r="L31" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="32" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="M31" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="2:13">
       <c r="B32" s="2">
         <v>10003005</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D32" s="2">
         <v>10003005</v>
@@ -2657,35 +2744,38 @@
       <c r="E32" s="2">
         <v>3</v>
       </c>
-      <c r="F32" s="2">
+      <c r="F32" s="3">
+        <v>29</v>
+      </c>
+      <c r="G32" s="2">
         <v>3</v>
       </c>
-      <c r="G32" s="2">
+      <c r="H32" s="2">
         <v>5</v>
       </c>
-      <c r="H32" s="2">
-        <v>1</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="I32" s="2">
+        <v>1</v>
+      </c>
+      <c r="J32" s="3">
         <f t="shared" si="0"/>
         <v>2900</v>
       </c>
-      <c r="J32" s="2">
-        <v>1</v>
-      </c>
       <c r="K32" s="2">
+        <v>1</v>
+      </c>
+      <c r="L32" s="2">
         <v>12000005</v>
       </c>
-      <c r="L32" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="33" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="M32" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="2:13">
       <c r="B33" s="2">
         <v>10003006</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D33" s="2">
         <v>10003006</v>
@@ -2693,27 +2783,30 @@
       <c r="E33" s="2">
         <v>3</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F33" s="3">
+        <v>30</v>
+      </c>
+      <c r="G33" s="2">
         <v>3</v>
       </c>
-      <c r="G33" s="2">
+      <c r="H33" s="2">
         <v>6</v>
       </c>
-      <c r="H33" s="2">
-        <v>1</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="I33" s="2">
+        <v>1</v>
+      </c>
+      <c r="J33" s="3">
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
-      <c r="J33" s="2">
-        <v>1</v>
-      </c>
       <c r="K33" s="2">
+        <v>1</v>
+      </c>
+      <c r="L33" s="2">
         <v>12000006</v>
       </c>
-      <c r="L33" s="2" t="s">
-        <v>77</v>
+      <c r="M33" s="2" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/ItemConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ItemConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -208,7 +208,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="81">
   <si>
     <t>##var</t>
   </si>
@@ -448,6 +448,9 @@
   </si>
   <si>
     <t>这是一个装备6</t>
+  </si>
+  <si>
+    <t>一个更吊的头盔</t>
   </si>
 </sst>
 </file>
@@ -643,12 +646,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -1508,7 +1511,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.875" style="3" customWidth="1"/>
@@ -1743,7 +1746,7 @@
         <v>1</v>
       </c>
       <c r="J6" s="3">
-        <f t="shared" ref="J6:J33" si="0">J5+100</f>
+        <f t="shared" ref="J6:J34" si="0">J5+100</f>
         <v>300</v>
       </c>
       <c r="K6" s="3">
@@ -2807,6 +2810,45 @@
       </c>
       <c r="M33" s="2" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="2:13">
+      <c r="B34" s="2">
+        <v>10003011</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D34" s="2">
+        <v>10003001</v>
+      </c>
+      <c r="E34" s="2">
+        <v>3</v>
+      </c>
+      <c r="F34" s="3">
+        <v>25</v>
+      </c>
+      <c r="G34" s="2">
+        <v>3</v>
+      </c>
+      <c r="H34" s="2">
+        <v>1</v>
+      </c>
+      <c r="I34" s="2">
+        <v>1</v>
+      </c>
+      <c r="J34" s="3">
+        <f t="shared" si="0"/>
+        <v>3100</v>
+      </c>
+      <c r="K34" s="2">
+        <v>1</v>
+      </c>
+      <c r="L34" s="2">
+        <v>12000011</v>
+      </c>
+      <c r="M34" s="2" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/ItemConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ItemConfig.xlsx
@@ -208,7 +208,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="85">
   <si>
     <t>##var</t>
   </si>
@@ -246,6 +246,9 @@
     <t>ItemEquipID</t>
   </si>
   <si>
+    <t>ItemUsePar</t>
+  </si>
+  <si>
     <t>ItemDescription</t>
   </si>
   <si>
@@ -291,6 +294,9 @@
     <t>装备ID</t>
   </si>
   <si>
+    <t>道具使用参数</t>
+  </si>
+  <si>
     <t>道具描述</t>
   </si>
   <si>
@@ -370,6 +376,12 @@
   </si>
   <si>
     <t>消耗入场券进入副本</t>
+  </si>
+  <si>
+    <t>英雄经验道具</t>
+  </si>
+  <si>
+    <t>英雄增加100经验</t>
   </si>
   <si>
     <t>大熊猫碎片</t>
@@ -637,6 +649,12 @@
     <font>
       <b/>
       <sz val="9"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -646,12 +664,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -1511,16 +1523,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.875" style="3" customWidth="1"/>
     <col min="2" max="12" width="17.875" style="3"/>
-    <col min="13" max="13" width="70.625" style="3" customWidth="1"/>
-    <col min="14" max="16384" width="17.875" style="3"/>
+    <col min="13" max="13" width="20.5" style="3" customWidth="1"/>
+    <col min="14" max="14" width="70.625" style="3" customWidth="1"/>
+    <col min="15" max="16384" width="17.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:13">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1560,95 +1573,104 @@
       <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="N1" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="G2" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:13">
+        <v>16</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" customHeight="1" spans="2:13">
+        <v>28</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="2:14">
       <c r="B4" s="3">
         <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>
@@ -1677,16 +1699,16 @@
       <c r="L4" s="3">
         <v>0</v>
       </c>
-      <c r="M4" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" customHeight="1" spans="2:13">
+      <c r="N4" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="2:14">
       <c r="B5" s="3">
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D5" s="3">
         <v>2</v>
@@ -1716,16 +1738,16 @@
       <c r="L5" s="3">
         <v>0</v>
       </c>
-      <c r="M5" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="2:13">
+      <c r="N5" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="2:14">
       <c r="B6" s="3">
         <v>3</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D6" s="3">
         <v>3</v>
@@ -1746,7 +1768,7 @@
         <v>1</v>
       </c>
       <c r="J6" s="3">
-        <f t="shared" ref="J6:J34" si="0">J5+100</f>
+        <f>J5+100</f>
         <v>300</v>
       </c>
       <c r="K6" s="3">
@@ -1755,16 +1777,16 @@
       <c r="L6" s="3">
         <v>0</v>
       </c>
-      <c r="M6" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="2:13">
+      <c r="N6" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="2:14">
       <c r="B7" s="3">
         <v>4</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D7" s="3">
         <v>4</v>
@@ -1785,7 +1807,7 @@
         <v>1</v>
       </c>
       <c r="J7" s="3">
-        <f t="shared" si="0"/>
+        <f>J6+100</f>
         <v>400</v>
       </c>
       <c r="K7" s="3">
@@ -1794,16 +1816,16 @@
       <c r="L7" s="3">
         <v>0</v>
       </c>
-      <c r="M7" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="2:13">
+      <c r="N7" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="2:14">
       <c r="B8" s="3">
         <v>5</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D8" s="3">
         <v>5</v>
@@ -1824,7 +1846,7 @@
         <v>1</v>
       </c>
       <c r="J8" s="3">
-        <f t="shared" si="0"/>
+        <f>J7+100</f>
         <v>500</v>
       </c>
       <c r="K8" s="3">
@@ -1833,16 +1855,16 @@
       <c r="L8" s="3">
         <v>0</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="2:13">
+      <c r="N8" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B9" s="2">
         <v>10001001</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D9" s="2">
         <v>10000001</v>
@@ -1863,7 +1885,7 @@
         <v>1</v>
       </c>
       <c r="J9" s="3">
-        <f t="shared" si="0"/>
+        <f>J8+100</f>
         <v>600</v>
       </c>
       <c r="K9" s="2">
@@ -1872,16 +1894,16 @@
       <c r="L9" s="2">
         <v>0</v>
       </c>
-      <c r="M9" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" s="2" customFormat="1" ht="19.5" customHeight="1" spans="2:13">
+      <c r="N9" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" ht="19.5" customHeight="1" spans="2:14">
       <c r="B10" s="2">
         <v>10001002</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D10" s="2">
         <v>10000002</v>
@@ -1902,7 +1924,7 @@
         <v>1</v>
       </c>
       <c r="J10" s="3">
-        <f t="shared" si="0"/>
+        <f>J9+100</f>
         <v>700</v>
       </c>
       <c r="K10" s="2">
@@ -1911,16 +1933,16 @@
       <c r="L10" s="2">
         <v>0</v>
       </c>
-      <c r="M10" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="2:13">
+      <c r="N10" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B11" s="2">
         <v>10001003</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D11" s="2">
         <v>10000003</v>
@@ -1941,7 +1963,7 @@
         <v>1</v>
       </c>
       <c r="J11" s="3">
-        <f t="shared" si="0"/>
+        <f>J10+100</f>
         <v>800</v>
       </c>
       <c r="K11" s="2">
@@ -1950,16 +1972,16 @@
       <c r="L11" s="2">
         <v>0</v>
       </c>
-      <c r="M11" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="2:13">
+      <c r="N11" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B12" s="2">
         <v>10001004</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D12" s="2">
         <v>10000004</v>
@@ -1980,7 +2002,7 @@
         <v>1</v>
       </c>
       <c r="J12" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="J12:J17" si="0">J11+100</f>
         <v>900</v>
       </c>
       <c r="K12" s="2">
@@ -1989,16 +2011,16 @@
       <c r="L12" s="2">
         <v>0</v>
       </c>
-      <c r="M12" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="2:13">
+      <c r="N12" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B13" s="2">
         <v>10001005</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D13" s="2">
         <v>10000005</v>
@@ -2028,16 +2050,16 @@
       <c r="L13" s="2">
         <v>0</v>
       </c>
-      <c r="M13" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="2:13">
+      <c r="N13" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B14" s="2">
         <v>10001006</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D14" s="2">
         <v>10000006</v>
@@ -2067,16 +2089,16 @@
       <c r="L14" s="2">
         <v>0</v>
       </c>
-      <c r="M14" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="15" s="2" customFormat="1" customHeight="1" spans="2:13">
+      <c r="N14" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B15" s="2">
         <v>10001007</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D15" s="2">
         <v>10000007</v>
@@ -2106,16 +2128,16 @@
       <c r="L15" s="2">
         <v>0</v>
       </c>
-      <c r="M15" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="16" s="2" customFormat="1" customHeight="1" spans="2:13">
+      <c r="N15" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B16" s="2">
         <v>10001008</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D16" s="2">
         <v>10000008</v>
@@ -2145,31 +2167,31 @@
       <c r="L16" s="2">
         <v>0</v>
       </c>
-      <c r="M16" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17" s="2" customFormat="1" customHeight="1" spans="2:13">
+      <c r="N16" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B17" s="2">
-        <v>10002001</v>
+        <v>10001009</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D17" s="2">
         <v>10000009</v>
       </c>
       <c r="E17" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" s="3">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G17" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H17" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I17" s="2">
         <v>1</v>
@@ -2179,30 +2201,33 @@
         <v>1400</v>
       </c>
       <c r="K17" s="2">
-        <v>999</v>
+        <v>99</v>
       </c>
       <c r="L17" s="2">
         <v>0</v>
       </c>
-      <c r="M17" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18" s="2" customFormat="1" customHeight="1" spans="2:13">
+      <c r="M17" s="2">
+        <v>100</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B18" s="2">
-        <v>10002002</v>
+        <v>10002001</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D18" s="2">
-        <v>10000010</v>
+        <v>10000009</v>
       </c>
       <c r="E18" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G18" s="2">
         <v>2</v>
@@ -2214,8 +2239,8 @@
         <v>1</v>
       </c>
       <c r="J18" s="3">
-        <f t="shared" si="0"/>
-        <v>1500</v>
+        <f>J16+100</f>
+        <v>1400</v>
       </c>
       <c r="K18" s="2">
         <v>999</v>
@@ -2223,25 +2248,25 @@
       <c r="L18" s="2">
         <v>0</v>
       </c>
-      <c r="M18" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="2:13">
+      <c r="N18" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B19" s="2">
-        <v>10002003</v>
+        <v>10002002</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D19" s="2">
-        <v>10000011</v>
+        <v>10000010</v>
       </c>
       <c r="E19" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F19" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G19" s="2">
         <v>2</v>
@@ -2253,8 +2278,8 @@
         <v>1</v>
       </c>
       <c r="J19" s="3">
-        <f t="shared" si="0"/>
-        <v>1600</v>
+        <f t="shared" ref="J18:J35" si="1">J18+100</f>
+        <v>1500</v>
       </c>
       <c r="K19" s="2">
         <v>999</v>
@@ -2262,25 +2287,25 @@
       <c r="L19" s="2">
         <v>0</v>
       </c>
-      <c r="M19" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="20" s="2" customFormat="1" customHeight="1" spans="2:13">
+      <c r="N19" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B20" s="2">
-        <v>10002004</v>
+        <v>10002003</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D20" s="2">
-        <v>10000012</v>
+        <v>10000011</v>
       </c>
       <c r="E20" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F20" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G20" s="2">
         <v>2</v>
@@ -2292,8 +2317,8 @@
         <v>1</v>
       </c>
       <c r="J20" s="3">
-        <f t="shared" si="0"/>
-        <v>1700</v>
+        <f t="shared" si="1"/>
+        <v>1600</v>
       </c>
       <c r="K20" s="2">
         <v>999</v>
@@ -2301,25 +2326,25 @@
       <c r="L20" s="2">
         <v>0</v>
       </c>
-      <c r="M20" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="21" s="2" customFormat="1" customHeight="1" spans="2:13">
+      <c r="N20" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B21" s="2">
-        <v>10002005</v>
+        <v>10002004</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D21" s="2">
-        <v>10000013</v>
+        <v>10000012</v>
       </c>
       <c r="E21" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F21" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G21" s="2">
         <v>2</v>
@@ -2331,8 +2356,8 @@
         <v>1</v>
       </c>
       <c r="J21" s="3">
-        <f t="shared" si="0"/>
-        <v>1800</v>
+        <f t="shared" si="1"/>
+        <v>1700</v>
       </c>
       <c r="K21" s="2">
         <v>999</v>
@@ -2340,25 +2365,25 @@
       <c r="L21" s="2">
         <v>0</v>
       </c>
-      <c r="M21" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="22" s="2" customFormat="1" customHeight="1" spans="2:13">
+      <c r="N21" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B22" s="2">
-        <v>10002006</v>
+        <v>10002005</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D22" s="2">
-        <v>10000001</v>
+        <v>10000013</v>
       </c>
       <c r="E22" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F22" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G22" s="2">
         <v>2</v>
@@ -2370,8 +2395,8 @@
         <v>1</v>
       </c>
       <c r="J22" s="3">
-        <f t="shared" si="0"/>
-        <v>1900</v>
+        <f t="shared" si="1"/>
+        <v>1800</v>
       </c>
       <c r="K22" s="2">
         <v>999</v>
@@ -2379,25 +2404,25 @@
       <c r="L22" s="2">
         <v>0</v>
       </c>
-      <c r="M22" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="23" s="2" customFormat="1" customHeight="1" spans="2:13">
+      <c r="N22" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B23" s="2">
-        <v>10002007</v>
+        <v>10002006</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D23" s="2">
-        <v>10000002</v>
+        <v>10000001</v>
       </c>
       <c r="E23" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G23" s="2">
         <v>2</v>
@@ -2409,8 +2434,8 @@
         <v>1</v>
       </c>
       <c r="J23" s="3">
-        <f t="shared" si="0"/>
-        <v>2000</v>
+        <f t="shared" si="1"/>
+        <v>1900</v>
       </c>
       <c r="K23" s="2">
         <v>999</v>
@@ -2418,25 +2443,25 @@
       <c r="L23" s="2">
         <v>0</v>
       </c>
-      <c r="M23" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="24" s="2" customFormat="1" customHeight="1" spans="2:13">
+      <c r="N23" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B24" s="2">
-        <v>10002008</v>
+        <v>10002007</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D24" s="2">
-        <v>10000003</v>
+        <v>10000002</v>
       </c>
       <c r="E24" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F24" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G24" s="2">
         <v>2</v>
@@ -2448,8 +2473,8 @@
         <v>1</v>
       </c>
       <c r="J24" s="3">
-        <f t="shared" si="0"/>
-        <v>2100</v>
+        <f t="shared" si="1"/>
+        <v>2000</v>
       </c>
       <c r="K24" s="2">
         <v>999</v>
@@ -2457,25 +2482,25 @@
       <c r="L24" s="2">
         <v>0</v>
       </c>
-      <c r="M24" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="25" s="2" customFormat="1" customHeight="1" spans="2:13">
+      <c r="N24" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B25" s="2">
-        <v>10002009</v>
+        <v>10002008</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D25" s="2">
-        <v>10000004</v>
+        <v>10000003</v>
       </c>
       <c r="E25" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F25" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G25" s="2">
         <v>2</v>
@@ -2487,8 +2512,8 @@
         <v>1</v>
       </c>
       <c r="J25" s="3">
-        <f t="shared" si="0"/>
-        <v>2200</v>
+        <f t="shared" si="1"/>
+        <v>2100</v>
       </c>
       <c r="K25" s="2">
         <v>999</v>
@@ -2496,25 +2521,25 @@
       <c r="L25" s="2">
         <v>0</v>
       </c>
-      <c r="M25" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="26" s="2" customFormat="1" customHeight="1" spans="2:13">
+      <c r="N25" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B26" s="2">
-        <v>10002010</v>
+        <v>10002009</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D26" s="2">
-        <v>10000005</v>
+        <v>10000004</v>
       </c>
       <c r="E26" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F26" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G26" s="2">
         <v>2</v>
@@ -2526,8 +2551,8 @@
         <v>1</v>
       </c>
       <c r="J26" s="3">
-        <f t="shared" si="0"/>
-        <v>2300</v>
+        <f t="shared" si="1"/>
+        <v>2200</v>
       </c>
       <c r="K26" s="2">
         <v>999</v>
@@ -2535,25 +2560,25 @@
       <c r="L26" s="2">
         <v>0</v>
       </c>
-      <c r="M26" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="27" s="2" customFormat="1" customHeight="1" spans="2:13">
+      <c r="N26" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B27" s="2">
-        <v>10002011</v>
+        <v>10002010</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D27" s="2">
-        <v>10000006</v>
+        <v>10000005</v>
       </c>
       <c r="E27" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F27" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G27" s="2">
         <v>2</v>
@@ -2565,8 +2590,8 @@
         <v>1</v>
       </c>
       <c r="J27" s="3">
-        <f t="shared" si="0"/>
-        <v>2400</v>
+        <f t="shared" si="1"/>
+        <v>2300</v>
       </c>
       <c r="K27" s="2">
         <v>999</v>
@@ -2574,281 +2599,320 @@
       <c r="L27" s="2">
         <v>0</v>
       </c>
-      <c r="M27" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="28" s="2" customFormat="1" customHeight="1" spans="2:13">
+      <c r="N27" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B28" s="2">
+        <v>10002011</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D28" s="2">
+        <v>10000006</v>
+      </c>
+      <c r="E28" s="2">
+        <v>6</v>
+      </c>
+      <c r="F28" s="3">
+        <v>24</v>
+      </c>
+      <c r="G28" s="2">
+        <v>2</v>
+      </c>
+      <c r="H28" s="2">
+        <v>0</v>
+      </c>
+      <c r="I28" s="2">
+        <v>1</v>
+      </c>
+      <c r="J28" s="3">
+        <f t="shared" si="1"/>
+        <v>2400</v>
+      </c>
+      <c r="K28" s="2">
+        <v>999</v>
+      </c>
+      <c r="L28" s="2">
+        <v>0</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="2:14">
+      <c r="B29" s="2">
         <v>10003001</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D28" s="2">
+      <c r="C29" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D29" s="2">
         <v>10003001</v>
-      </c>
-      <c r="E28" s="2">
-        <v>3</v>
-      </c>
-      <c r="F28" s="3">
-        <v>25</v>
-      </c>
-      <c r="G28" s="2">
-        <v>3</v>
-      </c>
-      <c r="H28" s="2">
-        <v>1</v>
-      </c>
-      <c r="I28" s="2">
-        <v>1</v>
-      </c>
-      <c r="J28" s="3">
-        <f t="shared" si="0"/>
-        <v>2500</v>
-      </c>
-      <c r="K28" s="2">
-        <v>1</v>
-      </c>
-      <c r="L28" s="2">
-        <v>12000001</v>
-      </c>
-      <c r="M28" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="29" s="2" customFormat="1" customHeight="1" spans="2:13">
-      <c r="B29" s="2">
-        <v>10003002</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D29" s="2">
-        <v>10003002</v>
       </c>
       <c r="E29" s="2">
         <v>3</v>
       </c>
       <c r="F29" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G29" s="2">
         <v>3</v>
       </c>
       <c r="H29" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I29" s="2">
         <v>1</v>
       </c>
       <c r="J29" s="3">
-        <f t="shared" si="0"/>
-        <v>2600</v>
+        <f t="shared" si="1"/>
+        <v>2500</v>
       </c>
       <c r="K29" s="2">
         <v>1</v>
       </c>
       <c r="L29" s="2">
-        <v>12000002</v>
-      </c>
-      <c r="M29" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="30" s="2" customFormat="1" customHeight="1" spans="2:13">
+        <v>12000001</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B30" s="2">
-        <v>10003003</v>
+        <v>10003002</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D30" s="2">
-        <v>10003003</v>
+        <v>10003002</v>
       </c>
       <c r="E30" s="2">
         <v>3</v>
       </c>
       <c r="F30" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G30" s="2">
         <v>3</v>
       </c>
       <c r="H30" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I30" s="2">
         <v>1</v>
       </c>
       <c r="J30" s="3">
-        <f t="shared" si="0"/>
-        <v>2700</v>
+        <f t="shared" si="1"/>
+        <v>2600</v>
       </c>
       <c r="K30" s="2">
         <v>1</v>
       </c>
       <c r="L30" s="2">
-        <v>12000003</v>
-      </c>
-      <c r="M30" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="31" s="2" customFormat="1" customHeight="1" spans="2:13">
+        <v>12000002</v>
+      </c>
+      <c r="N30" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B31" s="2">
-        <v>10003004</v>
+        <v>10003003</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D31" s="2">
-        <v>10003004</v>
+        <v>10003003</v>
       </c>
       <c r="E31" s="2">
         <v>3</v>
       </c>
       <c r="F31" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G31" s="2">
         <v>3</v>
       </c>
       <c r="H31" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I31" s="2">
         <v>1</v>
       </c>
       <c r="J31" s="3">
-        <f t="shared" si="0"/>
-        <v>2800</v>
+        <f t="shared" si="1"/>
+        <v>2700</v>
       </c>
       <c r="K31" s="2">
         <v>1</v>
       </c>
       <c r="L31" s="2">
-        <v>12000004</v>
-      </c>
-      <c r="M31" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="32" s="2" customFormat="1" customHeight="1" spans="2:13">
+        <v>12000003</v>
+      </c>
+      <c r="N31" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B32" s="2">
-        <v>10003005</v>
+        <v>10003004</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D32" s="2">
-        <v>10003005</v>
+        <v>10003004</v>
       </c>
       <c r="E32" s="2">
         <v>3</v>
       </c>
       <c r="F32" s="3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G32" s="2">
         <v>3</v>
       </c>
       <c r="H32" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I32" s="2">
         <v>1</v>
       </c>
       <c r="J32" s="3">
-        <f t="shared" si="0"/>
-        <v>2900</v>
+        <f t="shared" si="1"/>
+        <v>2800</v>
       </c>
       <c r="K32" s="2">
         <v>1</v>
       </c>
       <c r="L32" s="2">
-        <v>12000005</v>
-      </c>
-      <c r="M32" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="33" s="2" customFormat="1" customHeight="1" spans="2:13">
+        <v>12000004</v>
+      </c>
+      <c r="N32" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B33" s="2">
-        <v>10003006</v>
+        <v>10003005</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D33" s="2">
-        <v>10003006</v>
+        <v>10003005</v>
       </c>
       <c r="E33" s="2">
         <v>3</v>
       </c>
       <c r="F33" s="3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G33" s="2">
         <v>3</v>
       </c>
       <c r="H33" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I33" s="2">
         <v>1</v>
       </c>
       <c r="J33" s="3">
-        <f t="shared" si="0"/>
-        <v>3000</v>
+        <f t="shared" si="1"/>
+        <v>2900</v>
       </c>
       <c r="K33" s="2">
         <v>1</v>
       </c>
       <c r="L33" s="2">
-        <v>12000006</v>
-      </c>
-      <c r="M33" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="34" s="2" customFormat="1" customHeight="1" spans="2:13">
+        <v>12000005</v>
+      </c>
+      <c r="N33" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B34" s="2">
-        <v>10003011</v>
+        <v>10003006</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D34" s="2">
-        <v>10003001</v>
+        <v>10003006</v>
       </c>
       <c r="E34" s="2">
         <v>3</v>
       </c>
       <c r="F34" s="3">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G34" s="2">
         <v>3</v>
       </c>
       <c r="H34" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I34" s="2">
         <v>1</v>
       </c>
       <c r="J34" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
+        <v>3000</v>
+      </c>
+      <c r="K34" s="2">
+        <v>1</v>
+      </c>
+      <c r="L34" s="2">
+        <v>12000006</v>
+      </c>
+      <c r="N34" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="2:14">
+      <c r="B35" s="2">
+        <v>10003011</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D35" s="2">
+        <v>10003001</v>
+      </c>
+      <c r="E35" s="2">
+        <v>3</v>
+      </c>
+      <c r="F35" s="3">
+        <v>25</v>
+      </c>
+      <c r="G35" s="2">
+        <v>3</v>
+      </c>
+      <c r="H35" s="2">
+        <v>1</v>
+      </c>
+      <c r="I35" s="2">
+        <v>1</v>
+      </c>
+      <c r="J35" s="3">
+        <f t="shared" si="1"/>
         <v>3100</v>
       </c>
-      <c r="K34" s="2">
-        <v>1</v>
-      </c>
-      <c r="L34" s="2">
+      <c r="K35" s="2">
+        <v>1</v>
+      </c>
+      <c r="L35" s="2">
         <v>12000011</v>
       </c>
-      <c r="M34" s="2" t="s">
-        <v>69</v>
+      <c r="N35" s="2" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/ItemConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ItemConfig.xlsx
@@ -208,7 +208,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="87">
   <si>
     <t>##var</t>
   </si>
@@ -382,6 +382,12 @@
   </si>
   <si>
     <t>英雄增加100经验</t>
+  </si>
+  <si>
+    <t>低级魂石</t>
+  </si>
+  <si>
+    <t>英雄增加100魂石</t>
   </si>
   <si>
     <t>大熊猫碎片</t>
@@ -649,18 +655,18 @@
     <font>
       <b/>
       <sz val="9"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1523,7 +1529,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.875" style="3" customWidth="1"/>
@@ -1729,7 +1735,7 @@
         <v>1</v>
       </c>
       <c r="J5" s="3">
-        <f>J4+100</f>
+        <f t="shared" ref="J5:J11" si="0">J4+100</f>
         <v>200</v>
       </c>
       <c r="K5" s="3">
@@ -1768,7 +1774,7 @@
         <v>1</v>
       </c>
       <c r="J6" s="3">
-        <f>J5+100</f>
+        <f t="shared" si="0"/>
         <v>300</v>
       </c>
       <c r="K6" s="3">
@@ -1807,7 +1813,7 @@
         <v>1</v>
       </c>
       <c r="J7" s="3">
-        <f>J6+100</f>
+        <f t="shared" si="0"/>
         <v>400</v>
       </c>
       <c r="K7" s="3">
@@ -1846,7 +1852,7 @@
         <v>1</v>
       </c>
       <c r="J8" s="3">
-        <f>J7+100</f>
+        <f t="shared" si="0"/>
         <v>500</v>
       </c>
       <c r="K8" s="3">
@@ -1885,7 +1891,7 @@
         <v>1</v>
       </c>
       <c r="J9" s="3">
-        <f>J8+100</f>
+        <f t="shared" si="0"/>
         <v>600</v>
       </c>
       <c r="K9" s="2">
@@ -1924,7 +1930,7 @@
         <v>1</v>
       </c>
       <c r="J10" s="3">
-        <f>J9+100</f>
+        <f t="shared" si="0"/>
         <v>700</v>
       </c>
       <c r="K10" s="2">
@@ -1963,7 +1969,7 @@
         <v>1</v>
       </c>
       <c r="J11" s="3">
-        <f>J10+100</f>
+        <f t="shared" si="0"/>
         <v>800</v>
       </c>
       <c r="K11" s="2">
@@ -2002,7 +2008,7 @@
         <v>1</v>
       </c>
       <c r="J12" s="3">
-        <f t="shared" ref="J12:J17" si="0">J11+100</f>
+        <f t="shared" ref="J12:J18" si="1">J11+100</f>
         <v>900</v>
       </c>
       <c r="K12" s="2">
@@ -2041,7 +2047,7 @@
         <v>1</v>
       </c>
       <c r="J13" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1000</v>
       </c>
       <c r="K13" s="2">
@@ -2080,7 +2086,7 @@
         <v>1</v>
       </c>
       <c r="J14" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1100</v>
       </c>
       <c r="K14" s="2">
@@ -2119,7 +2125,7 @@
         <v>1</v>
       </c>
       <c r="J15" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1200</v>
       </c>
       <c r="K15" s="2">
@@ -2158,7 +2164,7 @@
         <v>1</v>
       </c>
       <c r="J16" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1300</v>
       </c>
       <c r="K16" s="2">
@@ -2197,7 +2203,7 @@
         <v>1</v>
       </c>
       <c r="J17" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1400</v>
       </c>
       <c r="K17" s="2">
@@ -2215,7 +2221,7 @@
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B18" s="2">
-        <v>10002001</v>
+        <v>10001010</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>58</v>
@@ -2224,63 +2230,66 @@
         <v>10000009</v>
       </c>
       <c r="E18" s="2">
+        <v>3</v>
+      </c>
+      <c r="F18" s="3">
+        <v>1</v>
+      </c>
+      <c r="G18" s="2">
+        <v>1</v>
+      </c>
+      <c r="H18" s="2">
+        <v>9</v>
+      </c>
+      <c r="I18" s="2">
+        <v>1</v>
+      </c>
+      <c r="J18" s="3">
+        <f t="shared" si="1"/>
+        <v>1500</v>
+      </c>
+      <c r="K18" s="2">
+        <v>99</v>
+      </c>
+      <c r="L18" s="2">
+        <v>0</v>
+      </c>
+      <c r="M18" s="2">
+        <v>100</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="2:14">
+      <c r="B19" s="2">
+        <v>10002001</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" s="2">
+        <v>10000009</v>
+      </c>
+      <c r="E19" s="2">
         <v>2</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F19" s="3">
         <v>14</v>
       </c>
-      <c r="G18" s="2">
+      <c r="G19" s="2">
         <v>2</v>
       </c>
-      <c r="H18" s="2">
-        <v>0</v>
-      </c>
-      <c r="I18" s="2">
-        <v>1</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="H19" s="2">
+        <v>0</v>
+      </c>
+      <c r="I19" s="2">
+        <v>1</v>
+      </c>
+      <c r="J19" s="3">
         <f>J16+100</f>
         <v>1400</v>
       </c>
-      <c r="K18" s="2">
-        <v>999</v>
-      </c>
-      <c r="L18" s="2">
-        <v>0</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="2:14">
-      <c r="B19" s="2">
-        <v>10002002</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D19" s="2">
-        <v>10000010</v>
-      </c>
-      <c r="E19" s="2">
-        <v>3</v>
-      </c>
-      <c r="F19" s="3">
-        <v>15</v>
-      </c>
-      <c r="G19" s="2">
-        <v>2</v>
-      </c>
-      <c r="H19" s="2">
-        <v>0</v>
-      </c>
-      <c r="I19" s="2">
-        <v>1</v>
-      </c>
-      <c r="J19" s="3">
-        <f t="shared" ref="J18:J35" si="1">J18+100</f>
-        <v>1500</v>
-      </c>
       <c r="K19" s="2">
         <v>999</v>
       </c>
@@ -2288,24 +2297,24 @@
         <v>0</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B20" s="2">
-        <v>10002003</v>
+        <v>10002002</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D20" s="2">
-        <v>10000011</v>
+        <v>10000010</v>
       </c>
       <c r="E20" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F20" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G20" s="2">
         <v>2</v>
@@ -2317,8 +2326,8 @@
         <v>1</v>
       </c>
       <c r="J20" s="3">
-        <f t="shared" si="1"/>
-        <v>1600</v>
+        <f t="shared" ref="J19:J36" si="2">J19+100</f>
+        <v>1500</v>
       </c>
       <c r="K20" s="2">
         <v>999</v>
@@ -2327,24 +2336,24 @@
         <v>0</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B21" s="2">
-        <v>10002004</v>
+        <v>10002003</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D21" s="2">
-        <v>10000012</v>
+        <v>10000011</v>
       </c>
       <c r="E21" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F21" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G21" s="2">
         <v>2</v>
@@ -2356,8 +2365,8 @@
         <v>1</v>
       </c>
       <c r="J21" s="3">
-        <f t="shared" si="1"/>
-        <v>1700</v>
+        <f t="shared" si="2"/>
+        <v>1600</v>
       </c>
       <c r="K21" s="2">
         <v>999</v>
@@ -2366,24 +2375,24 @@
         <v>0</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B22" s="2">
-        <v>10002005</v>
+        <v>10002004</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D22" s="2">
-        <v>10000013</v>
+        <v>10000012</v>
       </c>
       <c r="E22" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F22" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G22" s="2">
         <v>2</v>
@@ -2395,8 +2404,8 @@
         <v>1</v>
       </c>
       <c r="J22" s="3">
-        <f t="shared" si="1"/>
-        <v>1800</v>
+        <f t="shared" si="2"/>
+        <v>1700</v>
       </c>
       <c r="K22" s="2">
         <v>999</v>
@@ -2405,24 +2414,24 @@
         <v>0</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B23" s="2">
-        <v>10002006</v>
+        <v>10002005</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>60</v>
       </c>
       <c r="D23" s="2">
-        <v>10000001</v>
+        <v>10000013</v>
       </c>
       <c r="E23" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F23" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G23" s="2">
         <v>2</v>
@@ -2434,8 +2443,8 @@
         <v>1</v>
       </c>
       <c r="J23" s="3">
-        <f t="shared" si="1"/>
-        <v>1900</v>
+        <f t="shared" si="2"/>
+        <v>1800</v>
       </c>
       <c r="K23" s="2">
         <v>999</v>
@@ -2449,19 +2458,19 @@
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B24" s="2">
-        <v>10002007</v>
+        <v>10002006</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D24" s="2">
-        <v>10000002</v>
+        <v>10000001</v>
       </c>
       <c r="E24" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G24" s="2">
         <v>2</v>
@@ -2473,8 +2482,8 @@
         <v>1</v>
       </c>
       <c r="J24" s="3">
-        <f t="shared" si="1"/>
-        <v>2000</v>
+        <f t="shared" si="2"/>
+        <v>1900</v>
       </c>
       <c r="K24" s="2">
         <v>999</v>
@@ -2488,19 +2497,19 @@
     </row>
     <row r="25" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B25" s="2">
-        <v>10002008</v>
+        <v>10002007</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D25" s="2">
-        <v>10000003</v>
+        <v>10000002</v>
       </c>
       <c r="E25" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F25" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G25" s="2">
         <v>2</v>
@@ -2512,8 +2521,8 @@
         <v>1</v>
       </c>
       <c r="J25" s="3">
-        <f t="shared" si="1"/>
-        <v>2100</v>
+        <f t="shared" si="2"/>
+        <v>2000</v>
       </c>
       <c r="K25" s="2">
         <v>999</v>
@@ -2527,19 +2536,19 @@
     </row>
     <row r="26" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B26" s="2">
-        <v>10002009</v>
+        <v>10002008</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>66</v>
       </c>
       <c r="D26" s="2">
-        <v>10000004</v>
+        <v>10000003</v>
       </c>
       <c r="E26" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F26" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G26" s="2">
         <v>2</v>
@@ -2551,8 +2560,8 @@
         <v>1</v>
       </c>
       <c r="J26" s="3">
-        <f t="shared" si="1"/>
-        <v>2200</v>
+        <f t="shared" si="2"/>
+        <v>2100</v>
       </c>
       <c r="K26" s="2">
         <v>999</v>
@@ -2566,19 +2575,19 @@
     </row>
     <row r="27" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B27" s="2">
-        <v>10002010</v>
+        <v>10002009</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>68</v>
       </c>
       <c r="D27" s="2">
-        <v>10000005</v>
+        <v>10000004</v>
       </c>
       <c r="E27" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F27" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G27" s="2">
         <v>2</v>
@@ -2590,8 +2599,8 @@
         <v>1</v>
       </c>
       <c r="J27" s="3">
-        <f t="shared" si="1"/>
-        <v>2300</v>
+        <f t="shared" si="2"/>
+        <v>2200</v>
       </c>
       <c r="K27" s="2">
         <v>999</v>
@@ -2605,19 +2614,19 @@
     </row>
     <row r="28" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B28" s="2">
-        <v>10002011</v>
+        <v>10002010</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>70</v>
       </c>
       <c r="D28" s="2">
-        <v>10000006</v>
+        <v>10000005</v>
       </c>
       <c r="E28" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F28" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G28" s="2">
         <v>2</v>
@@ -2629,8 +2638,8 @@
         <v>1</v>
       </c>
       <c r="J28" s="3">
-        <f t="shared" si="1"/>
-        <v>2400</v>
+        <f t="shared" si="2"/>
+        <v>2300</v>
       </c>
       <c r="K28" s="2">
         <v>999</v>
@@ -2644,38 +2653,38 @@
     </row>
     <row r="29" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B29" s="2">
-        <v>10003001</v>
+        <v>10002011</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>72</v>
       </c>
       <c r="D29" s="2">
-        <v>10003001</v>
+        <v>10000006</v>
       </c>
       <c r="E29" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F29" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G29" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H29" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" s="2">
         <v>1</v>
       </c>
       <c r="J29" s="3">
-        <f t="shared" si="1"/>
-        <v>2500</v>
+        <f t="shared" si="2"/>
+        <v>2400</v>
       </c>
       <c r="K29" s="2">
-        <v>1</v>
+        <v>999</v>
       </c>
       <c r="L29" s="2">
-        <v>12000001</v>
+        <v>0</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>73</v>
@@ -2683,38 +2692,38 @@
     </row>
     <row r="30" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B30" s="2">
-        <v>10003002</v>
+        <v>10003001</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D30" s="2">
-        <v>10003002</v>
+        <v>10003001</v>
       </c>
       <c r="E30" s="2">
         <v>3</v>
       </c>
       <c r="F30" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G30" s="2">
         <v>3</v>
       </c>
       <c r="H30" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I30" s="2">
         <v>1</v>
       </c>
       <c r="J30" s="3">
-        <f t="shared" si="1"/>
-        <v>2600</v>
+        <f t="shared" si="2"/>
+        <v>2500</v>
       </c>
       <c r="K30" s="2">
         <v>1</v>
       </c>
       <c r="L30" s="2">
-        <v>12000002</v>
+        <v>12000001</v>
       </c>
       <c r="N30" s="2" t="s">
         <v>75</v>
@@ -2722,38 +2731,38 @@
     </row>
     <row r="31" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B31" s="2">
-        <v>10003003</v>
+        <v>10003002</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>76</v>
       </c>
       <c r="D31" s="2">
-        <v>10003003</v>
+        <v>10003002</v>
       </c>
       <c r="E31" s="2">
         <v>3</v>
       </c>
       <c r="F31" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G31" s="2">
         <v>3</v>
       </c>
       <c r="H31" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I31" s="2">
         <v>1</v>
       </c>
       <c r="J31" s="3">
-        <f t="shared" si="1"/>
-        <v>2700</v>
+        <f t="shared" si="2"/>
+        <v>2600</v>
       </c>
       <c r="K31" s="2">
         <v>1</v>
       </c>
       <c r="L31" s="2">
-        <v>12000003</v>
+        <v>12000002</v>
       </c>
       <c r="N31" s="2" t="s">
         <v>77</v>
@@ -2761,38 +2770,38 @@
     </row>
     <row r="32" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B32" s="2">
-        <v>10003004</v>
+        <v>10003003</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>78</v>
       </c>
       <c r="D32" s="2">
-        <v>10003004</v>
+        <v>10003003</v>
       </c>
       <c r="E32" s="2">
         <v>3</v>
       </c>
       <c r="F32" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G32" s="2">
         <v>3</v>
       </c>
       <c r="H32" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I32" s="2">
         <v>1</v>
       </c>
       <c r="J32" s="3">
-        <f t="shared" si="1"/>
-        <v>2800</v>
+        <f t="shared" si="2"/>
+        <v>2700</v>
       </c>
       <c r="K32" s="2">
         <v>1</v>
       </c>
       <c r="L32" s="2">
-        <v>12000004</v>
+        <v>12000003</v>
       </c>
       <c r="N32" s="2" t="s">
         <v>79</v>
@@ -2800,38 +2809,38 @@
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B33" s="2">
-        <v>10003005</v>
+        <v>10003004</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>80</v>
       </c>
       <c r="D33" s="2">
-        <v>10003005</v>
+        <v>10003004</v>
       </c>
       <c r="E33" s="2">
         <v>3</v>
       </c>
       <c r="F33" s="3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G33" s="2">
         <v>3</v>
       </c>
       <c r="H33" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I33" s="2">
         <v>1</v>
       </c>
       <c r="J33" s="3">
-        <f t="shared" si="1"/>
-        <v>2900</v>
+        <f t="shared" si="2"/>
+        <v>2800</v>
       </c>
       <c r="K33" s="2">
         <v>1</v>
       </c>
       <c r="L33" s="2">
-        <v>12000005</v>
+        <v>12000004</v>
       </c>
       <c r="N33" s="2" t="s">
         <v>81</v>
@@ -2839,38 +2848,38 @@
     </row>
     <row r="34" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B34" s="2">
-        <v>10003006</v>
+        <v>10003005</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>82</v>
       </c>
       <c r="D34" s="2">
-        <v>10003006</v>
+        <v>10003005</v>
       </c>
       <c r="E34" s="2">
         <v>3</v>
       </c>
       <c r="F34" s="3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G34" s="2">
         <v>3</v>
       </c>
       <c r="H34" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I34" s="2">
         <v>1</v>
       </c>
       <c r="J34" s="3">
-        <f t="shared" si="1"/>
-        <v>3000</v>
+        <f t="shared" si="2"/>
+        <v>2900</v>
       </c>
       <c r="K34" s="2">
         <v>1</v>
       </c>
       <c r="L34" s="2">
-        <v>12000006</v>
+        <v>12000005</v>
       </c>
       <c r="N34" s="2" t="s">
         <v>83</v>
@@ -2878,41 +2887,80 @@
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B35" s="2">
-        <v>10003011</v>
+        <v>10003006</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>84</v>
       </c>
       <c r="D35" s="2">
-        <v>10003001</v>
+        <v>10003006</v>
       </c>
       <c r="E35" s="2">
         <v>3</v>
       </c>
       <c r="F35" s="3">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G35" s="2">
         <v>3</v>
       </c>
       <c r="H35" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I35" s="2">
         <v>1</v>
       </c>
       <c r="J35" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
+        <v>3000</v>
+      </c>
+      <c r="K35" s="2">
+        <v>1</v>
+      </c>
+      <c r="L35" s="2">
+        <v>12000006</v>
+      </c>
+      <c r="N35" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="2:14">
+      <c r="B36" s="2">
+        <v>10003011</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D36" s="2">
+        <v>10003001</v>
+      </c>
+      <c r="E36" s="2">
+        <v>3</v>
+      </c>
+      <c r="F36" s="3">
+        <v>25</v>
+      </c>
+      <c r="G36" s="2">
+        <v>3</v>
+      </c>
+      <c r="H36" s="2">
+        <v>1</v>
+      </c>
+      <c r="I36" s="2">
+        <v>1</v>
+      </c>
+      <c r="J36" s="3">
+        <f t="shared" si="2"/>
         <v>3100</v>
       </c>
-      <c r="K35" s="2">
-        <v>1</v>
-      </c>
-      <c r="L35" s="2">
+      <c r="K36" s="2">
+        <v>1</v>
+      </c>
+      <c r="L36" s="2">
         <v>12000011</v>
       </c>
-      <c r="N35" s="2" t="s">
-        <v>73</v>
+      <c r="N36" s="2" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/ItemConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ItemConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12795"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -141,6 +141,8 @@
 5 使用后永久增加属性
 6 抽奖券
 7 副本入场券
+8 英雄经验
+9 英雄魂石
 </t>
         </r>
         <r>
@@ -2203,7 +2205,7 @@
         <v>1</v>
       </c>
       <c r="J17" s="3">
-        <f t="shared" si="1"/>
+        <f>J16+100</f>
         <v>1400</v>
       </c>
       <c r="K17" s="2">
@@ -2245,7 +2247,7 @@
         <v>1</v>
       </c>
       <c r="J18" s="3">
-        <f t="shared" si="1"/>
+        <f>J17+100</f>
         <v>1500</v>
       </c>
       <c r="K18" s="2">
@@ -2287,8 +2289,8 @@
         <v>1</v>
       </c>
       <c r="J19" s="3">
-        <f>J16+100</f>
-        <v>1400</v>
+        <f>J18+100</f>
+        <v>1600</v>
       </c>
       <c r="K19" s="2">
         <v>999</v>
@@ -2327,7 +2329,7 @@
       </c>
       <c r="J20" s="3">
         <f t="shared" ref="J19:J36" si="2">J19+100</f>
-        <v>1500</v>
+        <v>1700</v>
       </c>
       <c r="K20" s="2">
         <v>999</v>
@@ -2366,7 +2368,7 @@
       </c>
       <c r="J21" s="3">
         <f t="shared" si="2"/>
-        <v>1600</v>
+        <v>1800</v>
       </c>
       <c r="K21" s="2">
         <v>999</v>
@@ -2405,7 +2407,7 @@
       </c>
       <c r="J22" s="3">
         <f t="shared" si="2"/>
-        <v>1700</v>
+        <v>1900</v>
       </c>
       <c r="K22" s="2">
         <v>999</v>
@@ -2444,7 +2446,7 @@
       </c>
       <c r="J23" s="3">
         <f t="shared" si="2"/>
-        <v>1800</v>
+        <v>2000</v>
       </c>
       <c r="K23" s="2">
         <v>999</v>
@@ -2483,7 +2485,7 @@
       </c>
       <c r="J24" s="3">
         <f t="shared" si="2"/>
-        <v>1900</v>
+        <v>2100</v>
       </c>
       <c r="K24" s="2">
         <v>999</v>
@@ -2522,7 +2524,7 @@
       </c>
       <c r="J25" s="3">
         <f t="shared" si="2"/>
-        <v>2000</v>
+        <v>2200</v>
       </c>
       <c r="K25" s="2">
         <v>999</v>
@@ -2561,7 +2563,7 @@
       </c>
       <c r="J26" s="3">
         <f t="shared" si="2"/>
-        <v>2100</v>
+        <v>2300</v>
       </c>
       <c r="K26" s="2">
         <v>999</v>
@@ -2600,7 +2602,7 @@
       </c>
       <c r="J27" s="3">
         <f t="shared" si="2"/>
-        <v>2200</v>
+        <v>2400</v>
       </c>
       <c r="K27" s="2">
         <v>999</v>
@@ -2639,7 +2641,7 @@
       </c>
       <c r="J28" s="3">
         <f t="shared" si="2"/>
-        <v>2300</v>
+        <v>2500</v>
       </c>
       <c r="K28" s="2">
         <v>999</v>
@@ -2678,7 +2680,7 @@
       </c>
       <c r="J29" s="3">
         <f t="shared" si="2"/>
-        <v>2400</v>
+        <v>2600</v>
       </c>
       <c r="K29" s="2">
         <v>999</v>
@@ -2717,7 +2719,7 @@
       </c>
       <c r="J30" s="3">
         <f t="shared" si="2"/>
-        <v>2500</v>
+        <v>2700</v>
       </c>
       <c r="K30" s="2">
         <v>1</v>
@@ -2756,7 +2758,7 @@
       </c>
       <c r="J31" s="3">
         <f t="shared" si="2"/>
-        <v>2600</v>
+        <v>2800</v>
       </c>
       <c r="K31" s="2">
         <v>1</v>
@@ -2795,7 +2797,7 @@
       </c>
       <c r="J32" s="3">
         <f t="shared" si="2"/>
-        <v>2700</v>
+        <v>2900</v>
       </c>
       <c r="K32" s="2">
         <v>1</v>
@@ -2834,7 +2836,7 @@
       </c>
       <c r="J33" s="3">
         <f t="shared" si="2"/>
-        <v>2800</v>
+        <v>3000</v>
       </c>
       <c r="K33" s="2">
         <v>1</v>
@@ -2873,7 +2875,7 @@
       </c>
       <c r="J34" s="3">
         <f t="shared" si="2"/>
-        <v>2900</v>
+        <v>3100</v>
       </c>
       <c r="K34" s="2">
         <v>1</v>
@@ -2912,7 +2914,7 @@
       </c>
       <c r="J35" s="3">
         <f t="shared" si="2"/>
-        <v>3000</v>
+        <v>3200</v>
       </c>
       <c r="K35" s="2">
         <v>1</v>
@@ -2951,7 +2953,7 @@
       </c>
       <c r="J36" s="3">
         <f t="shared" si="2"/>
-        <v>3100</v>
+        <v>3300</v>
       </c>
       <c r="K36" s="2">
         <v>1</v>

--- a/Unity/Assets/Config/Excel/ItemConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ItemConfig.xlsx
@@ -1,38 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\DreamGit\Unity\Assets\Config\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FE6E043-F3EE-46D5-8606-10D429CA15D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="D3" authorId="0">
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -54,7 +47,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E3" authorId="0">
+    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -81,7 +74,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0">
+    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -106,7 +99,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="0">
+    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -134,15 +127,244 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">当道具类型为1（消耗品）时字段的意义
-1 获得金币值
-2 获得经验值
-3 随机宝箱
-4 自选宝箱
-5 使用后永久增加属性
-6 抽奖券
-7 副本入场券
-8 英雄经验
-9 英雄魂石
+1 </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="微软雅黑"/>
+            <family val="2"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">  </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">获得金币值
+2 </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="微软雅黑"/>
+            <family val="2"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">  </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>获得经验值
+3</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="微软雅黑"/>
+            <family val="2"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="微软雅黑"/>
+            <family val="2"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">随机宝箱
+4 </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="微软雅黑"/>
+            <family val="2"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">  </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">自选宝箱
+5 </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="微软雅黑"/>
+            <family val="2"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">  </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">使用后永久增加属性
+6 </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="微软雅黑"/>
+            <family val="2"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">  </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">抽奖券
+7 </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="微软雅黑"/>
+            <family val="2"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">  </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>副本入场券
+8</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="微软雅黑"/>
+            <family val="2"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="微软雅黑"/>
+            <family val="2"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>英雄经验
+9</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="微软雅黑"/>
+            <family val="2"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">  </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve"> 英雄魂石
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="微软雅黑"/>
+            <family val="2"/>
+            <charset val="134"/>
+          </rPr>
+          <t>10 英雄碎片</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
 </t>
         </r>
         <r>
@@ -161,7 +383,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I3" authorId="0">
+    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -183,7 +405,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L3" authorId="0">
+    <comment ref="L3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -210,7 +432,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="88">
   <si>
     <t>##var</t>
   </si>
@@ -332,15 +554,9 @@
     <t>联盟贡献度可以在联盟商店中兑换商品</t>
   </si>
   <si>
-    <t>随机红将碎片</t>
-  </si>
-  <si>
     <t>打开后从以下红色技能中随机获取一件</t>
   </si>
   <si>
-    <t>自选红将碎片</t>
-  </si>
-  <si>
     <t>打开后从以下红色技能中自选一件</t>
   </si>
   <si>
@@ -471,19 +687,25 @@
   </si>
   <si>
     <t>一个更吊的头盔</t>
+  </si>
+  <si>
+    <t>随机宝箱</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>自选宝箱</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>100,200</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="27">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -511,147 +733,10 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -676,8 +761,29 @@
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="36">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -702,194 +808,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="12">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -940,256 +860,14 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1205,69 +883,43 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 6" xfId="49"/>
+    <cellStyle name="常规 6" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1525,23 +1177,23 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N36"/>
-  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.875" style="3" customWidth="1"/>
     <col min="2" max="12" width="17.875" style="3"/>
-    <col min="13" max="13" width="20.5" style="3" customWidth="1"/>
+    <col min="13" max="13" width="20.5" style="10" customWidth="1"/>
     <col min="14" max="14" width="70.625" style="3" customWidth="1"/>
     <col min="15" max="16384" width="17.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:14">
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1578,14 +1230,14 @@
       <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="8" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:14">
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -1622,14 +1274,14 @@
       <c r="L2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="M2" s="8" t="s">
         <v>16</v>
       </c>
       <c r="N2" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:14">
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
@@ -1666,14 +1318,14 @@
       <c r="L3" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="9" t="s">
         <v>28</v>
       </c>
       <c r="N3" s="6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="2:14">
+    <row r="4" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="3">
         <v>1</v>
       </c>
@@ -1711,7 +1363,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="2:14">
+    <row r="5" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="3">
         <v>2</v>
       </c>
@@ -1750,7 +1402,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="2:14">
+    <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="3">
         <v>3</v>
       </c>
@@ -1789,7 +1441,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="2:14">
+    <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="3">
         <v>4</v>
       </c>
@@ -1828,7 +1480,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="2:14">
+    <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="3">
         <v>5</v>
       </c>
@@ -1867,12 +1519,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="2:14">
+    <row r="9" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="2">
         <v>10001001</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>40</v>
+      <c r="C9" s="7" t="s">
+        <v>85</v>
       </c>
       <c r="D9" s="2">
         <v>10000001</v>
@@ -1902,16 +1554,17 @@
       <c r="L9" s="2">
         <v>0</v>
       </c>
+      <c r="M9" s="11"/>
       <c r="N9" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" s="2" customFormat="1" ht="19.5" customHeight="1" spans="2:14">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="2">
         <v>10001002</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>42</v>
+      <c r="C10" s="7" t="s">
+        <v>86</v>
       </c>
       <c r="D10" s="2">
         <v>10000002</v>
@@ -1941,16 +1594,17 @@
       <c r="L10" s="2">
         <v>0</v>
       </c>
+      <c r="M10" s="11"/>
       <c r="N10" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="2:14">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="2">
         <v>10001003</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D11" s="2">
         <v>10000003</v>
@@ -1980,16 +1634,17 @@
       <c r="L11" s="2">
         <v>0</v>
       </c>
+      <c r="M11" s="11"/>
       <c r="N11" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="2:14">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="2">
         <v>10001004</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D12" s="2">
         <v>10000004</v>
@@ -2010,7 +1665,7 @@
         <v>1</v>
       </c>
       <c r="J12" s="3">
-        <f t="shared" ref="J12:J18" si="1">J11+100</f>
+        <f t="shared" ref="J12:J16" si="1">J11+100</f>
         <v>900</v>
       </c>
       <c r="K12" s="2">
@@ -2019,16 +1674,17 @@
       <c r="L12" s="2">
         <v>0</v>
       </c>
+      <c r="M12" s="11"/>
       <c r="N12" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="2:14">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="2">
         <v>10001005</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D13" s="2">
         <v>10000005</v>
@@ -2058,16 +1714,17 @@
       <c r="L13" s="2">
         <v>0</v>
       </c>
+      <c r="M13" s="11"/>
       <c r="N13" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="2:14">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="2">
         <v>10001006</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D14" s="2">
         <v>10000006</v>
@@ -2097,16 +1754,17 @@
       <c r="L14" s="2">
         <v>0</v>
       </c>
+      <c r="M14" s="11"/>
       <c r="N14" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="15" s="2" customFormat="1" customHeight="1" spans="2:14">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="2">
         <v>10001007</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D15" s="2">
         <v>10000007</v>
@@ -2136,16 +1794,17 @@
       <c r="L15" s="2">
         <v>0</v>
       </c>
+      <c r="M15" s="11"/>
       <c r="N15" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="16" s="2" customFormat="1" customHeight="1" spans="2:14">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="2">
         <v>10001008</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D16" s="2">
         <v>10000008</v>
@@ -2175,16 +1834,17 @@
       <c r="L16" s="2">
         <v>0</v>
       </c>
+      <c r="M16" s="11"/>
       <c r="N16" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" s="2" customFormat="1" customHeight="1" spans="2:14">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="2">
         <v>10001009</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D17" s="2">
         <v>10000009</v>
@@ -2214,19 +1874,19 @@
       <c r="L17" s="2">
         <v>0</v>
       </c>
-      <c r="M17" s="2">
-        <v>100</v>
+      <c r="M17" s="12" t="s">
+        <v>87</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="18" s="2" customFormat="1" customHeight="1" spans="2:14">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="2">
         <v>10001010</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D18" s="2">
         <v>10000009</v>
@@ -2256,19 +1916,19 @@
       <c r="L18" s="2">
         <v>0</v>
       </c>
-      <c r="M18" s="2">
-        <v>100</v>
+      <c r="M18" s="12" t="s">
+        <v>87</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="2:14">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="2">
         <v>10002001</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D19" s="2">
         <v>10000009</v>
@@ -2298,16 +1958,17 @@
       <c r="L19" s="2">
         <v>0</v>
       </c>
+      <c r="M19" s="11"/>
       <c r="N19" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="20" s="2" customFormat="1" customHeight="1" spans="2:14">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="2">
         <v>10002002</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D20" s="2">
         <v>10000010</v>
@@ -2328,7 +1989,7 @@
         <v>1</v>
       </c>
       <c r="J20" s="3">
-        <f t="shared" ref="J19:J36" si="2">J19+100</f>
+        <f t="shared" ref="J20:J36" si="2">J19+100</f>
         <v>1700</v>
       </c>
       <c r="K20" s="2">
@@ -2337,16 +1998,17 @@
       <c r="L20" s="2">
         <v>0</v>
       </c>
+      <c r="M20" s="11"/>
       <c r="N20" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="21" s="2" customFormat="1" customHeight="1" spans="2:14">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="2">
         <v>10002003</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D21" s="2">
         <v>10000011</v>
@@ -2376,16 +2038,17 @@
       <c r="L21" s="2">
         <v>0</v>
       </c>
+      <c r="M21" s="11"/>
       <c r="N21" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="22" s="2" customFormat="1" customHeight="1" spans="2:14">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="2">
         <v>10002004</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D22" s="2">
         <v>10000012</v>
@@ -2415,16 +2078,17 @@
       <c r="L22" s="2">
         <v>0</v>
       </c>
+      <c r="M22" s="11"/>
       <c r="N22" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="23" s="2" customFormat="1" customHeight="1" spans="2:14">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="2">
         <v>10002005</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D23" s="2">
         <v>10000013</v>
@@ -2454,16 +2118,17 @@
       <c r="L23" s="2">
         <v>0</v>
       </c>
+      <c r="M23" s="11"/>
       <c r="N23" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="24" s="2" customFormat="1" customHeight="1" spans="2:14">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B24" s="2">
         <v>10002006</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D24" s="2">
         <v>10000001</v>
@@ -2493,16 +2158,17 @@
       <c r="L24" s="2">
         <v>0</v>
       </c>
+      <c r="M24" s="11"/>
       <c r="N24" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="25" s="2" customFormat="1" customHeight="1" spans="2:14">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="2">
         <v>10002007</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D25" s="2">
         <v>10000002</v>
@@ -2532,16 +2198,17 @@
       <c r="L25" s="2">
         <v>0</v>
       </c>
+      <c r="M25" s="11"/>
       <c r="N25" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="26" s="2" customFormat="1" customHeight="1" spans="2:14">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="2">
         <v>10002008</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D26" s="2">
         <v>10000003</v>
@@ -2571,16 +2238,17 @@
       <c r="L26" s="2">
         <v>0</v>
       </c>
+      <c r="M26" s="11"/>
       <c r="N26" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="27" s="2" customFormat="1" customHeight="1" spans="2:14">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B27" s="2">
         <v>10002009</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D27" s="2">
         <v>10000004</v>
@@ -2610,16 +2278,17 @@
       <c r="L27" s="2">
         <v>0</v>
       </c>
+      <c r="M27" s="11"/>
       <c r="N27" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="28" s="2" customFormat="1" customHeight="1" spans="2:14">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B28" s="2">
         <v>10002010</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D28" s="2">
         <v>10000005</v>
@@ -2649,16 +2318,17 @@
       <c r="L28" s="2">
         <v>0</v>
       </c>
+      <c r="M28" s="11"/>
       <c r="N28" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="29" s="2" customFormat="1" customHeight="1" spans="2:14">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="2">
         <v>10002011</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D29" s="2">
         <v>10000006</v>
@@ -2688,16 +2358,17 @@
       <c r="L29" s="2">
         <v>0</v>
       </c>
+      <c r="M29" s="11"/>
       <c r="N29" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="30" s="2" customFormat="1" customHeight="1" spans="2:14">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B30" s="2">
         <v>10003001</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D30" s="2">
         <v>10003001</v>
@@ -2727,16 +2398,17 @@
       <c r="L30" s="2">
         <v>12000001</v>
       </c>
+      <c r="M30" s="11"/>
       <c r="N30" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="31" s="2" customFormat="1" customHeight="1" spans="2:14">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B31" s="2">
         <v>10003002</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D31" s="2">
         <v>10003002</v>
@@ -2766,16 +2438,17 @@
       <c r="L31" s="2">
         <v>12000002</v>
       </c>
+      <c r="M31" s="11"/>
       <c r="N31" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="32" s="2" customFormat="1" customHeight="1" spans="2:14">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="32" spans="2:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B32" s="2">
         <v>10003003</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D32" s="2">
         <v>10003003</v>
@@ -2805,16 +2478,17 @@
       <c r="L32" s="2">
         <v>12000003</v>
       </c>
+      <c r="M32" s="11"/>
       <c r="N32" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="33" s="2" customFormat="1" customHeight="1" spans="2:14">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B33" s="2">
         <v>10003004</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D33" s="2">
         <v>10003004</v>
@@ -2844,16 +2518,17 @@
       <c r="L33" s="2">
         <v>12000004</v>
       </c>
+      <c r="M33" s="11"/>
       <c r="N33" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="34" s="2" customFormat="1" customHeight="1" spans="2:14">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B34" s="2">
         <v>10003005</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D34" s="2">
         <v>10003005</v>
@@ -2883,16 +2558,17 @@
       <c r="L34" s="2">
         <v>12000005</v>
       </c>
+      <c r="M34" s="11"/>
       <c r="N34" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="35" s="2" customFormat="1" customHeight="1" spans="2:14">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B35" s="2">
         <v>10003006</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D35" s="2">
         <v>10003006</v>
@@ -2922,16 +2598,17 @@
       <c r="L35" s="2">
         <v>12000006</v>
       </c>
+      <c r="M35" s="11"/>
       <c r="N35" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="36" s="2" customFormat="1" customHeight="1" spans="2:14">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="36" spans="2:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B36" s="2">
         <v>10003011</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D36" s="2">
         <v>10003001</v>
@@ -2961,13 +2638,14 @@
       <c r="L36" s="2">
         <v>12000011</v>
       </c>
+      <c r="M36" s="11"/>
       <c r="N36" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Unity/Assets/Config/Excel/ItemConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ItemConfig.xlsx
@@ -1,31 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\DreamGit\Unity\Assets\Config\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FE6E043-F3EE-46D5-8606-10D429CA15D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="D3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -47,7 +54,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="E3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -74,7 +81,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="G3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -99,7 +106,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="H3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -127,244 +134,16 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">当道具类型为1（消耗品）时字段的意义
-1 </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="微软雅黑"/>
-            <family val="2"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">  </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">获得金币值
-2 </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="微软雅黑"/>
-            <family val="2"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">  </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>获得经验值
-3</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="微软雅黑"/>
-            <family val="2"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="微软雅黑"/>
-            <family val="2"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">随机宝箱
-4 </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="微软雅黑"/>
-            <family val="2"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">  </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">自选宝箱
-5 </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="微软雅黑"/>
-            <family val="2"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">  </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">使用后永久增加属性
-6 </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="微软雅黑"/>
-            <family val="2"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">  </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">抽奖券
-7 </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="微软雅黑"/>
-            <family val="2"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">  </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>副本入场券
-8</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="微软雅黑"/>
-            <family val="2"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="微软雅黑"/>
-            <family val="2"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>英雄经验
-9</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="微软雅黑"/>
-            <family val="2"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">  </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve"> 英雄魂石
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="微软雅黑"/>
-            <family val="2"/>
-            <charset val="134"/>
-          </rPr>
-          <t>10 英雄碎片</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
+1   获得金币值
+2   获得经验值
+3   随机宝箱
+4   自选宝箱
+5   使用后永久增加属性
+6   抽奖券
+7   副本入场券
+8   英雄经验
+9   英雄魂石
+10 英雄碎片
 </t>
         </r>
         <r>
@@ -383,7 +162,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="I3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -405,7 +184,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="L3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -432,7 +211,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="91">
   <si>
     <t>##var</t>
   </si>
@@ -554,9 +333,15 @@
     <t>联盟贡献度可以在联盟商店中兑换商品</t>
   </si>
   <si>
+    <t>随机宝箱</t>
+  </si>
+  <si>
     <t>打开后从以下红色技能中随机获取一件</t>
   </si>
   <si>
+    <t>自选宝箱</t>
+  </si>
+  <si>
     <t>打开后从以下红色技能中自选一件</t>
   </si>
   <si>
@@ -599,6 +384,9 @@
     <t>英雄经验道具</t>
   </si>
   <si>
+    <t>100,200</t>
+  </si>
+  <si>
     <t>英雄增加100经验</t>
   </si>
   <si>
@@ -608,6 +396,15 @@
     <t>英雄增加100魂石</t>
   </si>
   <si>
+    <t>金币袋子</t>
+  </si>
+  <si>
+    <t>4000</t>
+  </si>
+  <si>
+    <t>打开后获得4000金币</t>
+  </si>
+  <si>
     <t>大熊猫碎片</t>
   </si>
   <si>
@@ -687,25 +484,19 @@
   </si>
   <si>
     <t>一个更吊的头盔</t>
-  </si>
-  <si>
-    <t>随机宝箱</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>自选宝箱</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>100,200</t>
-    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -733,10 +524,153 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -761,29 +695,8 @@
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -808,8 +721,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -860,12 +959,254 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -880,46 +1221,90 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 6" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 6" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1177,155 +1562,155 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N36"/>
-  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:N37"/>
+  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.875" style="3" customWidth="1"/>
     <col min="2" max="12" width="17.875" style="3"/>
-    <col min="13" max="13" width="20.5" style="10" customWidth="1"/>
+    <col min="13" max="13" width="20.5" style="4" customWidth="1"/>
     <col min="14" max="14" width="70.625" style="3" customWidth="1"/>
     <col min="15" max="16384" width="17.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="M2" s="8" t="s">
+      <c r="M2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="N2" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="6" t="s">
+      <c r="B3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="M3" s="9" t="s">
+      <c r="M3" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="N3" s="7" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" customHeight="1" spans="2:14">
       <c r="B4" s="3">
         <v>1</v>
       </c>
@@ -1363,7 +1748,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" customHeight="1" spans="2:14">
       <c r="B5" s="3">
         <v>2</v>
       </c>
@@ -1402,7 +1787,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" customHeight="1" spans="2:14">
       <c r="B6" s="3">
         <v>3</v>
       </c>
@@ -1441,7 +1826,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" customHeight="1" spans="2:14">
       <c r="B7" s="3">
         <v>4</v>
       </c>
@@ -1480,7 +1865,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" customHeight="1" spans="2:14">
       <c r="B8" s="3">
         <v>5</v>
       </c>
@@ -1519,12 +1904,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B9" s="2">
         <v>10001001</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>85</v>
+      <c r="C9" s="8" t="s">
+        <v>40</v>
       </c>
       <c r="D9" s="2">
         <v>10000001</v>
@@ -1556,15 +1941,15 @@
       </c>
       <c r="M9" s="11"/>
       <c r="N9" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" ht="19.5" customHeight="1" spans="2:14">
       <c r="B10" s="2">
         <v>10001002</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>86</v>
+      <c r="C10" s="8" t="s">
+        <v>42</v>
       </c>
       <c r="D10" s="2">
         <v>10000002</v>
@@ -1596,15 +1981,15 @@
       </c>
       <c r="M10" s="11"/>
       <c r="N10" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B11" s="2">
         <v>10001003</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D11" s="2">
         <v>10000003</v>
@@ -1636,15 +2021,15 @@
       </c>
       <c r="M11" s="11"/>
       <c r="N11" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B12" s="2">
         <v>10001004</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D12" s="2">
         <v>10000004</v>
@@ -1665,7 +2050,7 @@
         <v>1</v>
       </c>
       <c r="J12" s="3">
-        <f t="shared" ref="J12:J16" si="1">J11+100</f>
+        <f t="shared" ref="J12:J19" si="1">J11+100</f>
         <v>900</v>
       </c>
       <c r="K12" s="2">
@@ -1676,15 +2061,15 @@
       </c>
       <c r="M12" s="11"/>
       <c r="N12" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B13" s="2">
         <v>10001005</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D13" s="2">
         <v>10000005</v>
@@ -1716,15 +2101,15 @@
       </c>
       <c r="M13" s="11"/>
       <c r="N13" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B14" s="2">
         <v>10001006</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D14" s="2">
         <v>10000006</v>
@@ -1756,15 +2141,15 @@
       </c>
       <c r="M14" s="11"/>
       <c r="N14" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B15" s="2">
         <v>10001007</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D15" s="2">
         <v>10000007</v>
@@ -1796,15 +2181,15 @@
       </c>
       <c r="M15" s="11"/>
       <c r="N15" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B16" s="2">
         <v>10001008</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D16" s="2">
         <v>10000008</v>
@@ -1836,15 +2221,15 @@
       </c>
       <c r="M16" s="11"/>
       <c r="N16" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17" spans="2:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B17" s="2">
         <v>10001009</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D17" s="2">
         <v>10000009</v>
@@ -1865,7 +2250,7 @@
         <v>1</v>
       </c>
       <c r="J17" s="3">
-        <f>J16+100</f>
+        <f t="shared" si="1"/>
         <v>1400</v>
       </c>
       <c r="K17" s="2">
@@ -1875,18 +2260,18 @@
         <v>0</v>
       </c>
       <c r="M17" s="12" t="s">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18" spans="2:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B18" s="2">
         <v>10001010</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D18" s="2">
         <v>10000009</v>
@@ -1907,7 +2292,7 @@
         <v>1</v>
       </c>
       <c r="J18" s="3">
-        <f>J17+100</f>
+        <f t="shared" si="1"/>
         <v>1500</v>
       </c>
       <c r="K18" s="2">
@@ -1917,33 +2302,33 @@
         <v>0</v>
       </c>
       <c r="M18" s="12" t="s">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="19" spans="2:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B19" s="2">
-        <v>10002001</v>
+        <v>10001011</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D19" s="2">
         <v>10000009</v>
       </c>
       <c r="E19" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F19" s="3">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G19" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" s="2">
         <v>1</v>
@@ -1953,31 +2338,33 @@
         <v>1600</v>
       </c>
       <c r="K19" s="2">
-        <v>999</v>
+        <v>99</v>
       </c>
       <c r="L19" s="2">
         <v>0</v>
       </c>
-      <c r="M19" s="11"/>
+      <c r="M19" s="12" t="s">
+        <v>62</v>
+      </c>
       <c r="N19" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="20" spans="2:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B20" s="2">
-        <v>10002002</v>
+        <v>10002001</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D20" s="2">
-        <v>10000010</v>
+        <v>10000009</v>
       </c>
       <c r="E20" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F20" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G20" s="2">
         <v>2</v>
@@ -1989,7 +2376,7 @@
         <v>1</v>
       </c>
       <c r="J20" s="3">
-        <f t="shared" ref="J20:J36" si="2">J19+100</f>
+        <f>J19+100</f>
         <v>1700</v>
       </c>
       <c r="K20" s="2">
@@ -2000,24 +2387,24 @@
       </c>
       <c r="M20" s="11"/>
       <c r="N20" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="21" spans="2:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B21" s="2">
-        <v>10002003</v>
+        <v>10002002</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D21" s="2">
-        <v>10000011</v>
+        <v>10000010</v>
       </c>
       <c r="E21" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F21" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G21" s="2">
         <v>2</v>
@@ -2029,7 +2416,7 @@
         <v>1</v>
       </c>
       <c r="J21" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="J21:J37" si="2">J20+100</f>
         <v>1800</v>
       </c>
       <c r="K21" s="2">
@@ -2040,24 +2427,24 @@
       </c>
       <c r="M21" s="11"/>
       <c r="N21" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="22" spans="2:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B22" s="2">
-        <v>10002004</v>
+        <v>10002003</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D22" s="2">
-        <v>10000012</v>
+        <v>10000011</v>
       </c>
       <c r="E22" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F22" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G22" s="2">
         <v>2</v>
@@ -2080,24 +2467,24 @@
       </c>
       <c r="M22" s="11"/>
       <c r="N22" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="23" spans="2:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B23" s="2">
-        <v>10002005</v>
+        <v>10002004</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D23" s="2">
-        <v>10000013</v>
+        <v>10000012</v>
       </c>
       <c r="E23" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F23" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G23" s="2">
         <v>2</v>
@@ -2120,24 +2507,24 @@
       </c>
       <c r="M23" s="11"/>
       <c r="N23" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="24" spans="2:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B24" s="2">
-        <v>10002006</v>
+        <v>10002005</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D24" s="2">
-        <v>10000001</v>
+        <v>10000013</v>
       </c>
       <c r="E24" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F24" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G24" s="2">
         <v>2</v>
@@ -2160,24 +2547,24 @@
       </c>
       <c r="M24" s="11"/>
       <c r="N24" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="25" spans="2:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B25" s="2">
-        <v>10002007</v>
+        <v>10002006</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D25" s="2">
-        <v>10000002</v>
+        <v>10000001</v>
       </c>
       <c r="E25" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G25" s="2">
         <v>2</v>
@@ -2200,24 +2587,24 @@
       </c>
       <c r="M25" s="11"/>
       <c r="N25" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="26" spans="2:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B26" s="2">
-        <v>10002008</v>
+        <v>10002007</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D26" s="2">
-        <v>10000003</v>
+        <v>10000002</v>
       </c>
       <c r="E26" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F26" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G26" s="2">
         <v>2</v>
@@ -2240,24 +2627,24 @@
       </c>
       <c r="M26" s="11"/>
       <c r="N26" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="27" spans="2:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B27" s="2">
-        <v>10002009</v>
+        <v>10002008</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D27" s="2">
-        <v>10000004</v>
+        <v>10000003</v>
       </c>
       <c r="E27" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F27" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G27" s="2">
         <v>2</v>
@@ -2280,24 +2667,24 @@
       </c>
       <c r="M27" s="11"/>
       <c r="N27" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="28" spans="2:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B28" s="2">
-        <v>10002010</v>
+        <v>10002009</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D28" s="2">
-        <v>10000005</v>
+        <v>10000004</v>
       </c>
       <c r="E28" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F28" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G28" s="2">
         <v>2</v>
@@ -2320,24 +2707,24 @@
       </c>
       <c r="M28" s="11"/>
       <c r="N28" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="29" spans="2:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B29" s="2">
-        <v>10002011</v>
+        <v>10002010</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D29" s="2">
-        <v>10000006</v>
+        <v>10000005</v>
       </c>
       <c r="E29" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F29" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G29" s="2">
         <v>2</v>
@@ -2360,30 +2747,30 @@
       </c>
       <c r="M29" s="11"/>
       <c r="N29" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="30" spans="2:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B30" s="2">
-        <v>10003001</v>
+        <v>10002011</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D30" s="2">
-        <v>10003001</v>
+        <v>10000006</v>
       </c>
       <c r="E30" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F30" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G30" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H30" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" s="2">
         <v>1</v>
@@ -2393,37 +2780,37 @@
         <v>2700</v>
       </c>
       <c r="K30" s="2">
-        <v>1</v>
+        <v>999</v>
       </c>
       <c r="L30" s="2">
-        <v>12000001</v>
+        <v>0</v>
       </c>
       <c r="M30" s="11"/>
       <c r="N30" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="31" spans="2:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B31" s="2">
-        <v>10003002</v>
+        <v>10003001</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D31" s="2">
-        <v>10003002</v>
+        <v>10003001</v>
       </c>
       <c r="E31" s="2">
         <v>3</v>
       </c>
       <c r="F31" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G31" s="2">
         <v>3</v>
       </c>
       <c r="H31" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I31" s="2">
         <v>1</v>
@@ -2436,34 +2823,34 @@
         <v>1</v>
       </c>
       <c r="L31" s="2">
-        <v>12000002</v>
+        <v>12000001</v>
       </c>
       <c r="M31" s="11"/>
       <c r="N31" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="32" spans="2:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B32" s="2">
-        <v>10003003</v>
+        <v>10003002</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D32" s="2">
-        <v>10003003</v>
+        <v>10003002</v>
       </c>
       <c r="E32" s="2">
         <v>3</v>
       </c>
       <c r="F32" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G32" s="2">
         <v>3</v>
       </c>
       <c r="H32" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I32" s="2">
         <v>1</v>
@@ -2476,34 +2863,34 @@
         <v>1</v>
       </c>
       <c r="L32" s="2">
-        <v>12000003</v>
+        <v>12000002</v>
       </c>
       <c r="M32" s="11"/>
       <c r="N32" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="33" spans="2:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B33" s="2">
-        <v>10003004</v>
+        <v>10003003</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D33" s="2">
-        <v>10003004</v>
+        <v>10003003</v>
       </c>
       <c r="E33" s="2">
         <v>3</v>
       </c>
       <c r="F33" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G33" s="2">
         <v>3</v>
       </c>
       <c r="H33" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I33" s="2">
         <v>1</v>
@@ -2516,34 +2903,34 @@
         <v>1</v>
       </c>
       <c r="L33" s="2">
-        <v>12000004</v>
+        <v>12000003</v>
       </c>
       <c r="M33" s="11"/>
       <c r="N33" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="34" spans="2:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B34" s="2">
-        <v>10003005</v>
+        <v>10003004</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D34" s="2">
-        <v>10003005</v>
+        <v>10003004</v>
       </c>
       <c r="E34" s="2">
         <v>3</v>
       </c>
       <c r="F34" s="3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G34" s="2">
         <v>3</v>
       </c>
       <c r="H34" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I34" s="2">
         <v>1</v>
@@ -2556,34 +2943,34 @@
         <v>1</v>
       </c>
       <c r="L34" s="2">
-        <v>12000005</v>
+        <v>12000004</v>
       </c>
       <c r="M34" s="11"/>
       <c r="N34" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="35" spans="2:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B35" s="2">
-        <v>10003006</v>
+        <v>10003005</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D35" s="2">
-        <v>10003006</v>
+        <v>10003005</v>
       </c>
       <c r="E35" s="2">
         <v>3</v>
       </c>
       <c r="F35" s="3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G35" s="2">
         <v>3</v>
       </c>
       <c r="H35" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I35" s="2">
         <v>1</v>
@@ -2596,34 +2983,34 @@
         <v>1</v>
       </c>
       <c r="L35" s="2">
-        <v>12000006</v>
+        <v>12000005</v>
       </c>
       <c r="M35" s="11"/>
       <c r="N35" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="36" spans="2:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B36" s="2">
-        <v>10003011</v>
+        <v>10003006</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D36" s="2">
-        <v>10003001</v>
+        <v>10003006</v>
       </c>
       <c r="E36" s="2">
         <v>3</v>
       </c>
       <c r="F36" s="3">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G36" s="2">
         <v>3</v>
       </c>
       <c r="H36" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I36" s="2">
         <v>1</v>
@@ -2636,16 +3023,56 @@
         <v>1</v>
       </c>
       <c r="L36" s="2">
-        <v>12000011</v>
+        <v>12000006</v>
       </c>
       <c r="M36" s="11"/>
       <c r="N36" s="2" t="s">
-        <v>73</v>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="37" s="2" customFormat="1" customHeight="1" spans="2:14">
+      <c r="B37" s="2">
+        <v>10003011</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D37" s="2">
+        <v>10003001</v>
+      </c>
+      <c r="E37" s="2">
+        <v>3</v>
+      </c>
+      <c r="F37" s="3">
+        <v>25</v>
+      </c>
+      <c r="G37" s="2">
+        <v>3</v>
+      </c>
+      <c r="H37" s="2">
+        <v>1</v>
+      </c>
+      <c r="I37" s="2">
+        <v>1</v>
+      </c>
+      <c r="J37" s="3">
+        <f t="shared" si="2"/>
+        <v>3400</v>
+      </c>
+      <c r="K37" s="2">
+        <v>1</v>
+      </c>
+      <c r="L37" s="2">
+        <v>12000011</v>
+      </c>
+      <c r="M37" s="11"/>
+      <c r="N37" s="2" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Unity/Assets/Config/Excel/ItemConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ItemConfig.xlsx
@@ -496,7 +496,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -520,12 +520,6 @@
     <font>
       <sz val="10"/>
       <color theme="0"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1077,138 +1071,138 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1233,9 +1227,6 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="4" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1243,9 +1234,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1615,7 +1603,7 @@
       <c r="L1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="8" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="6" t="s">
@@ -1659,7 +1647,7 @@
       <c r="L2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="M2" s="9" t="s">
+      <c r="M2" s="8" t="s">
         <v>16</v>
       </c>
       <c r="N2" s="6" t="s">
@@ -1703,7 +1691,7 @@
       <c r="L3" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="M3" s="10" t="s">
+      <c r="M3" s="9" t="s">
         <v>28</v>
       </c>
       <c r="N3" s="7" t="s">
@@ -1908,7 +1896,7 @@
       <c r="B9" s="2">
         <v>10001001</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="2" t="s">
         <v>40</v>
       </c>
       <c r="D9" s="2">
@@ -1939,7 +1927,7 @@
       <c r="L9" s="2">
         <v>0</v>
       </c>
-      <c r="M9" s="11"/>
+      <c r="M9" s="10"/>
       <c r="N9" s="2" t="s">
         <v>41</v>
       </c>
@@ -1948,7 +1936,7 @@
       <c r="B10" s="2">
         <v>10001002</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="2" t="s">
         <v>42</v>
       </c>
       <c r="D10" s="2">
@@ -1979,7 +1967,7 @@
       <c r="L10" s="2">
         <v>0</v>
       </c>
-      <c r="M10" s="11"/>
+      <c r="M10" s="10"/>
       <c r="N10" s="2" t="s">
         <v>43</v>
       </c>
@@ -2019,7 +2007,7 @@
       <c r="L11" s="2">
         <v>0</v>
       </c>
-      <c r="M11" s="11"/>
+      <c r="M11" s="10"/>
       <c r="N11" s="2" t="s">
         <v>45</v>
       </c>
@@ -2050,7 +2038,7 @@
         <v>1</v>
       </c>
       <c r="J12" s="3">
-        <f t="shared" ref="J12:J19" si="1">J11+100</f>
+        <f t="shared" ref="J12:J20" si="1">J11+100</f>
         <v>900</v>
       </c>
       <c r="K12" s="2">
@@ -2059,7 +2047,7 @@
       <c r="L12" s="2">
         <v>0</v>
       </c>
-      <c r="M12" s="11"/>
+      <c r="M12" s="10"/>
       <c r="N12" s="2" t="s">
         <v>47</v>
       </c>
@@ -2099,7 +2087,7 @@
       <c r="L13" s="2">
         <v>0</v>
       </c>
-      <c r="M13" s="11"/>
+      <c r="M13" s="10"/>
       <c r="N13" s="2" t="s">
         <v>49</v>
       </c>
@@ -2139,7 +2127,7 @@
       <c r="L14" s="2">
         <v>0</v>
       </c>
-      <c r="M14" s="11"/>
+      <c r="M14" s="10"/>
       <c r="N14" s="2" t="s">
         <v>51</v>
       </c>
@@ -2179,7 +2167,7 @@
       <c r="L15" s="2">
         <v>0</v>
       </c>
-      <c r="M15" s="11"/>
+      <c r="M15" s="10"/>
       <c r="N15" s="2" t="s">
         <v>53</v>
       </c>
@@ -2219,7 +2207,7 @@
       <c r="L16" s="2">
         <v>0</v>
       </c>
-      <c r="M16" s="11"/>
+      <c r="M16" s="10"/>
       <c r="N16" s="2" t="s">
         <v>55</v>
       </c>
@@ -2259,7 +2247,7 @@
       <c r="L17" s="2">
         <v>0</v>
       </c>
-      <c r="M17" s="12" t="s">
+      <c r="M17" s="10" t="s">
         <v>57</v>
       </c>
       <c r="N17" s="2" t="s">
@@ -2301,7 +2289,7 @@
       <c r="L18" s="2">
         <v>0</v>
       </c>
-      <c r="M18" s="12" t="s">
+      <c r="M18" s="10" t="s">
         <v>57</v>
       </c>
       <c r="N18" s="2" t="s">
@@ -2334,7 +2322,7 @@
         <v>1</v>
       </c>
       <c r="J19" s="3">
-        <f>J18+100</f>
+        <f t="shared" si="1"/>
         <v>1600</v>
       </c>
       <c r="K19" s="2">
@@ -2343,7 +2331,7 @@
       <c r="L19" s="2">
         <v>0</v>
       </c>
-      <c r="M19" s="12" t="s">
+      <c r="M19" s="10" t="s">
         <v>62</v>
       </c>
       <c r="N19" s="2" t="s">
@@ -2376,7 +2364,7 @@
         <v>1</v>
       </c>
       <c r="J20" s="3">
-        <f>J19+100</f>
+        <f t="shared" si="1"/>
         <v>1700</v>
       </c>
       <c r="K20" s="2">
@@ -2385,7 +2373,7 @@
       <c r="L20" s="2">
         <v>0</v>
       </c>
-      <c r="M20" s="11"/>
+      <c r="M20" s="10"/>
       <c r="N20" s="2" t="s">
         <v>65</v>
       </c>
@@ -2425,7 +2413,7 @@
       <c r="L21" s="2">
         <v>0</v>
       </c>
-      <c r="M21" s="11"/>
+      <c r="M21" s="10"/>
       <c r="N21" s="2" t="s">
         <v>65</v>
       </c>
@@ -2465,7 +2453,7 @@
       <c r="L22" s="2">
         <v>0</v>
       </c>
-      <c r="M22" s="11"/>
+      <c r="M22" s="10"/>
       <c r="N22" s="2" t="s">
         <v>65</v>
       </c>
@@ -2505,7 +2493,7 @@
       <c r="L23" s="2">
         <v>0</v>
       </c>
-      <c r="M23" s="11"/>
+      <c r="M23" s="10"/>
       <c r="N23" s="2" t="s">
         <v>65</v>
       </c>
@@ -2545,7 +2533,7 @@
       <c r="L24" s="2">
         <v>0</v>
       </c>
-      <c r="M24" s="11"/>
+      <c r="M24" s="10"/>
       <c r="N24" s="2" t="s">
         <v>65</v>
       </c>
@@ -2585,7 +2573,7 @@
       <c r="L25" s="2">
         <v>0</v>
       </c>
-      <c r="M25" s="11"/>
+      <c r="M25" s="10"/>
       <c r="N25" s="2" t="s">
         <v>67</v>
       </c>
@@ -2625,7 +2613,7 @@
       <c r="L26" s="2">
         <v>0</v>
       </c>
-      <c r="M26" s="11"/>
+      <c r="M26" s="10"/>
       <c r="N26" s="2" t="s">
         <v>69</v>
       </c>
@@ -2665,7 +2653,7 @@
       <c r="L27" s="2">
         <v>0</v>
       </c>
-      <c r="M27" s="11"/>
+      <c r="M27" s="10"/>
       <c r="N27" s="2" t="s">
         <v>71</v>
       </c>
@@ -2705,7 +2693,7 @@
       <c r="L28" s="2">
         <v>0</v>
       </c>
-      <c r="M28" s="11"/>
+      <c r="M28" s="10"/>
       <c r="N28" s="2" t="s">
         <v>73</v>
       </c>
@@ -2745,7 +2733,7 @@
       <c r="L29" s="2">
         <v>0</v>
       </c>
-      <c r="M29" s="11"/>
+      <c r="M29" s="10"/>
       <c r="N29" s="2" t="s">
         <v>75</v>
       </c>
@@ -2785,7 +2773,7 @@
       <c r="L30" s="2">
         <v>0</v>
       </c>
-      <c r="M30" s="11"/>
+      <c r="M30" s="10"/>
       <c r="N30" s="2" t="s">
         <v>77</v>
       </c>
@@ -2801,7 +2789,7 @@
         <v>10003001</v>
       </c>
       <c r="E31" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F31" s="3">
         <v>25</v>
@@ -2825,7 +2813,7 @@
       <c r="L31" s="2">
         <v>12000001</v>
       </c>
-      <c r="M31" s="11"/>
+      <c r="M31" s="10"/>
       <c r="N31" s="2" t="s">
         <v>79</v>
       </c>
@@ -2841,7 +2829,7 @@
         <v>10003002</v>
       </c>
       <c r="E32" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F32" s="3">
         <v>26</v>
@@ -2865,7 +2853,7 @@
       <c r="L32" s="2">
         <v>12000002</v>
       </c>
-      <c r="M32" s="11"/>
+      <c r="M32" s="10"/>
       <c r="N32" s="2" t="s">
         <v>81</v>
       </c>
@@ -2905,7 +2893,7 @@
       <c r="L33" s="2">
         <v>12000003</v>
       </c>
-      <c r="M33" s="11"/>
+      <c r="M33" s="10"/>
       <c r="N33" s="2" t="s">
         <v>83</v>
       </c>
@@ -2921,7 +2909,7 @@
         <v>10003004</v>
       </c>
       <c r="E34" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F34" s="3">
         <v>28</v>
@@ -2945,7 +2933,7 @@
       <c r="L34" s="2">
         <v>12000004</v>
       </c>
-      <c r="M34" s="11"/>
+      <c r="M34" s="10"/>
       <c r="N34" s="2" t="s">
         <v>85</v>
       </c>
@@ -2961,7 +2949,7 @@
         <v>10003005</v>
       </c>
       <c r="E35" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F35" s="3">
         <v>29</v>
@@ -2985,7 +2973,7 @@
       <c r="L35" s="2">
         <v>12000005</v>
       </c>
-      <c r="M35" s="11"/>
+      <c r="M35" s="10"/>
       <c r="N35" s="2" t="s">
         <v>87</v>
       </c>
@@ -3001,7 +2989,7 @@
         <v>10003006</v>
       </c>
       <c r="E36" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F36" s="3">
         <v>30</v>
@@ -3025,7 +3013,7 @@
       <c r="L36" s="2">
         <v>12000006</v>
       </c>
-      <c r="M36" s="11"/>
+      <c r="M36" s="10"/>
       <c r="N36" s="2" t="s">
         <v>89</v>
       </c>
@@ -3065,7 +3053,7 @@
       <c r="L37" s="2">
         <v>12000011</v>
       </c>
-      <c r="M37" s="11"/>
+      <c r="M37" s="10"/>
       <c r="N37" s="2" t="s">
         <v>79</v>
       </c>

--- a/Unity/Assets/Config/Excel/ItemConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ItemConfig.xlsx
@@ -72,11 +72,11 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-1.白
-2.绿
-3.蓝
-4.紫
-5.橙
+1.绿
+2.蓝
+3.黄
+4.橙
+5.紫
 6.红</t>
         </r>
       </text>
@@ -211,7 +211,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="93">
   <si>
     <t>##var</t>
   </si>
@@ -336,10 +336,16 @@
     <t>随机宝箱</t>
   </si>
   <si>
+    <t>10003001,10003002,10003003</t>
+  </si>
+  <si>
     <t>打开后从以下红色技能中随机获取一件</t>
   </si>
   <si>
     <t>自选宝箱</t>
+  </si>
+  <si>
+    <t>10003004,10003005,10003006</t>
   </si>
   <si>
     <t>打开后从以下红色技能中自选一件</t>
@@ -675,16 +681,16 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -1927,9 +1933,11 @@
       <c r="L9" s="2">
         <v>0</v>
       </c>
-      <c r="M9" s="10"/>
+      <c r="M9" s="10" t="s">
+        <v>41</v>
+      </c>
       <c r="N9" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" ht="19.5" customHeight="1" spans="2:14">
@@ -1937,7 +1945,7 @@
         <v>10001002</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D10" s="2">
         <v>10000002</v>
@@ -1967,9 +1975,11 @@
       <c r="L10" s="2">
         <v>0</v>
       </c>
-      <c r="M10" s="10"/>
+      <c r="M10" s="10" t="s">
+        <v>44</v>
+      </c>
       <c r="N10" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="2:14">
@@ -1977,7 +1987,7 @@
         <v>10001003</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D11" s="2">
         <v>10000003</v>
@@ -2009,7 +2019,7 @@
       </c>
       <c r="M11" s="10"/>
       <c r="N11" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="2:14">
@@ -2017,7 +2027,7 @@
         <v>10001004</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D12" s="2">
         <v>10000004</v>
@@ -2049,7 +2059,7 @@
       </c>
       <c r="M12" s="10"/>
       <c r="N12" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="2:14">
@@ -2057,7 +2067,7 @@
         <v>10001005</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D13" s="2">
         <v>10000005</v>
@@ -2089,7 +2099,7 @@
       </c>
       <c r="M13" s="10"/>
       <c r="N13" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" customHeight="1" spans="2:14">
@@ -2097,7 +2107,7 @@
         <v>10001006</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D14" s="2">
         <v>10000006</v>
@@ -2129,7 +2139,7 @@
       </c>
       <c r="M14" s="10"/>
       <c r="N14" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="2:14">
@@ -2137,7 +2147,7 @@
         <v>10001007</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D15" s="2">
         <v>10000007</v>
@@ -2169,7 +2179,7 @@
       </c>
       <c r="M15" s="10"/>
       <c r="N15" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="2:14">
@@ -2177,7 +2187,7 @@
         <v>10001008</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D16" s="2">
         <v>10000008</v>
@@ -2209,7 +2219,7 @@
       </c>
       <c r="M16" s="10"/>
       <c r="N16" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="2:14">
@@ -2217,7 +2227,7 @@
         <v>10001009</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D17" s="2">
         <v>10000009</v>
@@ -2248,10 +2258,10 @@
         <v>0</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="2:14">
@@ -2259,7 +2269,7 @@
         <v>10001010</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D18" s="2">
         <v>10000009</v>
@@ -2290,10 +2300,10 @@
         <v>0</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="2:14">
@@ -2301,7 +2311,7 @@
         <v>10001011</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D19" s="2">
         <v>10000009</v>
@@ -2332,10 +2342,10 @@
         <v>0</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="2:14">
@@ -2343,7 +2353,7 @@
         <v>10002001</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D20" s="2">
         <v>10000009</v>
@@ -2375,7 +2385,7 @@
       </c>
       <c r="M20" s="10"/>
       <c r="N20" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="2:14">
@@ -2383,7 +2393,7 @@
         <v>10002002</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D21" s="2">
         <v>10000010</v>
@@ -2415,7 +2425,7 @@
       </c>
       <c r="M21" s="10"/>
       <c r="N21" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="2:14">
@@ -2423,7 +2433,7 @@
         <v>10002003</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D22" s="2">
         <v>10000011</v>
@@ -2455,7 +2465,7 @@
       </c>
       <c r="M22" s="10"/>
       <c r="N22" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="2:14">
@@ -2463,7 +2473,7 @@
         <v>10002004</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D23" s="2">
         <v>10000012</v>
@@ -2495,7 +2505,7 @@
       </c>
       <c r="M23" s="10"/>
       <c r="N23" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="2:14">
@@ -2503,7 +2513,7 @@
         <v>10002005</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D24" s="2">
         <v>10000013</v>
@@ -2535,7 +2545,7 @@
       </c>
       <c r="M24" s="10"/>
       <c r="N24" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" customHeight="1" spans="2:14">
@@ -2543,7 +2553,7 @@
         <v>10002006</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D25" s="2">
         <v>10000001</v>
@@ -2575,7 +2585,7 @@
       </c>
       <c r="M25" s="10"/>
       <c r="N25" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" customHeight="1" spans="2:14">
@@ -2583,7 +2593,7 @@
         <v>10002007</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D26" s="2">
         <v>10000002</v>
@@ -2615,7 +2625,7 @@
       </c>
       <c r="M26" s="10"/>
       <c r="N26" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" customHeight="1" spans="2:14">
@@ -2623,7 +2633,7 @@
         <v>10002008</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D27" s="2">
         <v>10000003</v>
@@ -2655,7 +2665,7 @@
       </c>
       <c r="M27" s="10"/>
       <c r="N27" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" customHeight="1" spans="2:14">
@@ -2663,7 +2673,7 @@
         <v>10002009</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D28" s="2">
         <v>10000004</v>
@@ -2695,7 +2705,7 @@
       </c>
       <c r="M28" s="10"/>
       <c r="N28" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" s="2" customFormat="1" customHeight="1" spans="2:14">
@@ -2703,7 +2713,7 @@
         <v>10002010</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D29" s="2">
         <v>10000005</v>
@@ -2735,7 +2745,7 @@
       </c>
       <c r="M29" s="10"/>
       <c r="N29" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" s="2" customFormat="1" customHeight="1" spans="2:14">
@@ -2743,7 +2753,7 @@
         <v>10002011</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D30" s="2">
         <v>10000006</v>
@@ -2775,7 +2785,7 @@
       </c>
       <c r="M30" s="10"/>
       <c r="N30" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" s="2" customFormat="1" customHeight="1" spans="2:14">
@@ -2783,7 +2793,7 @@
         <v>10003001</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D31" s="2">
         <v>10003001</v>
@@ -2815,7 +2825,7 @@
       </c>
       <c r="M31" s="10"/>
       <c r="N31" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" s="2" customFormat="1" customHeight="1" spans="2:14">
@@ -2823,7 +2833,7 @@
         <v>10003002</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D32" s="2">
         <v>10003002</v>
@@ -2855,7 +2865,7 @@
       </c>
       <c r="M32" s="10"/>
       <c r="N32" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="2:14">
@@ -2863,7 +2873,7 @@
         <v>10003003</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D33" s="2">
         <v>10003003</v>
@@ -2895,7 +2905,7 @@
       </c>
       <c r="M33" s="10"/>
       <c r="N33" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="34" s="2" customFormat="1" customHeight="1" spans="2:14">
@@ -2903,7 +2913,7 @@
         <v>10003004</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D34" s="2">
         <v>10003004</v>
@@ -2935,7 +2945,7 @@
       </c>
       <c r="M34" s="10"/>
       <c r="N34" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="2:14">
@@ -2943,7 +2953,7 @@
         <v>10003005</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D35" s="2">
         <v>10003005</v>
@@ -2975,7 +2985,7 @@
       </c>
       <c r="M35" s="10"/>
       <c r="N35" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="2:14">
@@ -2983,7 +2993,7 @@
         <v>10003006</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D36" s="2">
         <v>10003006</v>
@@ -3015,7 +3025,7 @@
       </c>
       <c r="M36" s="10"/>
       <c r="N36" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="2:14">
@@ -3023,7 +3033,7 @@
         <v>10003011</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D37" s="2">
         <v>10003001</v>
@@ -3055,7 +3065,7 @@
       </c>
       <c r="M37" s="10"/>
       <c r="N37" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/ItemConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ItemConfig.xlsx
@@ -133,8 +133,7 @@
             <rFont val="微软雅黑"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">当道具类型为1（消耗品）时字段的意义
-1   获得金币值
+          <t xml:space="preserve">1   获得金币值
 2   获得经验值
 3   随机宝箱
 4   自选宝箱
@@ -211,7 +210,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="90">
   <si>
     <t>##var</t>
   </si>
@@ -387,6 +386,57 @@
     <t>消耗入场券进入副本</t>
   </si>
   <si>
+    <t>金币袋子</t>
+  </si>
+  <si>
+    <t>4000</t>
+  </si>
+  <si>
+    <t>打开后获得4000金币</t>
+  </si>
+  <si>
+    <t>大熊猫碎片</t>
+  </si>
+  <si>
+    <t>英雄碎片，合成英雄</t>
+  </si>
+  <si>
+    <t>材料1</t>
+  </si>
+  <si>
+    <t>一种材料1</t>
+  </si>
+  <si>
+    <t>材料2</t>
+  </si>
+  <si>
+    <t>一种材料2</t>
+  </si>
+  <si>
+    <t>材料3</t>
+  </si>
+  <si>
+    <t>一种材料3</t>
+  </si>
+  <si>
+    <t>材料4</t>
+  </si>
+  <si>
+    <t>一种材料4</t>
+  </si>
+  <si>
+    <t>材料5</t>
+  </si>
+  <si>
+    <t>一种材料5</t>
+  </si>
+  <si>
+    <t>材料6</t>
+  </si>
+  <si>
+    <t>一种材料6</t>
+  </si>
+  <si>
     <t>英雄经验道具</t>
   </si>
   <si>
@@ -402,94 +452,34 @@
     <t>英雄增加100魂石</t>
   </si>
   <si>
-    <t>金币袋子</t>
-  </si>
-  <si>
-    <t>4000</t>
-  </si>
-  <si>
-    <t>打开后获得4000金币</t>
-  </si>
-  <si>
-    <t>大熊猫碎片</t>
-  </si>
-  <si>
-    <t>英雄碎片，合成英雄</t>
-  </si>
-  <si>
-    <t>材料1</t>
-  </si>
-  <si>
-    <t>一种材料1</t>
-  </si>
-  <si>
-    <t>材料2</t>
-  </si>
-  <si>
-    <t>一种材料2</t>
-  </si>
-  <si>
-    <t>材料3</t>
-  </si>
-  <si>
-    <t>一种材料3</t>
-  </si>
-  <si>
-    <t>材料4</t>
-  </si>
-  <si>
-    <t>一种材料4</t>
-  </si>
-  <si>
-    <t>材料5</t>
-  </si>
-  <si>
-    <t>一种材料5</t>
-  </si>
-  <si>
-    <t>材料6</t>
-  </si>
-  <si>
-    <t>一种材料6</t>
-  </si>
-  <si>
-    <t>一个头盔</t>
+    <t>一个裤子</t>
+  </si>
+  <si>
+    <t>这是一个装备3</t>
+  </si>
+  <si>
+    <t>一个鞋子</t>
+  </si>
+  <si>
+    <t>这是一个装备4</t>
+  </si>
+  <si>
+    <t>一个项链</t>
+  </si>
+  <si>
+    <t>这是一个装备5</t>
+  </si>
+  <si>
+    <t>一个武器</t>
+  </si>
+  <si>
+    <t>这是一个装备6</t>
+  </si>
+  <si>
+    <t>一个更吊的头盔</t>
   </si>
   <si>
     <t>这是一个装备1</t>
-  </si>
-  <si>
-    <t>一个衣服</t>
-  </si>
-  <si>
-    <t>这是一个装备2</t>
-  </si>
-  <si>
-    <t>一个裤子</t>
-  </si>
-  <si>
-    <t>这是一个装备3</t>
-  </si>
-  <si>
-    <t>一个鞋子</t>
-  </si>
-  <si>
-    <t>这是一个装备4</t>
-  </si>
-  <si>
-    <t>一个项链</t>
-  </si>
-  <si>
-    <t>这是一个装备5</t>
-  </si>
-  <si>
-    <t>一个武器</t>
-  </si>
-  <si>
-    <t>这是一个装备6</t>
-  </si>
-  <si>
-    <t>一个更吊的头盔</t>
   </si>
 </sst>
 </file>
@@ -676,12 +666,13 @@
     <font>
       <b/>
       <sz val="9"/>
-      <name val="宋体"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
-      <name val="微软雅黑"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -690,7 +681,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -1562,7 +1552,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.875" style="3" customWidth="1"/>
@@ -2048,7 +2038,7 @@
         <v>1</v>
       </c>
       <c r="J12" s="3">
-        <f t="shared" ref="J12:J20" si="1">J11+100</f>
+        <f>J11+100</f>
         <v>900</v>
       </c>
       <c r="K12" s="2">
@@ -2088,7 +2078,7 @@
         <v>1</v>
       </c>
       <c r="J13" s="3">
-        <f t="shared" si="1"/>
+        <f>J12+100</f>
         <v>1000</v>
       </c>
       <c r="K13" s="2">
@@ -2128,7 +2118,7 @@
         <v>1</v>
       </c>
       <c r="J14" s="3">
-        <f t="shared" si="1"/>
+        <f>J13+100</f>
         <v>1100</v>
       </c>
       <c r="K14" s="2">
@@ -2168,7 +2158,7 @@
         <v>1</v>
       </c>
       <c r="J15" s="3">
-        <f t="shared" si="1"/>
+        <f>J14+100</f>
         <v>1200</v>
       </c>
       <c r="K15" s="2">
@@ -2208,7 +2198,7 @@
         <v>1</v>
       </c>
       <c r="J16" s="3">
-        <f t="shared" si="1"/>
+        <f>J15+100</f>
         <v>1300</v>
       </c>
       <c r="K16" s="2">
@@ -2224,7 +2214,7 @@
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B17" s="2">
-        <v>10001009</v>
+        <v>10001011</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>58</v>
@@ -2233,7 +2223,7 @@
         <v>10000009</v>
       </c>
       <c r="E17" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F17" s="3">
         <v>1</v>
@@ -2242,14 +2232,14 @@
         <v>1</v>
       </c>
       <c r="H17" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I17" s="2">
         <v>1</v>
       </c>
       <c r="J17" s="3">
-        <f t="shared" si="1"/>
-        <v>1400</v>
+        <f>J30+100</f>
+        <v>1600</v>
       </c>
       <c r="K17" s="2">
         <v>99</v>
@@ -2266,7 +2256,7 @@
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B18" s="2">
-        <v>10001010</v>
+        <v>10002001</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>61</v>
@@ -2275,94 +2265,90 @@
         <v>10000009</v>
       </c>
       <c r="E18" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18" s="3">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G18" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I18" s="2">
         <v>1</v>
       </c>
       <c r="J18" s="3">
-        <f t="shared" si="1"/>
-        <v>1500</v>
+        <f>J17+100</f>
+        <v>1700</v>
       </c>
       <c r="K18" s="2">
-        <v>99</v>
+        <v>999</v>
       </c>
       <c r="L18" s="2">
         <v>0</v>
       </c>
-      <c r="M18" s="10" t="s">
-        <v>59</v>
-      </c>
+      <c r="M18" s="10"/>
       <c r="N18" s="2" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B19" s="2">
-        <v>10001011</v>
+        <v>10002002</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D19" s="2">
-        <v>10000009</v>
+        <v>10000010</v>
       </c>
       <c r="E19" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F19" s="3">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G19" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H19" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" s="2">
         <v>1</v>
       </c>
       <c r="J19" s="3">
-        <f t="shared" si="1"/>
-        <v>1600</v>
+        <f t="shared" ref="J19:J35" si="1">J18+100</f>
+        <v>1800</v>
       </c>
       <c r="K19" s="2">
-        <v>99</v>
+        <v>999</v>
       </c>
       <c r="L19" s="2">
         <v>0</v>
       </c>
-      <c r="M19" s="10" t="s">
-        <v>64</v>
-      </c>
+      <c r="M19" s="10"/>
       <c r="N19" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B20" s="2">
-        <v>10002001</v>
+        <v>10002003</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D20" s="2">
-        <v>10000009</v>
+        <v>10000011</v>
       </c>
       <c r="E20" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F20" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G20" s="2">
         <v>2</v>
@@ -2375,7 +2361,7 @@
       </c>
       <c r="J20" s="3">
         <f t="shared" si="1"/>
-        <v>1700</v>
+        <v>1900</v>
       </c>
       <c r="K20" s="2">
         <v>999</v>
@@ -2385,24 +2371,24 @@
       </c>
       <c r="M20" s="10"/>
       <c r="N20" s="2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B21" s="2">
-        <v>10002002</v>
+        <v>10002004</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D21" s="2">
-        <v>10000010</v>
+        <v>10000012</v>
       </c>
       <c r="E21" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F21" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G21" s="2">
         <v>2</v>
@@ -2414,8 +2400,8 @@
         <v>1</v>
       </c>
       <c r="J21" s="3">
-        <f t="shared" ref="J21:J37" si="2">J20+100</f>
-        <v>1800</v>
+        <f t="shared" si="1"/>
+        <v>2000</v>
       </c>
       <c r="K21" s="2">
         <v>999</v>
@@ -2425,24 +2411,24 @@
       </c>
       <c r="M21" s="10"/>
       <c r="N21" s="2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B22" s="2">
-        <v>10002003</v>
+        <v>10002005</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D22" s="2">
-        <v>10000011</v>
+        <v>10000013</v>
       </c>
       <c r="E22" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F22" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G22" s="2">
         <v>2</v>
@@ -2454,8 +2440,8 @@
         <v>1</v>
       </c>
       <c r="J22" s="3">
-        <f t="shared" si="2"/>
-        <v>1900</v>
+        <f t="shared" si="1"/>
+        <v>2100</v>
       </c>
       <c r="K22" s="2">
         <v>999</v>
@@ -2465,24 +2451,24 @@
       </c>
       <c r="M22" s="10"/>
       <c r="N22" s="2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B23" s="2">
-        <v>10002004</v>
+        <v>10002006</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D23" s="2">
-        <v>10000012</v>
+        <v>10000001</v>
       </c>
       <c r="E23" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F23" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G23" s="2">
         <v>2</v>
@@ -2494,8 +2480,8 @@
         <v>1</v>
       </c>
       <c r="J23" s="3">
-        <f t="shared" si="2"/>
-        <v>2000</v>
+        <f t="shared" si="1"/>
+        <v>2200</v>
       </c>
       <c r="K23" s="2">
         <v>999</v>
@@ -2505,24 +2491,24 @@
       </c>
       <c r="M23" s="10"/>
       <c r="N23" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B24" s="2">
-        <v>10002005</v>
+        <v>10002007</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D24" s="2">
-        <v>10000013</v>
+        <v>10000002</v>
       </c>
       <c r="E24" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F24" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G24" s="2">
         <v>2</v>
@@ -2534,8 +2520,8 @@
         <v>1</v>
       </c>
       <c r="J24" s="3">
-        <f t="shared" si="2"/>
-        <v>2100</v>
+        <f t="shared" si="1"/>
+        <v>2300</v>
       </c>
       <c r="K24" s="2">
         <v>999</v>
@@ -2545,24 +2531,24 @@
       </c>
       <c r="M24" s="10"/>
       <c r="N24" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B25" s="2">
-        <v>10002006</v>
+        <v>10002008</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D25" s="2">
-        <v>10000001</v>
+        <v>10000003</v>
       </c>
       <c r="E25" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F25" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G25" s="2">
         <v>2</v>
@@ -2574,8 +2560,8 @@
         <v>1</v>
       </c>
       <c r="J25" s="3">
-        <f t="shared" si="2"/>
-        <v>2200</v>
+        <f t="shared" si="1"/>
+        <v>2400</v>
       </c>
       <c r="K25" s="2">
         <v>999</v>
@@ -2585,24 +2571,24 @@
       </c>
       <c r="M25" s="10"/>
       <c r="N25" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B26" s="2">
-        <v>10002007</v>
+        <v>10002009</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D26" s="2">
-        <v>10000002</v>
+        <v>10000004</v>
       </c>
       <c r="E26" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F26" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G26" s="2">
         <v>2</v>
@@ -2614,8 +2600,8 @@
         <v>1</v>
       </c>
       <c r="J26" s="3">
-        <f t="shared" si="2"/>
-        <v>2300</v>
+        <f t="shared" si="1"/>
+        <v>2500</v>
       </c>
       <c r="K26" s="2">
         <v>999</v>
@@ -2625,24 +2611,24 @@
       </c>
       <c r="M26" s="10"/>
       <c r="N26" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B27" s="2">
-        <v>10002008</v>
+        <v>10002010</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D27" s="2">
-        <v>10000003</v>
+        <v>10000005</v>
       </c>
       <c r="E27" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F27" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G27" s="2">
         <v>2</v>
@@ -2654,8 +2640,8 @@
         <v>1</v>
       </c>
       <c r="J27" s="3">
-        <f t="shared" si="2"/>
-        <v>2400</v>
+        <f t="shared" si="1"/>
+        <v>2600</v>
       </c>
       <c r="K27" s="2">
         <v>999</v>
@@ -2665,24 +2651,24 @@
       </c>
       <c r="M27" s="10"/>
       <c r="N27" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B28" s="2">
-        <v>10002009</v>
+        <v>10002011</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D28" s="2">
-        <v>10000004</v>
+        <v>10000006</v>
       </c>
       <c r="E28" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F28" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G28" s="2">
         <v>2</v>
@@ -2694,8 +2680,8 @@
         <v>1</v>
       </c>
       <c r="J28" s="3">
-        <f t="shared" si="2"/>
-        <v>2500</v>
+        <f t="shared" si="1"/>
+        <v>2700</v>
       </c>
       <c r="K28" s="2">
         <v>999</v>
@@ -2705,123 +2691,127 @@
       </c>
       <c r="M28" s="10"/>
       <c r="N28" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B29" s="2">
-        <v>10002010</v>
+        <v>10002012</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D29" s="2">
-        <v>10000005</v>
+        <v>10000009</v>
       </c>
       <c r="E29" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F29" s="3">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="G29" s="2">
         <v>2</v>
       </c>
       <c r="H29" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I29" s="2">
         <v>1</v>
       </c>
       <c r="J29" s="3">
-        <f t="shared" si="2"/>
-        <v>2600</v>
+        <f>J16+100</f>
+        <v>1400</v>
       </c>
       <c r="K29" s="2">
-        <v>999</v>
+        <v>99</v>
       </c>
       <c r="L29" s="2">
         <v>0</v>
       </c>
-      <c r="M29" s="10"/>
+      <c r="M29" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="N29" s="2" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="30" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B30" s="2">
-        <v>10002011</v>
+        <v>10002013</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>78</v>
       </c>
       <c r="D30" s="2">
-        <v>10000006</v>
+        <v>10000009</v>
       </c>
       <c r="E30" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F30" s="3">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="G30" s="2">
         <v>2</v>
       </c>
       <c r="H30" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I30" s="2">
         <v>1</v>
       </c>
       <c r="J30" s="3">
-        <f t="shared" si="2"/>
-        <v>2700</v>
+        <f>J29+100</f>
+        <v>1500</v>
       </c>
       <c r="K30" s="2">
-        <v>999</v>
+        <v>99</v>
       </c>
       <c r="L30" s="2">
         <v>0</v>
       </c>
-      <c r="M30" s="10"/>
+      <c r="M30" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="N30" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="31" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B31" s="2">
-        <v>10003001</v>
+        <v>10003003</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>80</v>
       </c>
       <c r="D31" s="2">
-        <v>10003001</v>
+        <v>10003003</v>
       </c>
       <c r="E31" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F31" s="3">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G31" s="2">
         <v>3</v>
       </c>
       <c r="H31" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I31" s="2">
         <v>1</v>
       </c>
-      <c r="J31" s="3">
-        <f t="shared" si="2"/>
-        <v>2800</v>
+      <c r="J31" s="3" t="e">
+        <f>#REF!+100</f>
+        <v>#REF!</v>
       </c>
       <c r="K31" s="2">
         <v>1</v>
       </c>
       <c r="L31" s="2">
-        <v>12000001</v>
+        <v>12000003</v>
       </c>
       <c r="M31" s="10"/>
       <c r="N31" s="2" t="s">
@@ -2830,38 +2820,38 @@
     </row>
     <row r="32" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B32" s="2">
-        <v>10003002</v>
+        <v>10003004</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>82</v>
       </c>
       <c r="D32" s="2">
-        <v>10003002</v>
+        <v>10003004</v>
       </c>
       <c r="E32" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F32" s="3">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G32" s="2">
         <v>3</v>
       </c>
       <c r="H32" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I32" s="2">
         <v>1</v>
       </c>
-      <c r="J32" s="3">
-        <f t="shared" si="2"/>
-        <v>2900</v>
+      <c r="J32" s="3" t="e">
+        <f t="shared" si="1"/>
+        <v>#REF!</v>
       </c>
       <c r="K32" s="2">
         <v>1</v>
       </c>
       <c r="L32" s="2">
-        <v>12000002</v>
+        <v>12000004</v>
       </c>
       <c r="M32" s="10"/>
       <c r="N32" s="2" t="s">
@@ -2870,38 +2860,38 @@
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B33" s="2">
-        <v>10003003</v>
+        <v>10003005</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>84</v>
       </c>
       <c r="D33" s="2">
-        <v>10003003</v>
+        <v>10003005</v>
       </c>
       <c r="E33" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F33" s="3">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G33" s="2">
         <v>3</v>
       </c>
       <c r="H33" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I33" s="2">
         <v>1</v>
       </c>
-      <c r="J33" s="3">
-        <f t="shared" si="2"/>
-        <v>3000</v>
+      <c r="J33" s="3" t="e">
+        <f t="shared" si="1"/>
+        <v>#REF!</v>
       </c>
       <c r="K33" s="2">
         <v>1</v>
       </c>
       <c r="L33" s="2">
-        <v>12000003</v>
+        <v>12000005</v>
       </c>
       <c r="M33" s="10"/>
       <c r="N33" s="2" t="s">
@@ -2910,38 +2900,38 @@
     </row>
     <row r="34" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B34" s="2">
-        <v>10003004</v>
+        <v>10003006</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>86</v>
       </c>
       <c r="D34" s="2">
-        <v>10003004</v>
+        <v>10003006</v>
       </c>
       <c r="E34" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F34" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G34" s="2">
         <v>3</v>
       </c>
       <c r="H34" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I34" s="2">
         <v>1</v>
       </c>
-      <c r="J34" s="3">
-        <f t="shared" si="2"/>
-        <v>3100</v>
+      <c r="J34" s="3" t="e">
+        <f t="shared" si="1"/>
+        <v>#REF!</v>
       </c>
       <c r="K34" s="2">
         <v>1</v>
       </c>
       <c r="L34" s="2">
-        <v>12000004</v>
+        <v>12000006</v>
       </c>
       <c r="M34" s="10"/>
       <c r="N34" s="2" t="s">
@@ -2950,122 +2940,42 @@
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B35" s="2">
-        <v>10003005</v>
+        <v>10003011</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>88</v>
       </c>
       <c r="D35" s="2">
-        <v>10003005</v>
+        <v>10003001</v>
       </c>
       <c r="E35" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F35" s="3">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G35" s="2">
         <v>3</v>
       </c>
       <c r="H35" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I35" s="2">
         <v>1</v>
       </c>
-      <c r="J35" s="3">
-        <f t="shared" si="2"/>
-        <v>3200</v>
+      <c r="J35" s="3" t="e">
+        <f t="shared" si="1"/>
+        <v>#REF!</v>
       </c>
       <c r="K35" s="2">
         <v>1</v>
       </c>
       <c r="L35" s="2">
-        <v>12000005</v>
+        <v>12000011</v>
       </c>
       <c r="M35" s="10"/>
       <c r="N35" s="2" t="s">
         <v>89</v>
-      </c>
-    </row>
-    <row r="36" s="2" customFormat="1" customHeight="1" spans="2:14">
-      <c r="B36" s="2">
-        <v>10003006</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D36" s="2">
-        <v>10003006</v>
-      </c>
-      <c r="E36" s="2">
-        <v>6</v>
-      </c>
-      <c r="F36" s="3">
-        <v>30</v>
-      </c>
-      <c r="G36" s="2">
-        <v>3</v>
-      </c>
-      <c r="H36" s="2">
-        <v>6</v>
-      </c>
-      <c r="I36" s="2">
-        <v>1</v>
-      </c>
-      <c r="J36" s="3">
-        <f t="shared" si="2"/>
-        <v>3300</v>
-      </c>
-      <c r="K36" s="2">
-        <v>1</v>
-      </c>
-      <c r="L36" s="2">
-        <v>12000006</v>
-      </c>
-      <c r="M36" s="10"/>
-      <c r="N36" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="37" s="2" customFormat="1" customHeight="1" spans="2:14">
-      <c r="B37" s="2">
-        <v>10003011</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D37" s="2">
-        <v>10003001</v>
-      </c>
-      <c r="E37" s="2">
-        <v>3</v>
-      </c>
-      <c r="F37" s="3">
-        <v>25</v>
-      </c>
-      <c r="G37" s="2">
-        <v>3</v>
-      </c>
-      <c r="H37" s="2">
-        <v>1</v>
-      </c>
-      <c r="I37" s="2">
-        <v>1</v>
-      </c>
-      <c r="J37" s="3">
-        <f t="shared" si="2"/>
-        <v>3400</v>
-      </c>
-      <c r="K37" s="2">
-        <v>1</v>
-      </c>
-      <c r="L37" s="2">
-        <v>12000011</v>
-      </c>
-      <c r="M37" s="10"/>
-      <c r="N37" s="2" t="s">
-        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/ItemConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ItemConfig.xlsx
@@ -210,7 +210,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="92">
   <si>
     <t>##var</t>
   </si>
@@ -450,6 +450,12 @@
   </si>
   <si>
     <t>英雄增加100魂石</t>
+  </si>
+  <si>
+    <t>一个头盔</t>
+  </si>
+  <si>
+    <t>一个衣服</t>
   </si>
   <si>
     <t>一个裤子</t>
@@ -664,9 +670,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
-      <name val="微软雅黑"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -676,8 +681,9 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
-      <name val="宋体"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1552,7 +1558,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.875" style="3" customWidth="1"/>
@@ -1758,7 +1764,7 @@
         <v>1</v>
       </c>
       <c r="J5" s="3">
-        <f t="shared" ref="J5:J11" si="0">J4+100</f>
+        <f t="shared" ref="J5:J16" si="0">J4+100</f>
         <v>200</v>
       </c>
       <c r="K5" s="3">
@@ -2038,7 +2044,7 @@
         <v>1</v>
       </c>
       <c r="J12" s="3">
-        <f>J11+100</f>
+        <f t="shared" si="0"/>
         <v>900</v>
       </c>
       <c r="K12" s="2">
@@ -2078,7 +2084,7 @@
         <v>1</v>
       </c>
       <c r="J13" s="3">
-        <f>J12+100</f>
+        <f t="shared" si="0"/>
         <v>1000</v>
       </c>
       <c r="K13" s="2">
@@ -2118,7 +2124,7 @@
         <v>1</v>
       </c>
       <c r="J14" s="3">
-        <f>J13+100</f>
+        <f t="shared" si="0"/>
         <v>1100</v>
       </c>
       <c r="K14" s="2">
@@ -2158,7 +2164,7 @@
         <v>1</v>
       </c>
       <c r="J15" s="3">
-        <f>J14+100</f>
+        <f t="shared" si="0"/>
         <v>1200</v>
       </c>
       <c r="K15" s="2">
@@ -2198,7 +2204,7 @@
         <v>1</v>
       </c>
       <c r="J16" s="3">
-        <f>J15+100</f>
+        <f t="shared" si="0"/>
         <v>1300</v>
       </c>
       <c r="K16" s="2">
@@ -2238,8 +2244,8 @@
         <v>1</v>
       </c>
       <c r="J17" s="3">
-        <f>J30+100</f>
-        <v>1600</v>
+        <f>J16+100</f>
+        <v>1400</v>
       </c>
       <c r="K17" s="2">
         <v>99</v>
@@ -2281,7 +2287,7 @@
       </c>
       <c r="J18" s="3">
         <f>J17+100</f>
-        <v>1700</v>
+        <v>1500</v>
       </c>
       <c r="K18" s="2">
         <v>999</v>
@@ -2321,7 +2327,7 @@
       </c>
       <c r="J19" s="3">
         <f t="shared" ref="J19:J35" si="1">J18+100</f>
-        <v>1800</v>
+        <v>1600</v>
       </c>
       <c r="K19" s="2">
         <v>999</v>
@@ -2361,7 +2367,7 @@
       </c>
       <c r="J20" s="3">
         <f t="shared" si="1"/>
-        <v>1900</v>
+        <v>1700</v>
       </c>
       <c r="K20" s="2">
         <v>999</v>
@@ -2401,7 +2407,7 @@
       </c>
       <c r="J21" s="3">
         <f t="shared" si="1"/>
-        <v>2000</v>
+        <v>1800</v>
       </c>
       <c r="K21" s="2">
         <v>999</v>
@@ -2441,7 +2447,7 @@
       </c>
       <c r="J22" s="3">
         <f t="shared" si="1"/>
-        <v>2100</v>
+        <v>1900</v>
       </c>
       <c r="K22" s="2">
         <v>999</v>
@@ -2481,7 +2487,7 @@
       </c>
       <c r="J23" s="3">
         <f t="shared" si="1"/>
-        <v>2200</v>
+        <v>2000</v>
       </c>
       <c r="K23" s="2">
         <v>999</v>
@@ -2521,7 +2527,7 @@
       </c>
       <c r="J24" s="3">
         <f t="shared" si="1"/>
-        <v>2300</v>
+        <v>2100</v>
       </c>
       <c r="K24" s="2">
         <v>999</v>
@@ -2561,7 +2567,7 @@
       </c>
       <c r="J25" s="3">
         <f t="shared" si="1"/>
-        <v>2400</v>
+        <v>2200</v>
       </c>
       <c r="K25" s="2">
         <v>999</v>
@@ -2601,7 +2607,7 @@
       </c>
       <c r="J26" s="3">
         <f t="shared" si="1"/>
-        <v>2500</v>
+        <v>2300</v>
       </c>
       <c r="K26" s="2">
         <v>999</v>
@@ -2641,7 +2647,7 @@
       </c>
       <c r="J27" s="3">
         <f t="shared" si="1"/>
-        <v>2600</v>
+        <v>2400</v>
       </c>
       <c r="K27" s="2">
         <v>999</v>
@@ -2681,7 +2687,7 @@
       </c>
       <c r="J28" s="3">
         <f t="shared" si="1"/>
-        <v>2700</v>
+        <v>2500</v>
       </c>
       <c r="K28" s="2">
         <v>999</v>
@@ -2720,8 +2726,8 @@
         <v>1</v>
       </c>
       <c r="J29" s="3">
-        <f>J16+100</f>
-        <v>1400</v>
+        <f>J28+100</f>
+        <v>2600</v>
       </c>
       <c r="K29" s="2">
         <v>99</v>
@@ -2763,7 +2769,7 @@
       </c>
       <c r="J30" s="3">
         <f>J29+100</f>
-        <v>1500</v>
+        <v>2700</v>
       </c>
       <c r="K30" s="2">
         <v>99</v>
@@ -2778,204 +2784,277 @@
         <v>79</v>
       </c>
     </row>
-    <row r="31" s="2" customFormat="1" customHeight="1" spans="2:14">
+    <row r="31" s="2" customFormat="1" customHeight="1" spans="2:13">
       <c r="B31" s="2">
-        <v>10003003</v>
+        <v>10003001</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>80</v>
       </c>
       <c r="D31" s="2">
-        <v>10003003</v>
+        <v>10003001</v>
       </c>
       <c r="E31" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F31" s="3">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G31" s="2">
         <v>3</v>
       </c>
       <c r="H31" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I31" s="2">
         <v>1</v>
       </c>
-      <c r="J31" s="3" t="e">
-        <f>#REF!+100</f>
-        <v>#REF!</v>
+      <c r="J31" s="3">
+        <v>2800</v>
       </c>
       <c r="K31" s="2">
         <v>1</v>
       </c>
       <c r="L31" s="2">
-        <v>12000003</v>
+        <v>12000001</v>
       </c>
       <c r="M31" s="10"/>
-      <c r="N31" s="2" t="s">
+    </row>
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="2:13">
+      <c r="B32" s="2">
+        <v>10003002</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="32" s="2" customFormat="1" customHeight="1" spans="2:14">
-      <c r="B32" s="2">
-        <v>10003004</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="D32" s="2">
-        <v>10003004</v>
+        <v>10003002</v>
       </c>
       <c r="E32" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F32" s="3">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G32" s="2">
         <v>3</v>
       </c>
       <c r="H32" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I32" s="2">
         <v>1</v>
       </c>
-      <c r="J32" s="3" t="e">
-        <f t="shared" si="1"/>
-        <v>#REF!</v>
+      <c r="J32" s="3">
+        <f>J31+100</f>
+        <v>2900</v>
       </c>
       <c r="K32" s="2">
         <v>1</v>
       </c>
       <c r="L32" s="2">
-        <v>12000004</v>
+        <v>12000002</v>
       </c>
       <c r="M32" s="10"/>
-      <c r="N32" s="2" t="s">
-        <v>83</v>
-      </c>
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B33" s="2">
-        <v>10003005</v>
+        <v>10003003</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D33" s="2">
-        <v>10003005</v>
+        <v>10003003</v>
       </c>
       <c r="E33" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F33" s="3">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G33" s="2">
         <v>3</v>
       </c>
       <c r="H33" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I33" s="2">
         <v>1</v>
       </c>
-      <c r="J33" s="3" t="e">
-        <f t="shared" si="1"/>
-        <v>#REF!</v>
+      <c r="J33" s="3">
+        <f>J32+100</f>
+        <v>3000</v>
       </c>
       <c r="K33" s="2">
         <v>1</v>
       </c>
       <c r="L33" s="2">
-        <v>12000005</v>
+        <v>12000003</v>
       </c>
       <c r="M33" s="10"/>
       <c r="N33" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="34" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B34" s="2">
-        <v>10003006</v>
+        <v>10003004</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D34" s="2">
-        <v>10003006</v>
+        <v>10003004</v>
       </c>
       <c r="E34" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F34" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G34" s="2">
         <v>3</v>
       </c>
       <c r="H34" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I34" s="2">
         <v>1</v>
       </c>
-      <c r="J34" s="3" t="e">
-        <f t="shared" si="1"/>
-        <v>#REF!</v>
+      <c r="J34" s="3">
+        <f>J33+100</f>
+        <v>3100</v>
       </c>
       <c r="K34" s="2">
         <v>1</v>
       </c>
       <c r="L34" s="2">
-        <v>12000006</v>
+        <v>12000004</v>
       </c>
       <c r="M34" s="10"/>
       <c r="N34" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B35" s="2">
-        <v>10003011</v>
+        <v>10003005</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D35" s="2">
-        <v>10003001</v>
+        <v>10003005</v>
       </c>
       <c r="E35" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F35" s="3">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G35" s="2">
         <v>3</v>
       </c>
       <c r="H35" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I35" s="2">
         <v>1</v>
       </c>
-      <c r="J35" s="3" t="e">
-        <f t="shared" si="1"/>
-        <v>#REF!</v>
+      <c r="J35" s="3">
+        <f>J34+100</f>
+        <v>3200</v>
       </c>
       <c r="K35" s="2">
         <v>1</v>
       </c>
       <c r="L35" s="2">
-        <v>12000011</v>
+        <v>12000005</v>
       </c>
       <c r="M35" s="10"/>
       <c r="N35" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="2:14">
+      <c r="B36" s="2">
+        <v>10003006</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D36" s="2">
+        <v>10003006</v>
+      </c>
+      <c r="E36" s="2">
+        <v>6</v>
+      </c>
+      <c r="F36" s="3">
+        <v>30</v>
+      </c>
+      <c r="G36" s="2">
+        <v>3</v>
+      </c>
+      <c r="H36" s="2">
+        <v>6</v>
+      </c>
+      <c r="I36" s="2">
+        <v>1</v>
+      </c>
+      <c r="J36" s="3">
+        <f>J35+100</f>
+        <v>3300</v>
+      </c>
+      <c r="K36" s="2">
+        <v>1</v>
+      </c>
+      <c r="L36" s="2">
+        <v>12000006</v>
+      </c>
+      <c r="M36" s="10"/>
+      <c r="N36" s="2" t="s">
         <v>89</v>
+      </c>
+    </row>
+    <row r="37" s="2" customFormat="1" customHeight="1" spans="2:14">
+      <c r="B37" s="2">
+        <v>10003011</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D37" s="2">
+        <v>10003001</v>
+      </c>
+      <c r="E37" s="2">
+        <v>3</v>
+      </c>
+      <c r="F37" s="3">
+        <v>25</v>
+      </c>
+      <c r="G37" s="2">
+        <v>3</v>
+      </c>
+      <c r="H37" s="2">
+        <v>1</v>
+      </c>
+      <c r="I37" s="2">
+        <v>1</v>
+      </c>
+      <c r="J37" s="3">
+        <f>J36+100</f>
+        <v>3400</v>
+      </c>
+      <c r="K37" s="2">
+        <v>1</v>
+      </c>
+      <c r="L37" s="2">
+        <v>12000011</v>
+      </c>
+      <c r="M37" s="10"/>
+      <c r="N37" s="2" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/ItemConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ItemConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -152,12 +152,12 @@
             <charset val="134"/>
           </rPr>
           <t>当道具类型为3（装备）时该字段的意义
-1 头盔
-2 衣服
-3 裤子
-4 鞋子
-5 项链
-6 武器</t>
+3001 头盔
+3002 衣服
+3003 裤子
+3004 鞋子
+3005 项链
+3006 武器</t>
         </r>
       </text>
     </comment>
@@ -670,12 +670,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1632,10 +1632,10 @@
         <v>15</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>15</v>
@@ -1764,7 +1764,7 @@
         <v>1</v>
       </c>
       <c r="J5" s="3">
-        <f t="shared" ref="J5:J16" si="0">J4+100</f>
+        <f t="shared" ref="J5:J18" si="0">J4+100</f>
         <v>200</v>
       </c>
       <c r="K5" s="3">
@@ -2244,7 +2244,7 @@
         <v>1</v>
       </c>
       <c r="J17" s="3">
-        <f>J16+100</f>
+        <f t="shared" si="0"/>
         <v>1400</v>
       </c>
       <c r="K17" s="2">
@@ -2286,7 +2286,7 @@
         <v>1</v>
       </c>
       <c r="J18" s="3">
-        <f>J17+100</f>
+        <f t="shared" si="0"/>
         <v>1500</v>
       </c>
       <c r="K18" s="2">
@@ -2726,7 +2726,7 @@
         <v>1</v>
       </c>
       <c r="J29" s="3">
-        <f>J28+100</f>
+        <f t="shared" si="1"/>
         <v>2600</v>
       </c>
       <c r="K29" s="2">
@@ -2768,7 +2768,7 @@
         <v>1</v>
       </c>
       <c r="J30" s="3">
-        <f>J29+100</f>
+        <f t="shared" si="1"/>
         <v>2700</v>
       </c>
       <c r="K30" s="2">
@@ -2804,7 +2804,7 @@
         <v>3</v>
       </c>
       <c r="H31" s="2">
-        <v>1</v>
+        <v>3001</v>
       </c>
       <c r="I31" s="2">
         <v>1</v>
@@ -2840,13 +2840,13 @@
         <v>3</v>
       </c>
       <c r="H32" s="2">
-        <v>2</v>
+        <v>3002</v>
       </c>
       <c r="I32" s="2">
         <v>1</v>
       </c>
       <c r="J32" s="3">
-        <f>J31+100</f>
+        <f t="shared" ref="J32:J37" si="2">J31+100</f>
         <v>2900</v>
       </c>
       <c r="K32" s="2">
@@ -2877,13 +2877,13 @@
         <v>3</v>
       </c>
       <c r="H33" s="2">
-        <v>3</v>
+        <v>3003</v>
       </c>
       <c r="I33" s="2">
         <v>1</v>
       </c>
       <c r="J33" s="3">
-        <f>J32+100</f>
+        <f t="shared" si="2"/>
         <v>3000</v>
       </c>
       <c r="K33" s="2">
@@ -2917,13 +2917,13 @@
         <v>3</v>
       </c>
       <c r="H34" s="2">
-        <v>4</v>
+        <v>3004</v>
       </c>
       <c r="I34" s="2">
         <v>1</v>
       </c>
       <c r="J34" s="3">
-        <f>J33+100</f>
+        <f t="shared" si="2"/>
         <v>3100</v>
       </c>
       <c r="K34" s="2">
@@ -2957,13 +2957,13 @@
         <v>3</v>
       </c>
       <c r="H35" s="2">
-        <v>5</v>
+        <v>3005</v>
       </c>
       <c r="I35" s="2">
         <v>1</v>
       </c>
       <c r="J35" s="3">
-        <f>J34+100</f>
+        <f t="shared" si="2"/>
         <v>3200</v>
       </c>
       <c r="K35" s="2">
@@ -2997,13 +2997,13 @@
         <v>3</v>
       </c>
       <c r="H36" s="2">
-        <v>6</v>
+        <v>3006</v>
       </c>
       <c r="I36" s="2">
         <v>1</v>
       </c>
       <c r="J36" s="3">
-        <f>J35+100</f>
+        <f t="shared" si="2"/>
         <v>3300</v>
       </c>
       <c r="K36" s="2">
@@ -3037,13 +3037,13 @@
         <v>3</v>
       </c>
       <c r="H37" s="2">
-        <v>1</v>
+        <v>3001</v>
       </c>
       <c r="I37" s="2">
         <v>1</v>
       </c>
       <c r="J37" s="3">
-        <f>J36+100</f>
+        <f t="shared" si="2"/>
         <v>3400</v>
       </c>
       <c r="K37" s="2">

--- a/Unity/Assets/Config/Excel/ItemConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ItemConfig.xlsx
@@ -210,7 +210,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="96">
   <si>
     <t>##var</t>
   </si>
@@ -395,10 +395,22 @@
     <t>打开后获得4000金币</t>
   </si>
   <si>
+    <t>斧王碎片</t>
+  </si>
+  <si>
+    <t>10001001,30</t>
+  </si>
+  <si>
+    <t>英雄碎片，合成英雄</t>
+  </si>
+  <si>
+    <t>流浪剑客碎片</t>
+  </si>
+  <si>
+    <t>10001002,30</t>
+  </si>
+  <si>
     <t>大熊猫碎片</t>
-  </si>
-  <si>
-    <t>英雄碎片，合成英雄</t>
   </si>
   <si>
     <t>材料1</t>
@@ -1563,7 +1575,7 @@
   <cols>
     <col min="1" max="1" width="10.875" style="3" customWidth="1"/>
     <col min="2" max="12" width="17.875" style="3"/>
-    <col min="13" max="13" width="20.5" style="4" customWidth="1"/>
+    <col min="13" max="13" width="27.25" style="4" customWidth="1"/>
     <col min="14" max="14" width="70.625" style="3" customWidth="1"/>
     <col min="15" max="16384" width="17.875" style="3"/>
   </cols>
@@ -2295,9 +2307,11 @@
       <c r="L18" s="2">
         <v>0</v>
       </c>
-      <c r="M18" s="10"/>
+      <c r="M18" s="10" t="s">
+        <v>62</v>
+      </c>
       <c r="N18" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="2:14">
@@ -2305,7 +2319,7 @@
         <v>10002002</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D19" s="2">
         <v>10000010</v>
@@ -2335,9 +2349,11 @@
       <c r="L19" s="2">
         <v>0</v>
       </c>
-      <c r="M19" s="10"/>
+      <c r="M19" s="10" t="s">
+        <v>65</v>
+      </c>
       <c r="N19" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="2:14">
@@ -2345,7 +2361,7 @@
         <v>10002003</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D20" s="2">
         <v>10000011</v>
@@ -2377,7 +2393,7 @@
       </c>
       <c r="M20" s="10"/>
       <c r="N20" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="2:14">
@@ -2385,7 +2401,7 @@
         <v>10002004</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D21" s="2">
         <v>10000012</v>
@@ -2417,7 +2433,7 @@
       </c>
       <c r="M21" s="10"/>
       <c r="N21" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="2:14">
@@ -2425,7 +2441,7 @@
         <v>10002005</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D22" s="2">
         <v>10000013</v>
@@ -2457,7 +2473,7 @@
       </c>
       <c r="M22" s="10"/>
       <c r="N22" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="2:14">
@@ -2465,7 +2481,7 @@
         <v>10002006</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D23" s="2">
         <v>10000001</v>
@@ -2497,7 +2513,7 @@
       </c>
       <c r="M23" s="10"/>
       <c r="N23" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="2:14">
@@ -2505,7 +2521,7 @@
         <v>10002007</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D24" s="2">
         <v>10000002</v>
@@ -2537,7 +2553,7 @@
       </c>
       <c r="M24" s="10"/>
       <c r="N24" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" customHeight="1" spans="2:14">
@@ -2545,7 +2561,7 @@
         <v>10002008</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D25" s="2">
         <v>10000003</v>
@@ -2577,7 +2593,7 @@
       </c>
       <c r="M25" s="10"/>
       <c r="N25" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" customHeight="1" spans="2:14">
@@ -2585,7 +2601,7 @@
         <v>10002009</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D26" s="2">
         <v>10000004</v>
@@ -2617,7 +2633,7 @@
       </c>
       <c r="M26" s="10"/>
       <c r="N26" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" customHeight="1" spans="2:14">
@@ -2625,7 +2641,7 @@
         <v>10002010</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D27" s="2">
         <v>10000005</v>
@@ -2657,7 +2673,7 @@
       </c>
       <c r="M27" s="10"/>
       <c r="N27" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" customHeight="1" spans="2:14">
@@ -2665,7 +2681,7 @@
         <v>10002011</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D28" s="2">
         <v>10000006</v>
@@ -2697,7 +2713,7 @@
       </c>
       <c r="M28" s="10"/>
       <c r="N28" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29" s="2" customFormat="1" customHeight="1" spans="2:14">
@@ -2705,7 +2721,7 @@
         <v>10002012</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D29" s="2">
         <v>10000009</v>
@@ -2736,10 +2752,10 @@
         <v>0</v>
       </c>
       <c r="M29" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" s="2" customFormat="1" customHeight="1" spans="2:14">
@@ -2747,7 +2763,7 @@
         <v>10002013</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D30" s="2">
         <v>10000009</v>
@@ -2778,10 +2794,10 @@
         <v>0</v>
       </c>
       <c r="M30" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" s="2" customFormat="1" customHeight="1" spans="2:13">
@@ -2789,7 +2805,7 @@
         <v>10003001</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D31" s="2">
         <v>10003001</v>
@@ -2825,7 +2841,7 @@
         <v>10003002</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D32" s="2">
         <v>10003002</v>
@@ -2862,7 +2878,7 @@
         <v>10003003</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D33" s="2">
         <v>10003003</v>
@@ -2894,7 +2910,7 @@
       </c>
       <c r="M33" s="10"/>
       <c r="N33" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" s="2" customFormat="1" customHeight="1" spans="2:14">
@@ -2902,7 +2918,7 @@
         <v>10003004</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D34" s="2">
         <v>10003004</v>
@@ -2934,7 +2950,7 @@
       </c>
       <c r="M34" s="10"/>
       <c r="N34" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="2:14">
@@ -2942,7 +2958,7 @@
         <v>10003005</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D35" s="2">
         <v>10003005</v>
@@ -2974,7 +2990,7 @@
       </c>
       <c r="M35" s="10"/>
       <c r="N35" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="2:14">
@@ -2982,7 +2998,7 @@
         <v>10003006</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D36" s="2">
         <v>10003006</v>
@@ -3014,7 +3030,7 @@
       </c>
       <c r="M36" s="10"/>
       <c r="N36" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="2:14">
@@ -3022,7 +3038,7 @@
         <v>10003011</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D37" s="2">
         <v>10003001</v>
@@ -3054,7 +3070,7 @@
       </c>
       <c r="M37" s="10"/>
       <c r="N37" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/ItemConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ItemConfig.xlsx
@@ -210,7 +210,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="103">
   <si>
     <t>##var</t>
   </si>
@@ -410,7 +410,28 @@
     <t>10001002,30</t>
   </si>
   <si>
-    <t>大熊猫碎片</t>
+    <t>剑圣碎片</t>
+  </si>
+  <si>
+    <t>10001003,30</t>
+  </si>
+  <si>
+    <t>全能骑士碎片</t>
+  </si>
+  <si>
+    <t>10001004,30</t>
+  </si>
+  <si>
+    <t>冰女碎片</t>
+  </si>
+  <si>
+    <t>10002001,30</t>
+  </si>
+  <si>
+    <t>术士碎片</t>
+  </si>
+  <si>
+    <t>10002002,30</t>
   </si>
   <si>
     <t>材料1</t>
@@ -1570,7 +1591,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.875" style="3" customWidth="1"/>
@@ -2292,7 +2313,7 @@
         <v>2</v>
       </c>
       <c r="H18" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I18" s="2">
         <v>1</v>
@@ -2334,13 +2355,13 @@
         <v>2</v>
       </c>
       <c r="H19" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I19" s="2">
         <v>1</v>
       </c>
       <c r="J19" s="3">
-        <f t="shared" ref="J19:J35" si="1">J18+100</f>
+        <f t="shared" ref="J19:J23" si="1">J18+100</f>
         <v>1600</v>
       </c>
       <c r="K19" s="2">
@@ -2376,7 +2397,7 @@
         <v>2</v>
       </c>
       <c r="H20" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I20" s="2">
         <v>1</v>
@@ -2391,7 +2412,9 @@
       <c r="L20" s="2">
         <v>0</v>
       </c>
-      <c r="M20" s="10"/>
+      <c r="M20" s="10" t="s">
+        <v>67</v>
+      </c>
       <c r="N20" s="2" t="s">
         <v>63</v>
       </c>
@@ -2401,7 +2424,7 @@
         <v>10002004</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D21" s="2">
         <v>10000012</v>
@@ -2416,7 +2439,7 @@
         <v>2</v>
       </c>
       <c r="H21" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I21" s="2">
         <v>1</v>
@@ -2431,7 +2454,9 @@
       <c r="L21" s="2">
         <v>0</v>
       </c>
-      <c r="M21" s="10"/>
+      <c r="M21" s="10" t="s">
+        <v>69</v>
+      </c>
       <c r="N21" s="2" t="s">
         <v>63</v>
       </c>
@@ -2441,7 +2466,7 @@
         <v>10002005</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D22" s="2">
         <v>10000013</v>
@@ -2456,7 +2481,7 @@
         <v>2</v>
       </c>
       <c r="H22" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I22" s="2">
         <v>1</v>
@@ -2471,7 +2496,9 @@
       <c r="L22" s="2">
         <v>0</v>
       </c>
-      <c r="M22" s="10"/>
+      <c r="M22" s="10" t="s">
+        <v>71</v>
+      </c>
       <c r="N22" s="2" t="s">
         <v>63</v>
       </c>
@@ -2481,22 +2508,22 @@
         <v>10002006</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D23" s="2">
-        <v>10000001</v>
+        <v>10000013</v>
       </c>
       <c r="E23" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F23" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G23" s="2">
         <v>2</v>
       </c>
       <c r="H23" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I23" s="2">
         <v>1</v>
@@ -2511,26 +2538,28 @@
       <c r="L23" s="2">
         <v>0</v>
       </c>
-      <c r="M23" s="10"/>
+      <c r="M23" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="N23" s="2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B24" s="2">
-        <v>10002007</v>
+        <v>10002101</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D24" s="2">
-        <v>10000002</v>
+        <v>10000001</v>
       </c>
       <c r="E24" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G24" s="2">
         <v>2</v>
@@ -2542,8 +2571,8 @@
         <v>1</v>
       </c>
       <c r="J24" s="3">
-        <f t="shared" si="1"/>
-        <v>2100</v>
+        <f>J22+100</f>
+        <v>2000</v>
       </c>
       <c r="K24" s="2">
         <v>999</v>
@@ -2553,24 +2582,24 @@
       </c>
       <c r="M24" s="10"/>
       <c r="N24" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B25" s="2">
-        <v>10002008</v>
+        <v>10002102</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D25" s="2">
-        <v>10000003</v>
+        <v>10000002</v>
       </c>
       <c r="E25" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F25" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G25" s="2">
         <v>2</v>
@@ -2582,8 +2611,8 @@
         <v>1</v>
       </c>
       <c r="J25" s="3">
-        <f t="shared" si="1"/>
-        <v>2200</v>
+        <f t="shared" ref="J24:J36" si="2">J24+100</f>
+        <v>2100</v>
       </c>
       <c r="K25" s="2">
         <v>999</v>
@@ -2593,24 +2622,24 @@
       </c>
       <c r="M25" s="10"/>
       <c r="N25" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B26" s="2">
-        <v>10002009</v>
+        <v>10002103</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D26" s="2">
-        <v>10000004</v>
+        <v>10000003</v>
       </c>
       <c r="E26" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F26" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G26" s="2">
         <v>2</v>
@@ -2622,8 +2651,8 @@
         <v>1</v>
       </c>
       <c r="J26" s="3">
-        <f t="shared" si="1"/>
-        <v>2300</v>
+        <f t="shared" si="2"/>
+        <v>2200</v>
       </c>
       <c r="K26" s="2">
         <v>999</v>
@@ -2633,24 +2662,24 @@
       </c>
       <c r="M26" s="10"/>
       <c r="N26" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B27" s="2">
-        <v>10002010</v>
+        <v>10002104</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D27" s="2">
-        <v>10000005</v>
+        <v>10000004</v>
       </c>
       <c r="E27" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F27" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G27" s="2">
         <v>2</v>
@@ -2662,8 +2691,8 @@
         <v>1</v>
       </c>
       <c r="J27" s="3">
-        <f t="shared" si="1"/>
-        <v>2400</v>
+        <f t="shared" si="2"/>
+        <v>2300</v>
       </c>
       <c r="K27" s="2">
         <v>999</v>
@@ -2673,24 +2702,24 @@
       </c>
       <c r="M27" s="10"/>
       <c r="N27" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B28" s="2">
-        <v>10002011</v>
+        <v>10002105</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D28" s="2">
-        <v>10000006</v>
+        <v>10000005</v>
       </c>
       <c r="E28" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F28" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G28" s="2">
         <v>2</v>
@@ -2702,8 +2731,8 @@
         <v>1</v>
       </c>
       <c r="J28" s="3">
-        <f t="shared" si="1"/>
-        <v>2500</v>
+        <f t="shared" si="2"/>
+        <v>2400</v>
       </c>
       <c r="K28" s="2">
         <v>999</v>
@@ -2713,57 +2742,55 @@
       </c>
       <c r="M28" s="10"/>
       <c r="N28" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B29" s="2">
-        <v>10002012</v>
+        <v>10002106</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D29" s="2">
-        <v>10000009</v>
+        <v>10000006</v>
       </c>
       <c r="E29" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F29" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="G29" s="2">
         <v>2</v>
       </c>
       <c r="H29" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I29" s="2">
         <v>1</v>
       </c>
       <c r="J29" s="3">
-        <f t="shared" si="1"/>
-        <v>2600</v>
+        <f t="shared" si="2"/>
+        <v>2500</v>
       </c>
       <c r="K29" s="2">
-        <v>99</v>
+        <v>999</v>
       </c>
       <c r="L29" s="2">
         <v>0</v>
       </c>
-      <c r="M29" s="10" t="s">
-        <v>80</v>
-      </c>
+      <c r="M29" s="10"/>
       <c r="N29" s="2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B30" s="2">
-        <v>10002013</v>
+        <v>10002012</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D30" s="2">
         <v>10000009</v>
@@ -2778,14 +2805,14 @@
         <v>2</v>
       </c>
       <c r="H30" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I30" s="2">
         <v>1</v>
       </c>
       <c r="J30" s="3">
-        <f t="shared" si="1"/>
-        <v>2700</v>
+        <f t="shared" si="2"/>
+        <v>2600</v>
       </c>
       <c r="K30" s="2">
         <v>99</v>
@@ -2794,283 +2821,325 @@
         <v>0</v>
       </c>
       <c r="M30" s="10" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="31" s="2" customFormat="1" customHeight="1" spans="2:13">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B31" s="2">
-        <v>10003001</v>
+        <v>10002013</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D31" s="2">
-        <v>10003001</v>
+        <v>10000009</v>
       </c>
       <c r="E31" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F31" s="3">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="G31" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H31" s="2">
-        <v>3001</v>
+        <v>9</v>
       </c>
       <c r="I31" s="2">
         <v>1</v>
       </c>
       <c r="J31" s="3">
-        <v>2800</v>
+        <f t="shared" si="2"/>
+        <v>2700</v>
       </c>
       <c r="K31" s="2">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="L31" s="2">
-        <v>12000001</v>
-      </c>
-      <c r="M31" s="10"/>
+        <v>0</v>
+      </c>
+      <c r="M31" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="N31" s="2" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="32" s="2" customFormat="1" customHeight="1" spans="2:13">
       <c r="B32" s="2">
-        <v>10003002</v>
+        <v>10003001</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D32" s="2">
-        <v>10003002</v>
+        <v>10003001</v>
       </c>
       <c r="E32" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F32" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G32" s="2">
         <v>3</v>
       </c>
       <c r="H32" s="2">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="I32" s="2">
         <v>1</v>
       </c>
       <c r="J32" s="3">
-        <f t="shared" ref="J32:J37" si="2">J31+100</f>
-        <v>2900</v>
+        <v>2800</v>
       </c>
       <c r="K32" s="2">
         <v>1</v>
       </c>
       <c r="L32" s="2">
-        <v>12000002</v>
+        <v>12000001</v>
       </c>
       <c r="M32" s="10"/>
     </row>
-    <row r="33" s="2" customFormat="1" customHeight="1" spans="2:14">
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="2:13">
       <c r="B33" s="2">
-        <v>10003003</v>
+        <v>10003002</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D33" s="2">
-        <v>10003003</v>
+        <v>10003002</v>
       </c>
       <c r="E33" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F33" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G33" s="2">
         <v>3</v>
       </c>
       <c r="H33" s="2">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="I33" s="2">
         <v>1</v>
       </c>
       <c r="J33" s="3">
-        <f t="shared" si="2"/>
-        <v>3000</v>
+        <f t="shared" ref="J33:J38" si="3">J32+100</f>
+        <v>2900</v>
       </c>
       <c r="K33" s="2">
         <v>1</v>
       </c>
       <c r="L33" s="2">
-        <v>12000003</v>
+        <v>12000002</v>
       </c>
       <c r="M33" s="10"/>
-      <c r="N33" s="2" t="s">
-        <v>87</v>
-      </c>
     </row>
     <row r="34" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B34" s="2">
-        <v>10003004</v>
+        <v>10003003</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D34" s="2">
-        <v>10003004</v>
+        <v>10003003</v>
       </c>
       <c r="E34" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F34" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G34" s="2">
         <v>3</v>
       </c>
       <c r="H34" s="2">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="I34" s="2">
         <v>1</v>
       </c>
       <c r="J34" s="3">
-        <f t="shared" si="2"/>
-        <v>3100</v>
+        <f t="shared" si="3"/>
+        <v>3000</v>
       </c>
       <c r="K34" s="2">
         <v>1</v>
       </c>
       <c r="L34" s="2">
-        <v>12000004</v>
+        <v>12000003</v>
       </c>
       <c r="M34" s="10"/>
       <c r="N34" s="2" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B35" s="2">
-        <v>10003005</v>
+        <v>10003004</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D35" s="2">
-        <v>10003005</v>
+        <v>10003004</v>
       </c>
       <c r="E35" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F35" s="3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G35" s="2">
         <v>3</v>
       </c>
       <c r="H35" s="2">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="I35" s="2">
         <v>1</v>
       </c>
       <c r="J35" s="3">
-        <f t="shared" si="2"/>
-        <v>3200</v>
+        <f t="shared" si="3"/>
+        <v>3100</v>
       </c>
       <c r="K35" s="2">
         <v>1</v>
       </c>
       <c r="L35" s="2">
-        <v>12000005</v>
+        <v>12000004</v>
       </c>
       <c r="M35" s="10"/>
       <c r="N35" s="2" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B36" s="2">
-        <v>10003006</v>
+        <v>10003005</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D36" s="2">
-        <v>10003006</v>
+        <v>10003005</v>
       </c>
       <c r="E36" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F36" s="3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G36" s="2">
         <v>3</v>
       </c>
       <c r="H36" s="2">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="I36" s="2">
         <v>1</v>
       </c>
       <c r="J36" s="3">
-        <f t="shared" si="2"/>
-        <v>3300</v>
+        <f t="shared" si="3"/>
+        <v>3200</v>
       </c>
       <c r="K36" s="2">
         <v>1</v>
       </c>
       <c r="L36" s="2">
-        <v>12000006</v>
+        <v>12000005</v>
       </c>
       <c r="M36" s="10"/>
       <c r="N36" s="2" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B37" s="2">
-        <v>10003011</v>
+        <v>10003006</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D37" s="2">
-        <v>10003001</v>
+        <v>10003006</v>
       </c>
       <c r="E37" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F37" s="3">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G37" s="2">
         <v>3</v>
       </c>
       <c r="H37" s="2">
-        <v>3001</v>
+        <v>3006</v>
       </c>
       <c r="I37" s="2">
         <v>1</v>
       </c>
       <c r="J37" s="3">
-        <f t="shared" si="2"/>
-        <v>3400</v>
+        <f t="shared" si="3"/>
+        <v>3300</v>
       </c>
       <c r="K37" s="2">
         <v>1</v>
       </c>
       <c r="L37" s="2">
-        <v>12000011</v>
+        <v>12000006</v>
       </c>
       <c r="M37" s="10"/>
       <c r="N37" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" s="2" customFormat="1" customHeight="1" spans="2:14">
+      <c r="B38" s="2">
+        <v>10003011</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D38" s="2">
+        <v>10003001</v>
+      </c>
+      <c r="E38" s="2">
+        <v>3</v>
+      </c>
+      <c r="F38" s="3">
+        <v>25</v>
+      </c>
+      <c r="G38" s="2">
+        <v>3</v>
+      </c>
+      <c r="H38" s="2">
+        <v>3001</v>
+      </c>
+      <c r="I38" s="2">
+        <v>1</v>
+      </c>
+      <c r="J38" s="3">
+        <f t="shared" si="3"/>
+        <v>3400</v>
+      </c>
+      <c r="K38" s="2">
+        <v>1</v>
+      </c>
+      <c r="L38" s="2">
+        <v>12000011</v>
+      </c>
+      <c r="M38" s="10"/>
+      <c r="N38" s="2" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/ItemConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ItemConfig.xlsx
@@ -210,7 +210,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="106">
   <si>
     <t>##var</t>
   </si>
@@ -251,6 +251,9 @@
     <t>ItemUsePar</t>
   </si>
   <si>
+    <t>ItemUseParInt</t>
+  </si>
+  <si>
     <t>ItemDescription</t>
   </si>
   <si>
@@ -263,6 +266,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>(array#sep=,),int</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
@@ -297,6 +303,9 @@
   </si>
   <si>
     <t>道具使用参数</t>
+  </si>
+  <si>
+    <t>道具使用参数int</t>
   </si>
   <si>
     <t>道具描述</t>
@@ -1591,17 +1600,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N38"/>
+  <dimension ref="A1:O38"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.875" style="3" customWidth="1"/>
     <col min="2" max="12" width="17.875" style="3"/>
-    <col min="13" max="13" width="27.25" style="4" customWidth="1"/>
-    <col min="14" max="14" width="70.625" style="3" customWidth="1"/>
-    <col min="15" max="16384" width="17.875" style="3"/>
+    <col min="13" max="14" width="27.25" style="4" customWidth="1"/>
+    <col min="15" max="15" width="70.625" style="3" customWidth="1"/>
+    <col min="16" max="16384" width="17.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:14">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1641,28 +1650,31 @@
       <c r="M1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="8" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="O1" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="F2" s="6" t="s">
         <v>16</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>15</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>6</v>
@@ -1671,74 +1683,80 @@
         <v>7</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M2" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:14">
+        <v>17</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A3" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="N3" s="7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" customHeight="1" spans="2:14">
+        <v>30</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="O3" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="2:15">
       <c r="B4" s="3">
         <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>
@@ -1767,16 +1785,16 @@
       <c r="L4" s="3">
         <v>0</v>
       </c>
-      <c r="N4" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" customHeight="1" spans="2:14">
+      <c r="O4" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="2:15">
       <c r="B5" s="3">
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D5" s="3">
         <v>2</v>
@@ -1806,16 +1824,16 @@
       <c r="L5" s="3">
         <v>0</v>
       </c>
-      <c r="N5" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="2:14">
+      <c r="O5" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="2:15">
       <c r="B6" s="3">
         <v>3</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D6" s="3">
         <v>3</v>
@@ -1845,16 +1863,16 @@
       <c r="L6" s="3">
         <v>0</v>
       </c>
-      <c r="N6" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="2:14">
+      <c r="O6" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="2:15">
       <c r="B7" s="3">
         <v>4</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D7" s="3">
         <v>4</v>
@@ -1884,16 +1902,16 @@
       <c r="L7" s="3">
         <v>0</v>
       </c>
-      <c r="N7" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="2:14">
+      <c r="O7" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="2:15">
       <c r="B8" s="3">
         <v>5</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D8" s="3">
         <v>5</v>
@@ -1923,16 +1941,16 @@
       <c r="L8" s="3">
         <v>0</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="2:14">
+      <c r="O8" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="2:15">
       <c r="B9" s="2">
         <v>10001001</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D9" s="2">
         <v>10000001</v>
@@ -1962,19 +1980,20 @@
       <c r="L9" s="2">
         <v>0</v>
       </c>
-      <c r="M9" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" s="2" customFormat="1" ht="19.5" customHeight="1" spans="2:14">
+      <c r="M9" s="10"/>
+      <c r="N9" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" ht="19.5" customHeight="1" spans="2:15">
       <c r="B10" s="2">
         <v>10001002</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D10" s="2">
         <v>10000002</v>
@@ -2004,19 +2023,20 @@
       <c r="L10" s="2">
         <v>0</v>
       </c>
-      <c r="M10" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="2:14">
+      <c r="M10" s="10"/>
+      <c r="N10" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="2:15">
       <c r="B11" s="2">
         <v>10001003</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D11" s="2">
         <v>10000003</v>
@@ -2047,16 +2067,17 @@
         <v>0</v>
       </c>
       <c r="M11" s="10"/>
-      <c r="N11" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="2:14">
+      <c r="N11" s="10"/>
+      <c r="O11" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="2:15">
       <c r="B12" s="2">
         <v>10001004</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D12" s="2">
         <v>10000004</v>
@@ -2087,16 +2108,17 @@
         <v>0</v>
       </c>
       <c r="M12" s="10"/>
-      <c r="N12" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="2:14">
+      <c r="N12" s="10"/>
+      <c r="O12" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="2:15">
       <c r="B13" s="2">
         <v>10001005</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D13" s="2">
         <v>10000005</v>
@@ -2127,16 +2149,17 @@
         <v>0</v>
       </c>
       <c r="M13" s="10"/>
-      <c r="N13" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="2:14">
+      <c r="N13" s="10"/>
+      <c r="O13" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="2:15">
       <c r="B14" s="2">
         <v>10001006</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D14" s="2">
         <v>10000006</v>
@@ -2167,16 +2190,17 @@
         <v>0</v>
       </c>
       <c r="M14" s="10"/>
-      <c r="N14" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" s="2" customFormat="1" customHeight="1" spans="2:14">
+      <c r="N14" s="10"/>
+      <c r="O14" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="2:15">
       <c r="B15" s="2">
         <v>10001007</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D15" s="2">
         <v>10000007</v>
@@ -2207,16 +2231,17 @@
         <v>0</v>
       </c>
       <c r="M15" s="10"/>
-      <c r="N15" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" s="2" customFormat="1" customHeight="1" spans="2:14">
+      <c r="N15" s="10"/>
+      <c r="O15" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="2:15">
       <c r="B16" s="2">
         <v>10001008</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D16" s="2">
         <v>10000008</v>
@@ -2247,16 +2272,17 @@
         <v>0</v>
       </c>
       <c r="M16" s="10"/>
-      <c r="N16" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="17" s="2" customFormat="1" customHeight="1" spans="2:14">
+      <c r="N16" s="10"/>
+      <c r="O16" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="2:15">
       <c r="B17" s="2">
         <v>10001011</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D17" s="2">
         <v>10000009</v>
@@ -2286,19 +2312,20 @@
       <c r="L17" s="2">
         <v>0</v>
       </c>
-      <c r="M17" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" s="2" customFormat="1" customHeight="1" spans="2:14">
+      <c r="M17" s="10"/>
+      <c r="N17" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="2:15">
       <c r="B18" s="2">
         <v>10002001</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D18" s="2">
         <v>10000009</v>
@@ -2328,19 +2355,20 @@
       <c r="L18" s="2">
         <v>0</v>
       </c>
-      <c r="M18" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="2:14">
+      <c r="M18" s="10"/>
+      <c r="N18" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="2:15">
       <c r="B19" s="2">
         <v>10002002</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D19" s="2">
         <v>10000010</v>
@@ -2370,19 +2398,20 @@
       <c r="L19" s="2">
         <v>0</v>
       </c>
-      <c r="M19" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="20" s="2" customFormat="1" customHeight="1" spans="2:14">
+      <c r="M19" s="10"/>
+      <c r="N19" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="2:15">
       <c r="B20" s="2">
         <v>10002003</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D20" s="2">
         <v>10000011</v>
@@ -2412,19 +2441,20 @@
       <c r="L20" s="2">
         <v>0</v>
       </c>
-      <c r="M20" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="N20" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" s="2" customFormat="1" customHeight="1" spans="2:14">
+      <c r="M20" s="10"/>
+      <c r="N20" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="2:15">
       <c r="B21" s="2">
         <v>10002004</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D21" s="2">
         <v>10000012</v>
@@ -2454,19 +2484,20 @@
       <c r="L21" s="2">
         <v>0</v>
       </c>
-      <c r="M21" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="N21" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="22" s="2" customFormat="1" customHeight="1" spans="2:14">
+      <c r="M21" s="10"/>
+      <c r="N21" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="2:15">
       <c r="B22" s="2">
         <v>10002005</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D22" s="2">
         <v>10000013</v>
@@ -2496,19 +2527,20 @@
       <c r="L22" s="2">
         <v>0</v>
       </c>
-      <c r="M22" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="23" s="2" customFormat="1" customHeight="1" spans="2:14">
+      <c r="M22" s="10"/>
+      <c r="N22" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="2:15">
       <c r="B23" s="2">
         <v>10002006</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D23" s="2">
         <v>10000013</v>
@@ -2538,19 +2570,20 @@
       <c r="L23" s="2">
         <v>0</v>
       </c>
-      <c r="M23" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="N23" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="24" s="2" customFormat="1" customHeight="1" spans="2:14">
+      <c r="M23" s="10"/>
+      <c r="N23" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="2:15">
       <c r="B24" s="2">
         <v>10002101</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D24" s="2">
         <v>10000001</v>
@@ -2581,16 +2614,17 @@
         <v>0</v>
       </c>
       <c r="M24" s="10"/>
-      <c r="N24" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="25" s="2" customFormat="1" customHeight="1" spans="2:14">
+      <c r="N24" s="10"/>
+      <c r="O24" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="2:15">
       <c r="B25" s="2">
         <v>10002102</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D25" s="2">
         <v>10000002</v>
@@ -2621,16 +2655,17 @@
         <v>0</v>
       </c>
       <c r="M25" s="10"/>
-      <c r="N25" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="26" s="2" customFormat="1" customHeight="1" spans="2:14">
+      <c r="N25" s="10"/>
+      <c r="O25" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="2:15">
       <c r="B26" s="2">
         <v>10002103</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D26" s="2">
         <v>10000003</v>
@@ -2661,16 +2696,17 @@
         <v>0</v>
       </c>
       <c r="M26" s="10"/>
-      <c r="N26" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="27" s="2" customFormat="1" customHeight="1" spans="2:14">
+      <c r="N26" s="10"/>
+      <c r="O26" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="2:15">
       <c r="B27" s="2">
         <v>10002104</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D27" s="2">
         <v>10000004</v>
@@ -2701,16 +2737,17 @@
         <v>0</v>
       </c>
       <c r="M27" s="10"/>
-      <c r="N27" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="28" s="2" customFormat="1" customHeight="1" spans="2:14">
+      <c r="N27" s="10"/>
+      <c r="O27" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="2:15">
       <c r="B28" s="2">
         <v>10002105</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D28" s="2">
         <v>10000005</v>
@@ -2741,16 +2778,17 @@
         <v>0</v>
       </c>
       <c r="M28" s="10"/>
-      <c r="N28" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="29" s="2" customFormat="1" customHeight="1" spans="2:14">
+      <c r="N28" s="10"/>
+      <c r="O28" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="2:15">
       <c r="B29" s="2">
         <v>10002106</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D29" s="2">
         <v>10000006</v>
@@ -2781,16 +2819,17 @@
         <v>0</v>
       </c>
       <c r="M29" s="10"/>
-      <c r="N29" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="30" s="2" customFormat="1" customHeight="1" spans="2:14">
+      <c r="N29" s="10"/>
+      <c r="O29" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="2:15">
       <c r="B30" s="2">
         <v>10002012</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D30" s="2">
         <v>10000009</v>
@@ -2820,19 +2859,20 @@
       <c r="L30" s="2">
         <v>0</v>
       </c>
-      <c r="M30" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="N30" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="31" s="2" customFormat="1" customHeight="1" spans="2:14">
+      <c r="M30" s="10"/>
+      <c r="N30" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="O30" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" customHeight="1" spans="2:15">
       <c r="B31" s="2">
         <v>10002013</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D31" s="2">
         <v>10000009</v>
@@ -2862,19 +2902,20 @@
       <c r="L31" s="2">
         <v>0</v>
       </c>
-      <c r="M31" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="N31" s="2" t="s">
+      <c r="M31" s="10"/>
+      <c r="N31" s="10" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="32" s="2" customFormat="1" customHeight="1" spans="2:13">
+      <c r="O31" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B32" s="2">
         <v>10003001</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D32" s="2">
         <v>10003001</v>
@@ -2904,13 +2945,14 @@
         <v>12000001</v>
       </c>
       <c r="M32" s="10"/>
-    </row>
-    <row r="33" s="2" customFormat="1" customHeight="1" spans="2:13">
+      <c r="N32" s="10"/>
+    </row>
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="2:14">
       <c r="B33" s="2">
         <v>10003002</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D33" s="2">
         <v>10003002</v>
@@ -2941,13 +2983,14 @@
         <v>12000002</v>
       </c>
       <c r="M33" s="10"/>
-    </row>
-    <row r="34" s="2" customFormat="1" customHeight="1" spans="2:14">
+      <c r="N33" s="10"/>
+    </row>
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="2:15">
       <c r="B34" s="2">
         <v>10003003</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D34" s="2">
         <v>10003003</v>
@@ -2978,16 +3021,17 @@
         <v>12000003</v>
       </c>
       <c r="M34" s="10"/>
-      <c r="N34" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="35" s="2" customFormat="1" customHeight="1" spans="2:14">
+      <c r="N34" s="10"/>
+      <c r="O34" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="2:15">
       <c r="B35" s="2">
         <v>10003004</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D35" s="2">
         <v>10003004</v>
@@ -3018,16 +3062,17 @@
         <v>12000004</v>
       </c>
       <c r="M35" s="10"/>
-      <c r="N35" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="36" s="2" customFormat="1" customHeight="1" spans="2:14">
+      <c r="N35" s="10"/>
+      <c r="O35" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="2:15">
       <c r="B36" s="2">
         <v>10003005</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D36" s="2">
         <v>10003005</v>
@@ -3058,16 +3103,17 @@
         <v>12000005</v>
       </c>
       <c r="M36" s="10"/>
-      <c r="N36" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="37" s="2" customFormat="1" customHeight="1" spans="2:14">
+      <c r="N36" s="10"/>
+      <c r="O36" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="37" s="2" customFormat="1" customHeight="1" spans="2:15">
       <c r="B37" s="2">
         <v>10003006</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D37" s="2">
         <v>10003006</v>
@@ -3098,16 +3144,17 @@
         <v>12000006</v>
       </c>
       <c r="M37" s="10"/>
-      <c r="N37" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="38" s="2" customFormat="1" customHeight="1" spans="2:14">
+      <c r="N37" s="10"/>
+      <c r="O37" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="38" s="2" customFormat="1" customHeight="1" spans="2:15">
       <c r="B38" s="2">
         <v>10003011</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D38" s="2">
         <v>10003001</v>
@@ -3138,8 +3185,9 @@
         <v>12000011</v>
       </c>
       <c r="M38" s="10"/>
-      <c r="N38" s="2" t="s">
-        <v>102</v>
+      <c r="N38" s="10"/>
+      <c r="O38" s="2" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/ItemConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ItemConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12795"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -718,14 +718,14 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
-      <name val="宋体"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
-      <name val="微软雅黑"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1268,10 +1268,10 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="4" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1647,10 +1647,10 @@
       <c r="L1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="N1" s="7" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="6" t="s">
@@ -1694,10 +1694,10 @@
       <c r="L2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="M2" s="8" t="s">
+      <c r="M2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="N2" s="8" t="s">
+      <c r="N2" s="7" t="s">
         <v>18</v>
       </c>
       <c r="O2" s="6" t="s">
@@ -1711,34 +1711,34 @@
       <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="8" t="s">
         <v>29</v>
       </c>
       <c r="M3" s="9" t="s">
@@ -1747,11 +1747,11 @@
       <c r="N3" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="O3" s="8" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="2:15">
+    <row r="4" customHeight="1" spans="1:15">
       <c r="B4" s="3">
         <v>1</v>
       </c>
@@ -1789,7 +1789,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="2:15">
+    <row r="5" customHeight="1" spans="1:15">
       <c r="B5" s="3">
         <v>2</v>
       </c>
@@ -1828,7 +1828,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="2:15">
+    <row r="6" customHeight="1" spans="1:15">
       <c r="B6" s="3">
         <v>3</v>
       </c>
@@ -1867,7 +1867,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="2:15">
+    <row r="7" customHeight="1" spans="1:15">
       <c r="B7" s="3">
         <v>4</v>
       </c>
@@ -1906,7 +1906,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="2:15">
+    <row r="8" customHeight="1" spans="1:15">
       <c r="B8" s="3">
         <v>5</v>
       </c>
@@ -1945,7 +1945,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="2:15">
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="1:15">
       <c r="B9" s="2">
         <v>10001001</v>
       </c>
@@ -1988,7 +1988,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" ht="19.5" customHeight="1" spans="2:15">
+    <row r="10" s="2" customFormat="1" ht="19.5" customHeight="1" spans="1:15">
       <c r="B10" s="2">
         <v>10001002</v>
       </c>
@@ -2031,7 +2031,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="2:15">
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:15">
       <c r="B11" s="2">
         <v>10001003</v>
       </c>
@@ -2072,7 +2072,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="2:15">
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:15">
       <c r="B12" s="2">
         <v>10001004</v>
       </c>
@@ -2113,7 +2113,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="2:15">
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:15">
       <c r="B13" s="2">
         <v>10001005</v>
       </c>
@@ -2154,7 +2154,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="2:15">
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:15">
       <c r="B14" s="2">
         <v>10001006</v>
       </c>
@@ -2195,7 +2195,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="15" s="2" customFormat="1" customHeight="1" spans="2:15">
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="1:15">
       <c r="B15" s="2">
         <v>10001007</v>
       </c>
@@ -2236,7 +2236,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="16" s="2" customFormat="1" customHeight="1" spans="2:15">
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="1:15">
       <c r="B16" s="2">
         <v>10001008</v>
       </c>
@@ -2604,8 +2604,8 @@
         <v>1</v>
       </c>
       <c r="J24" s="3">
-        <f>J22+100</f>
-        <v>2000</v>
+        <f>J23+100</f>
+        <v>2100</v>
       </c>
       <c r="K24" s="2">
         <v>999</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="J25" s="3">
         <f t="shared" ref="J24:J36" si="2">J24+100</f>
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="K25" s="2">
         <v>999</v>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="J26" s="3">
         <f t="shared" si="2"/>
-        <v>2200</v>
+        <v>2300</v>
       </c>
       <c r="K26" s="2">
         <v>999</v>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="J27" s="3">
         <f t="shared" si="2"/>
-        <v>2300</v>
+        <v>2400</v>
       </c>
       <c r="K27" s="2">
         <v>999</v>
@@ -2769,7 +2769,7 @@
       </c>
       <c r="J28" s="3">
         <f t="shared" si="2"/>
-        <v>2400</v>
+        <v>2500</v>
       </c>
       <c r="K28" s="2">
         <v>999</v>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="J29" s="3">
         <f t="shared" si="2"/>
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="K29" s="2">
         <v>999</v>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="J30" s="3">
         <f t="shared" si="2"/>
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="K30" s="2">
         <v>99</v>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="J31" s="3">
         <f t="shared" si="2"/>
-        <v>2700</v>
+        <v>2800</v>
       </c>
       <c r="K31" s="2">
         <v>99</v>
@@ -2910,7 +2910,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="32" s="2" customFormat="1" customHeight="1" spans="2:14">
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="2:15">
       <c r="B32" s="2">
         <v>10003001</v>
       </c>
@@ -2947,7 +2947,7 @@
       <c r="M32" s="10"/>
       <c r="N32" s="10"/>
     </row>
-    <row r="33" s="2" customFormat="1" customHeight="1" spans="2:14">
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="2:15">
       <c r="B33" s="2">
         <v>10003002</v>
       </c>

--- a/Unity/Assets/Config/Excel/ItemConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ItemConfig.xlsx
@@ -712,15 +712,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
-      <name val="宋体"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
-      <name val="微软雅黑"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -729,6 +728,7 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -1677,7 +1677,7 @@
         <v>16</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>7</v>
@@ -2389,7 +2389,7 @@
         <v>1</v>
       </c>
       <c r="J19" s="3">
-        <f t="shared" ref="J19:J23" si="1">J18+100</f>
+        <f t="shared" ref="J19:J24" si="1">J18+100</f>
         <v>1600</v>
       </c>
       <c r="K19" s="2">
@@ -2604,7 +2604,7 @@
         <v>1</v>
       </c>
       <c r="J24" s="3">
-        <f>J23+100</f>
+        <f t="shared" si="1"/>
         <v>2100</v>
       </c>
       <c r="K24" s="2">

--- a/Unity/Assets/Config/Excel/ItemConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ItemConfig.xlsx
@@ -712,14 +712,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
-      <name val="微软雅黑"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
-      <name val="宋体"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1677,7 +1677,7 @@
         <v>16</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>7</v>

--- a/Unity/Assets/Config/Excel/ItemConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ItemConfig.xlsx
@@ -81,7 +81,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0">
+    <comment ref="H3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -106,7 +106,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="0">
+    <comment ref="I3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -161,7 +161,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I3" authorId="0">
+    <comment ref="J3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -183,7 +183,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L3" authorId="0">
+    <comment ref="M3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -210,7 +210,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="140">
   <si>
     <t>##var</t>
   </si>
@@ -227,6 +227,9 @@
     <t>ItemQuality</t>
   </si>
   <si>
+    <t>RecycleItem</t>
+  </si>
+  <si>
     <t>UseLv</t>
   </si>
   <si>
@@ -266,6 +269,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>(array#sep=@),rewardItem</t>
+  </si>
+  <si>
     <t>(array#sep=,),int</t>
   </si>
   <si>
@@ -281,6 +287,9 @@
     <t>道具品质</t>
   </si>
   <si>
+    <t>分解奖励</t>
+  </si>
+  <si>
     <t>使用等级</t>
   </si>
   <si>
@@ -314,6 +323,9 @@
     <t>金币</t>
   </si>
   <si>
+    <t>0;0</t>
+  </si>
+  <si>
     <t>一种货币</t>
   </si>
   <si>
@@ -344,6 +356,9 @@
     <t>随机宝箱</t>
   </si>
   <si>
+    <t>1;1@2;1</t>
+  </si>
+  <si>
     <t>10003001,10003002,10003003</t>
   </si>
   <si>
@@ -353,6 +368,9 @@
     <t>自选宝箱</t>
   </si>
   <si>
+    <t>1;1@2;2</t>
+  </si>
+  <si>
     <t>10003004,10003005,10003006</t>
   </si>
   <si>
@@ -362,42 +380,63 @@
     <t>英雄召唤券</t>
   </si>
   <si>
+    <t>1;1@2;3</t>
+  </si>
+  <si>
     <t>可以在招募中心召唤随从</t>
   </si>
   <si>
     <t>大力丸</t>
   </si>
   <si>
+    <t>1;1@2;4</t>
+  </si>
+  <si>
     <t>使用后永久增加攻击资质</t>
   </si>
   <si>
     <t>金刚丸</t>
   </si>
   <si>
+    <t>1;1@2;5</t>
+  </si>
+  <si>
     <t>使用后永久增加防御资质</t>
   </si>
   <si>
     <t>气血丸</t>
   </si>
   <si>
+    <t>1;1@2;6</t>
+  </si>
+  <si>
     <t>使用后永久增加气血资质</t>
   </si>
   <si>
     <t>神速丸</t>
   </si>
   <si>
+    <t>1;1@2;7</t>
+  </si>
+  <si>
     <t>使用后永久增加闪避资质</t>
   </si>
   <si>
     <t>入场券</t>
   </si>
   <si>
+    <t>1;1@2;8</t>
+  </si>
+  <si>
     <t>消耗入场券进入副本</t>
   </si>
   <si>
     <t>金币袋子</t>
   </si>
   <si>
+    <t>1;1@2;9</t>
+  </si>
+  <si>
     <t>4000</t>
   </si>
   <si>
@@ -407,6 +446,9 @@
     <t>斧王碎片</t>
   </si>
   <si>
+    <t>1;1@2;10</t>
+  </si>
+  <si>
     <t>10001001,30</t>
   </si>
   <si>
@@ -416,72 +458,108 @@
     <t>流浪剑客碎片</t>
   </si>
   <si>
+    <t>1;1@2;11</t>
+  </si>
+  <si>
     <t>10001002,30</t>
   </si>
   <si>
     <t>剑圣碎片</t>
   </si>
   <si>
+    <t>1;1@2;12</t>
+  </si>
+  <si>
     <t>10001003,30</t>
   </si>
   <si>
     <t>全能骑士碎片</t>
   </si>
   <si>
+    <t>1;1@2;13</t>
+  </si>
+  <si>
     <t>10001004,30</t>
   </si>
   <si>
     <t>冰女碎片</t>
   </si>
   <si>
+    <t>1;1@2;14</t>
+  </si>
+  <si>
     <t>10002001,30</t>
   </si>
   <si>
     <t>术士碎片</t>
   </si>
   <si>
+    <t>1;1@2;15</t>
+  </si>
+  <si>
     <t>10002002,30</t>
   </si>
   <si>
     <t>材料1</t>
   </si>
   <si>
+    <t>1;1@2;16</t>
+  </si>
+  <si>
     <t>一种材料1</t>
   </si>
   <si>
     <t>材料2</t>
   </si>
   <si>
+    <t>1;1@2;17</t>
+  </si>
+  <si>
     <t>一种材料2</t>
   </si>
   <si>
     <t>材料3</t>
   </si>
   <si>
+    <t>1;1@2;18</t>
+  </si>
+  <si>
     <t>一种材料3</t>
   </si>
   <si>
     <t>材料4</t>
   </si>
   <si>
+    <t>1;1@2;19</t>
+  </si>
+  <si>
     <t>一种材料4</t>
   </si>
   <si>
     <t>材料5</t>
   </si>
   <si>
+    <t>1;1@2;20</t>
+  </si>
+  <si>
     <t>一种材料5</t>
   </si>
   <si>
     <t>材料6</t>
   </si>
   <si>
+    <t>1;1@2;21</t>
+  </si>
+  <si>
     <t>一种材料6</t>
   </si>
   <si>
     <t>英雄经验道具</t>
   </si>
   <si>
+    <t>1;1@2;22</t>
+  </si>
+  <si>
     <t>100,200</t>
   </si>
   <si>
@@ -491,40 +569,64 @@
     <t>低级魂石</t>
   </si>
   <si>
+    <t>1;1@2;23</t>
+  </si>
+  <si>
     <t>英雄增加100魂石</t>
   </si>
   <si>
     <t>一个头盔</t>
   </si>
   <si>
+    <t>1;1@2;24</t>
+  </si>
+  <si>
     <t>一个衣服</t>
   </si>
   <si>
+    <t>1;1@2;25</t>
+  </si>
+  <si>
     <t>一个裤子</t>
   </si>
   <si>
+    <t>1;1@2;26</t>
+  </si>
+  <si>
     <t>这是一个装备3</t>
   </si>
   <si>
     <t>一个鞋子</t>
   </si>
   <si>
+    <t>1;1@2;27</t>
+  </si>
+  <si>
     <t>这是一个装备4</t>
   </si>
   <si>
     <t>一个项链</t>
   </si>
   <si>
+    <t>1;1@2;28</t>
+  </si>
+  <si>
     <t>这是一个装备5</t>
   </si>
   <si>
     <t>一个武器</t>
   </si>
   <si>
+    <t>1;1@2;29</t>
+  </si>
+  <si>
     <t>这是一个装备6</t>
   </si>
   <si>
     <t>一个更吊的头盔</t>
+  </si>
+  <si>
+    <t>1;1@2;30</t>
   </si>
   <si>
     <t>这是一个装备1</t>
@@ -719,16 +821,16 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
+      <sz val="9"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -1600,17 +1702,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O38"/>
+  <dimension ref="A1:P38"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.875" style="3" customWidth="1"/>
-    <col min="2" max="12" width="17.875" style="3"/>
-    <col min="13" max="14" width="27.25" style="4" customWidth="1"/>
-    <col min="15" max="15" width="70.625" style="3" customWidth="1"/>
-    <col min="16" max="16384" width="17.875" style="3"/>
+    <col min="2" max="5" width="17.875" style="3"/>
+    <col min="6" max="6" width="35.625" style="3" customWidth="1"/>
+    <col min="7" max="13" width="17.875" style="3"/>
+    <col min="14" max="15" width="27.25" style="4" customWidth="1"/>
+    <col min="16" max="16" width="70.625" style="3" customWidth="1"/>
+    <col min="17" max="16384" width="17.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:15">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1626,7 +1730,7 @@
       <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="6" t="s">
@@ -1647,116 +1751,125 @@
       <c r="L1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="6" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="O1" s="7" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P1" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="F2" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="6" t="s">
         <v>17</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>6</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>7</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="M2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2" s="6" t="s">
         <v>17</v>
       </c>
       <c r="N2" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="O2" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="O2" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A3" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="M3" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>32</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="O3" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" customHeight="1" spans="1:15">
+        <v>33</v>
+      </c>
+      <c r="O3" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="P3" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="1:16">
       <c r="B4" s="3">
         <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>
@@ -1764,37 +1877,40 @@
       <c r="E4" s="3">
         <v>3</v>
       </c>
-      <c r="F4" s="3">
-        <v>1</v>
+      <c r="F4" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="G4" s="3">
         <v>1</v>
       </c>
       <c r="H4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="3">
+        <v>1</v>
+      </c>
+      <c r="K4" s="3">
         <v>100</v>
       </c>
-      <c r="K4" s="3">
+      <c r="L4" s="3">
         <v>99999999</v>
       </c>
-      <c r="L4" s="3">
-        <v>0</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" customHeight="1" spans="1:15">
+      <c r="M4" s="3">
+        <v>0</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="1:16">
       <c r="B5" s="3">
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D5" s="3">
         <v>2</v>
@@ -1802,38 +1918,41 @@
       <c r="E5" s="3">
         <v>5</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="3">
         <v>2</v>
       </c>
-      <c r="G5" s="3">
-        <v>1</v>
-      </c>
       <c r="H5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3">
-        <f t="shared" ref="J5:J18" si="0">J4+100</f>
+        <v>1</v>
+      </c>
+      <c r="K5" s="3">
+        <f t="shared" ref="K5:K18" si="0">K4+100</f>
         <v>200</v>
       </c>
-      <c r="K5" s="3">
+      <c r="L5" s="3">
         <v>99999999</v>
       </c>
-      <c r="L5" s="3">
-        <v>0</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="1:15">
+      <c r="M5" s="3">
+        <v>0</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:16">
       <c r="B6" s="3">
         <v>3</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D6" s="3">
         <v>3</v>
@@ -1841,38 +1960,41 @@
       <c r="E6" s="3">
         <v>5</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="3">
         <v>3</v>
       </c>
-      <c r="G6" s="3">
-        <v>1</v>
-      </c>
       <c r="H6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" s="3">
+        <v>1</v>
+      </c>
+      <c r="K6" s="3">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="K6" s="3">
+      <c r="L6" s="3">
         <v>99999999</v>
       </c>
-      <c r="L6" s="3">
-        <v>0</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="1:15">
+      <c r="M6" s="3">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:16">
       <c r="B7" s="3">
         <v>4</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D7" s="3">
         <v>4</v>
@@ -1880,38 +2002,41 @@
       <c r="E7" s="3">
         <v>5</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="3">
         <v>4</v>
       </c>
-      <c r="G7" s="3">
-        <v>1</v>
-      </c>
       <c r="H7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" s="3">
+        <v>1</v>
+      </c>
+      <c r="K7" s="3">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="K7" s="3">
+      <c r="L7" s="3">
         <v>99999999</v>
       </c>
-      <c r="L7" s="3">
-        <v>0</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="1:15">
+      <c r="M7" s="3">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:16">
       <c r="B8" s="3">
         <v>5</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D8" s="3">
         <v>5</v>
@@ -1919,38 +2044,41 @@
       <c r="E8" s="3">
         <v>4</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="3">
         <v>5</v>
       </c>
-      <c r="G8" s="3">
-        <v>1</v>
-      </c>
       <c r="H8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3">
+        <v>1</v>
+      </c>
+      <c r="K8" s="3">
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>99999999</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="1:15">
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="1:16">
       <c r="B9" s="2">
         <v>10001001</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D9" s="2">
         <v>10000001</v>
@@ -1958,42 +2086,45 @@
       <c r="E9" s="2">
         <v>6</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="3">
         <v>6</v>
       </c>
-      <c r="G9" s="2">
-        <v>1</v>
-      </c>
       <c r="H9" s="2">
+        <v>1</v>
+      </c>
+      <c r="I9" s="2">
         <v>3</v>
       </c>
-      <c r="I9" s="2">
-        <v>1</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="J9" s="2">
+        <v>1</v>
+      </c>
+      <c r="K9" s="3">
         <f t="shared" si="0"/>
         <v>600</v>
       </c>
-      <c r="K9" s="2">
+      <c r="L9" s="2">
         <v>99</v>
       </c>
-      <c r="L9" s="2">
-        <v>0</v>
-      </c>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" s="2" customFormat="1" ht="19.5" customHeight="1" spans="1:15">
+      <c r="M9" s="2">
+        <v>0</v>
+      </c>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" ht="19.5" customHeight="1" spans="1:16">
       <c r="B10" s="2">
         <v>10001002</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D10" s="2">
         <v>10000002</v>
@@ -2001,42 +2132,45 @@
       <c r="E10" s="2">
         <v>6</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10" s="3">
         <v>7</v>
       </c>
-      <c r="G10" s="2">
-        <v>1</v>
-      </c>
       <c r="H10" s="2">
+        <v>1</v>
+      </c>
+      <c r="I10" s="2">
         <v>4</v>
       </c>
-      <c r="I10" s="2">
-        <v>1</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="J10" s="2">
+        <v>1</v>
+      </c>
+      <c r="K10" s="3">
         <f t="shared" si="0"/>
         <v>700</v>
       </c>
-      <c r="K10" s="2">
+      <c r="L10" s="2">
         <v>99</v>
       </c>
-      <c r="L10" s="2">
-        <v>0</v>
-      </c>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:15">
+      <c r="M10" s="2">
+        <v>0</v>
+      </c>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:16">
       <c r="B11" s="2">
         <v>10001003</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D11" s="2">
         <v>10000003</v>
@@ -2044,40 +2178,43 @@
       <c r="E11" s="2">
         <v>5</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G11" s="3">
         <v>8</v>
       </c>
-      <c r="G11" s="2">
-        <v>1</v>
-      </c>
       <c r="H11" s="2">
+        <v>1</v>
+      </c>
+      <c r="I11" s="2">
         <v>6</v>
       </c>
-      <c r="I11" s="2">
-        <v>1</v>
-      </c>
-      <c r="J11" s="3">
+      <c r="J11" s="2">
+        <v>1</v>
+      </c>
+      <c r="K11" s="3">
         <f t="shared" si="0"/>
         <v>800</v>
       </c>
-      <c r="K11" s="2">
+      <c r="L11" s="2">
         <v>99</v>
       </c>
-      <c r="L11" s="2">
-        <v>0</v>
-      </c>
-      <c r="M11" s="10"/>
+      <c r="M11" s="2">
+        <v>0</v>
+      </c>
       <c r="N11" s="10"/>
-      <c r="O11" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:15">
+      <c r="O11" s="10"/>
+      <c r="P11" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:16">
       <c r="B12" s="2">
         <v>10001004</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D12" s="2">
         <v>10000004</v>
@@ -2085,40 +2222,43 @@
       <c r="E12" s="2">
         <v>5</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12" s="3">
         <v>9</v>
       </c>
-      <c r="G12" s="2">
-        <v>1</v>
-      </c>
       <c r="H12" s="2">
+        <v>1</v>
+      </c>
+      <c r="I12" s="2">
         <v>5</v>
       </c>
-      <c r="I12" s="2">
-        <v>1</v>
-      </c>
-      <c r="J12" s="3">
+      <c r="J12" s="2">
+        <v>1</v>
+      </c>
+      <c r="K12" s="3">
         <f t="shared" si="0"/>
         <v>900</v>
       </c>
-      <c r="K12" s="2">
+      <c r="L12" s="2">
         <v>99</v>
       </c>
-      <c r="L12" s="2">
-        <v>0</v>
-      </c>
-      <c r="M12" s="10"/>
+      <c r="M12" s="2">
+        <v>0</v>
+      </c>
       <c r="N12" s="10"/>
-      <c r="O12" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:15">
+      <c r="O12" s="10"/>
+      <c r="P12" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:16">
       <c r="B13" s="2">
         <v>10001005</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D13" s="2">
         <v>10000005</v>
@@ -2126,40 +2266,43 @@
       <c r="E13" s="2">
         <v>5</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="G13" s="3">
         <v>10</v>
       </c>
-      <c r="G13" s="2">
-        <v>1</v>
-      </c>
       <c r="H13" s="2">
+        <v>1</v>
+      </c>
+      <c r="I13" s="2">
         <v>5</v>
       </c>
-      <c r="I13" s="2">
-        <v>1</v>
-      </c>
-      <c r="J13" s="3">
+      <c r="J13" s="2">
+        <v>1</v>
+      </c>
+      <c r="K13" s="3">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
-      <c r="K13" s="2">
+      <c r="L13" s="2">
         <v>99</v>
       </c>
-      <c r="L13" s="2">
-        <v>0</v>
-      </c>
-      <c r="M13" s="10"/>
+      <c r="M13" s="2">
+        <v>0</v>
+      </c>
       <c r="N13" s="10"/>
-      <c r="O13" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:15">
+      <c r="O13" s="10"/>
+      <c r="P13" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:16">
       <c r="B14" s="2">
         <v>10001006</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="D14" s="2">
         <v>10000006</v>
@@ -2167,40 +2310,43 @@
       <c r="E14" s="2">
         <v>5</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="G14" s="3">
         <v>11</v>
       </c>
-      <c r="G14" s="2">
-        <v>1</v>
-      </c>
       <c r="H14" s="2">
+        <v>1</v>
+      </c>
+      <c r="I14" s="2">
         <v>5</v>
       </c>
-      <c r="I14" s="2">
-        <v>1</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="2">
+        <v>1</v>
+      </c>
+      <c r="K14" s="3">
         <f t="shared" si="0"/>
         <v>1100</v>
       </c>
-      <c r="K14" s="2">
+      <c r="L14" s="2">
         <v>99</v>
       </c>
-      <c r="L14" s="2">
-        <v>0</v>
-      </c>
-      <c r="M14" s="10"/>
+      <c r="M14" s="2">
+        <v>0</v>
+      </c>
       <c r="N14" s="10"/>
-      <c r="O14" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="15" s="2" customFormat="1" customHeight="1" spans="1:15">
+      <c r="O14" s="10"/>
+      <c r="P14" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="1:16">
       <c r="B15" s="2">
         <v>10001007</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D15" s="2">
         <v>10000007</v>
@@ -2208,40 +2354,43 @@
       <c r="E15" s="2">
         <v>5</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="G15" s="3">
         <v>12</v>
       </c>
-      <c r="G15" s="2">
-        <v>1</v>
-      </c>
       <c r="H15" s="2">
+        <v>1</v>
+      </c>
+      <c r="I15" s="2">
         <v>5</v>
       </c>
-      <c r="I15" s="2">
-        <v>1</v>
-      </c>
-      <c r="J15" s="3">
+      <c r="J15" s="2">
+        <v>1</v>
+      </c>
+      <c r="K15" s="3">
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
-      <c r="K15" s="2">
+      <c r="L15" s="2">
         <v>99</v>
       </c>
-      <c r="L15" s="2">
-        <v>0</v>
-      </c>
-      <c r="M15" s="10"/>
+      <c r="M15" s="2">
+        <v>0</v>
+      </c>
       <c r="N15" s="10"/>
-      <c r="O15" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="16" s="2" customFormat="1" customHeight="1" spans="1:15">
+      <c r="O15" s="10"/>
+      <c r="P15" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="1:16">
       <c r="B16" s="2">
         <v>10001008</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="D16" s="2">
         <v>10000008</v>
@@ -2249,40 +2398,43 @@
       <c r="E16" s="2">
         <v>3</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="G16" s="3">
         <v>13</v>
       </c>
-      <c r="G16" s="2">
-        <v>1</v>
-      </c>
       <c r="H16" s="2">
+        <v>1</v>
+      </c>
+      <c r="I16" s="2">
         <v>7</v>
       </c>
-      <c r="I16" s="2">
-        <v>1</v>
-      </c>
-      <c r="J16" s="3">
+      <c r="J16" s="2">
+        <v>1</v>
+      </c>
+      <c r="K16" s="3">
         <f t="shared" si="0"/>
         <v>1300</v>
       </c>
-      <c r="K16" s="2">
+      <c r="L16" s="2">
         <v>99</v>
       </c>
-      <c r="L16" s="2">
-        <v>0</v>
-      </c>
-      <c r="M16" s="10"/>
+      <c r="M16" s="2">
+        <v>0</v>
+      </c>
       <c r="N16" s="10"/>
-      <c r="O16" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" s="2" customFormat="1" customHeight="1" spans="2:15">
+      <c r="O16" s="10"/>
+      <c r="P16" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="2:16">
       <c r="B17" s="2">
         <v>10001011</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="D17" s="2">
         <v>10000009</v>
@@ -2290,10 +2442,10 @@
       <c r="E17" s="2">
         <v>5</v>
       </c>
-      <c r="F17" s="3">
-        <v>1</v>
-      </c>
-      <c r="G17" s="2">
+      <c r="F17" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G17" s="3">
         <v>1</v>
       </c>
       <c r="H17" s="2">
@@ -2302,30 +2454,33 @@
       <c r="I17" s="2">
         <v>1</v>
       </c>
-      <c r="J17" s="3">
+      <c r="J17" s="2">
+        <v>1</v>
+      </c>
+      <c r="K17" s="3">
         <f t="shared" si="0"/>
         <v>1400</v>
       </c>
-      <c r="K17" s="2">
+      <c r="L17" s="2">
         <v>99</v>
       </c>
-      <c r="L17" s="2">
-        <v>0</v>
-      </c>
-      <c r="M17" s="10"/>
-      <c r="N17" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="O17" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="18" s="2" customFormat="1" customHeight="1" spans="2:15">
+      <c r="M17" s="2">
+        <v>0</v>
+      </c>
+      <c r="N17" s="10"/>
+      <c r="O17" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="2:16">
       <c r="B18" s="2">
         <v>10002001</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="D18" s="2">
         <v>10000009</v>
@@ -2333,42 +2488,45 @@
       <c r="E18" s="2">
         <v>2</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="G18" s="3">
         <v>14</v>
       </c>
-      <c r="G18" s="2">
+      <c r="H18" s="2">
         <v>2</v>
       </c>
-      <c r="H18" s="2">
+      <c r="I18" s="2">
         <v>10</v>
       </c>
-      <c r="I18" s="2">
-        <v>1</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="J18" s="2">
+        <v>1</v>
+      </c>
+      <c r="K18" s="3">
         <f t="shared" si="0"/>
         <v>1500</v>
       </c>
-      <c r="K18" s="2">
+      <c r="L18" s="2">
         <v>999</v>
       </c>
-      <c r="L18" s="2">
-        <v>0</v>
-      </c>
-      <c r="M18" s="10"/>
-      <c r="N18" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="2:15">
+      <c r="M18" s="2">
+        <v>0</v>
+      </c>
+      <c r="N18" s="10"/>
+      <c r="O18" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="2:16">
       <c r="B19" s="2">
         <v>10002002</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="D19" s="2">
         <v>10000010</v>
@@ -2376,42 +2534,45 @@
       <c r="E19" s="2">
         <v>3</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="G19" s="3">
         <v>15</v>
       </c>
-      <c r="G19" s="2">
+      <c r="H19" s="2">
         <v>2</v>
       </c>
-      <c r="H19" s="2">
+      <c r="I19" s="2">
         <v>10</v>
       </c>
-      <c r="I19" s="2">
-        <v>1</v>
-      </c>
-      <c r="J19" s="3">
-        <f t="shared" ref="J19:J24" si="1">J18+100</f>
+      <c r="J19" s="2">
+        <v>1</v>
+      </c>
+      <c r="K19" s="3">
+        <f t="shared" ref="K19:K24" si="1">K18+100</f>
         <v>1600</v>
       </c>
-      <c r="K19" s="2">
+      <c r="L19" s="2">
         <v>999</v>
       </c>
-      <c r="L19" s="2">
-        <v>0</v>
-      </c>
-      <c r="M19" s="10"/>
-      <c r="N19" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="20" s="2" customFormat="1" customHeight="1" spans="2:15">
+      <c r="M19" s="2">
+        <v>0</v>
+      </c>
+      <c r="N19" s="10"/>
+      <c r="O19" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="2:16">
       <c r="B20" s="2">
         <v>10002003</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="D20" s="2">
         <v>10000011</v>
@@ -2419,42 +2580,45 @@
       <c r="E20" s="2">
         <v>4</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="G20" s="3">
         <v>16</v>
       </c>
-      <c r="G20" s="2">
+      <c r="H20" s="2">
         <v>2</v>
       </c>
-      <c r="H20" s="2">
+      <c r="I20" s="2">
         <v>10</v>
       </c>
-      <c r="I20" s="2">
-        <v>1</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="J20" s="2">
+        <v>1</v>
+      </c>
+      <c r="K20" s="3">
         <f t="shared" si="1"/>
         <v>1700</v>
       </c>
-      <c r="K20" s="2">
+      <c r="L20" s="2">
         <v>999</v>
       </c>
-      <c r="L20" s="2">
-        <v>0</v>
-      </c>
-      <c r="M20" s="10"/>
-      <c r="N20" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="O20" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="21" s="2" customFormat="1" customHeight="1" spans="2:15">
+      <c r="M20" s="2">
+        <v>0</v>
+      </c>
+      <c r="N20" s="10"/>
+      <c r="O20" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="2:16">
       <c r="B21" s="2">
         <v>10002004</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="D21" s="2">
         <v>10000012</v>
@@ -2462,42 +2626,45 @@
       <c r="E21" s="2">
         <v>5</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G21" s="3">
         <v>17</v>
       </c>
-      <c r="G21" s="2">
+      <c r="H21" s="2">
         <v>2</v>
       </c>
-      <c r="H21" s="2">
+      <c r="I21" s="2">
         <v>10</v>
       </c>
-      <c r="I21" s="2">
-        <v>1</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="J21" s="2">
+        <v>1</v>
+      </c>
+      <c r="K21" s="3">
         <f t="shared" si="1"/>
         <v>1800</v>
       </c>
-      <c r="K21" s="2">
+      <c r="L21" s="2">
         <v>999</v>
       </c>
-      <c r="L21" s="2">
-        <v>0</v>
-      </c>
-      <c r="M21" s="10"/>
-      <c r="N21" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="22" s="2" customFormat="1" customHeight="1" spans="2:15">
+      <c r="M21" s="2">
+        <v>0</v>
+      </c>
+      <c r="N21" s="10"/>
+      <c r="O21" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="2:16">
       <c r="B22" s="2">
         <v>10002005</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="D22" s="2">
         <v>10000013</v>
@@ -2505,42 +2672,45 @@
       <c r="E22" s="2">
         <v>6</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="G22" s="3">
         <v>18</v>
       </c>
-      <c r="G22" s="2">
+      <c r="H22" s="2">
         <v>2</v>
       </c>
-      <c r="H22" s="2">
+      <c r="I22" s="2">
         <v>10</v>
       </c>
-      <c r="I22" s="2">
-        <v>1</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="J22" s="2">
+        <v>1</v>
+      </c>
+      <c r="K22" s="3">
         <f t="shared" si="1"/>
         <v>1900</v>
       </c>
-      <c r="K22" s="2">
+      <c r="L22" s="2">
         <v>999</v>
       </c>
-      <c r="L22" s="2">
-        <v>0</v>
-      </c>
-      <c r="M22" s="10"/>
-      <c r="N22" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="O22" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="23" s="2" customFormat="1" customHeight="1" spans="2:15">
+      <c r="M22" s="2">
+        <v>0</v>
+      </c>
+      <c r="N22" s="10"/>
+      <c r="O22" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="2:16">
       <c r="B23" s="2">
         <v>10002006</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="D23" s="2">
         <v>10000013</v>
@@ -2548,42 +2718,45 @@
       <c r="E23" s="2">
         <v>6</v>
       </c>
-      <c r="F23" s="3">
+      <c r="F23" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="G23" s="3">
         <v>18</v>
       </c>
-      <c r="G23" s="2">
+      <c r="H23" s="2">
         <v>2</v>
       </c>
-      <c r="H23" s="2">
+      <c r="I23" s="2">
         <v>10</v>
       </c>
-      <c r="I23" s="2">
-        <v>1</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="J23" s="2">
+        <v>1</v>
+      </c>
+      <c r="K23" s="3">
         <f t="shared" si="1"/>
         <v>2000</v>
       </c>
-      <c r="K23" s="2">
+      <c r="L23" s="2">
         <v>999</v>
       </c>
-      <c r="L23" s="2">
-        <v>0</v>
-      </c>
-      <c r="M23" s="10"/>
-      <c r="N23" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="O23" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="24" s="2" customFormat="1" customHeight="1" spans="2:15">
+      <c r="M23" s="2">
+        <v>0</v>
+      </c>
+      <c r="N23" s="10"/>
+      <c r="O23" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="2:16">
       <c r="B24" s="2">
         <v>10002101</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="D24" s="2">
         <v>10000001</v>
@@ -2591,40 +2764,43 @@
       <c r="E24" s="2">
         <v>1</v>
       </c>
-      <c r="F24" s="3">
+      <c r="F24" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="G24" s="3">
         <v>19</v>
       </c>
-      <c r="G24" s="2">
+      <c r="H24" s="2">
         <v>2</v>
       </c>
-      <c r="H24" s="2">
-        <v>0</v>
-      </c>
       <c r="I24" s="2">
-        <v>1</v>
-      </c>
-      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="2">
+        <v>1</v>
+      </c>
+      <c r="K24" s="3">
         <f t="shared" si="1"/>
         <v>2100</v>
       </c>
-      <c r="K24" s="2">
+      <c r="L24" s="2">
         <v>999</v>
       </c>
-      <c r="L24" s="2">
-        <v>0</v>
-      </c>
-      <c r="M24" s="10"/>
+      <c r="M24" s="2">
+        <v>0</v>
+      </c>
       <c r="N24" s="10"/>
-      <c r="O24" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="25" s="2" customFormat="1" customHeight="1" spans="2:15">
+      <c r="O24" s="10"/>
+      <c r="P24" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="2:16">
       <c r="B25" s="2">
         <v>10002102</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="D25" s="2">
         <v>10000002</v>
@@ -2632,40 +2808,43 @@
       <c r="E25" s="2">
         <v>2</v>
       </c>
-      <c r="F25" s="3">
+      <c r="F25" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="G25" s="3">
         <v>20</v>
       </c>
-      <c r="G25" s="2">
+      <c r="H25" s="2">
         <v>2</v>
       </c>
-      <c r="H25" s="2">
-        <v>0</v>
-      </c>
       <c r="I25" s="2">
-        <v>1</v>
-      </c>
-      <c r="J25" s="3">
-        <f t="shared" ref="J24:J36" si="2">J24+100</f>
+        <v>0</v>
+      </c>
+      <c r="J25" s="2">
+        <v>1</v>
+      </c>
+      <c r="K25" s="3">
+        <f t="shared" ref="K24:K36" si="2">K24+100</f>
         <v>2200</v>
       </c>
-      <c r="K25" s="2">
+      <c r="L25" s="2">
         <v>999</v>
       </c>
-      <c r="L25" s="2">
-        <v>0</v>
-      </c>
-      <c r="M25" s="10"/>
+      <c r="M25" s="2">
+        <v>0</v>
+      </c>
       <c r="N25" s="10"/>
-      <c r="O25" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="26" s="2" customFormat="1" customHeight="1" spans="2:15">
+      <c r="O25" s="10"/>
+      <c r="P25" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="2:16">
       <c r="B26" s="2">
         <v>10002103</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="D26" s="2">
         <v>10000003</v>
@@ -2673,40 +2852,43 @@
       <c r="E26" s="2">
         <v>3</v>
       </c>
-      <c r="F26" s="3">
+      <c r="F26" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="G26" s="3">
         <v>21</v>
       </c>
-      <c r="G26" s="2">
+      <c r="H26" s="2">
         <v>2</v>
       </c>
-      <c r="H26" s="2">
-        <v>0</v>
-      </c>
       <c r="I26" s="2">
-        <v>1</v>
-      </c>
-      <c r="J26" s="3">
+        <v>0</v>
+      </c>
+      <c r="J26" s="2">
+        <v>1</v>
+      </c>
+      <c r="K26" s="3">
         <f t="shared" si="2"/>
         <v>2300</v>
       </c>
-      <c r="K26" s="2">
+      <c r="L26" s="2">
         <v>999</v>
       </c>
-      <c r="L26" s="2">
-        <v>0</v>
-      </c>
-      <c r="M26" s="10"/>
+      <c r="M26" s="2">
+        <v>0</v>
+      </c>
       <c r="N26" s="10"/>
-      <c r="O26" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="27" s="2" customFormat="1" customHeight="1" spans="2:15">
+      <c r="O26" s="10"/>
+      <c r="P26" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="2:16">
       <c r="B27" s="2">
         <v>10002104</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="D27" s="2">
         <v>10000004</v>
@@ -2714,40 +2896,43 @@
       <c r="E27" s="2">
         <v>4</v>
       </c>
-      <c r="F27" s="3">
+      <c r="F27" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="G27" s="3">
         <v>22</v>
       </c>
-      <c r="G27" s="2">
+      <c r="H27" s="2">
         <v>2</v>
       </c>
-      <c r="H27" s="2">
-        <v>0</v>
-      </c>
       <c r="I27" s="2">
-        <v>1</v>
-      </c>
-      <c r="J27" s="3">
+        <v>0</v>
+      </c>
+      <c r="J27" s="2">
+        <v>1</v>
+      </c>
+      <c r="K27" s="3">
         <f t="shared" si="2"/>
         <v>2400</v>
       </c>
-      <c r="K27" s="2">
+      <c r="L27" s="2">
         <v>999</v>
       </c>
-      <c r="L27" s="2">
-        <v>0</v>
-      </c>
-      <c r="M27" s="10"/>
+      <c r="M27" s="2">
+        <v>0</v>
+      </c>
       <c r="N27" s="10"/>
-      <c r="O27" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="28" s="2" customFormat="1" customHeight="1" spans="2:15">
+      <c r="O27" s="10"/>
+      <c r="P27" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="2:16">
       <c r="B28" s="2">
         <v>10002105</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="D28" s="2">
         <v>10000005</v>
@@ -2755,40 +2940,43 @@
       <c r="E28" s="2">
         <v>5</v>
       </c>
-      <c r="F28" s="3">
+      <c r="F28" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="G28" s="3">
         <v>23</v>
       </c>
-      <c r="G28" s="2">
+      <c r="H28" s="2">
         <v>2</v>
       </c>
-      <c r="H28" s="2">
-        <v>0</v>
-      </c>
       <c r="I28" s="2">
-        <v>1</v>
-      </c>
-      <c r="J28" s="3">
+        <v>0</v>
+      </c>
+      <c r="J28" s="2">
+        <v>1</v>
+      </c>
+      <c r="K28" s="3">
         <f t="shared" si="2"/>
         <v>2500</v>
       </c>
-      <c r="K28" s="2">
+      <c r="L28" s="2">
         <v>999</v>
       </c>
-      <c r="L28" s="2">
-        <v>0</v>
-      </c>
-      <c r="M28" s="10"/>
+      <c r="M28" s="2">
+        <v>0</v>
+      </c>
       <c r="N28" s="10"/>
-      <c r="O28" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="29" s="2" customFormat="1" customHeight="1" spans="2:15">
+      <c r="O28" s="10"/>
+      <c r="P28" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="2:16">
       <c r="B29" s="2">
         <v>10002106</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="D29" s="2">
         <v>10000006</v>
@@ -2796,40 +2984,43 @@
       <c r="E29" s="2">
         <v>6</v>
       </c>
-      <c r="F29" s="3">
+      <c r="F29" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="G29" s="3">
         <v>24</v>
       </c>
-      <c r="G29" s="2">
+      <c r="H29" s="2">
         <v>2</v>
       </c>
-      <c r="H29" s="2">
-        <v>0</v>
-      </c>
       <c r="I29" s="2">
-        <v>1</v>
-      </c>
-      <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="2">
+        <v>1</v>
+      </c>
+      <c r="K29" s="3">
         <f t="shared" si="2"/>
         <v>2600</v>
       </c>
-      <c r="K29" s="2">
+      <c r="L29" s="2">
         <v>999</v>
       </c>
-      <c r="L29" s="2">
-        <v>0</v>
-      </c>
-      <c r="M29" s="10"/>
+      <c r="M29" s="2">
+        <v>0</v>
+      </c>
       <c r="N29" s="10"/>
-      <c r="O29" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="30" s="2" customFormat="1" customHeight="1" spans="2:15">
+      <c r="O29" s="10"/>
+      <c r="P29" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="2:16">
       <c r="B30" s="2">
         <v>10002012</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="D30" s="2">
         <v>10000009</v>
@@ -2837,42 +3028,45 @@
       <c r="E30" s="2">
         <v>3</v>
       </c>
-      <c r="F30" s="3">
-        <v>1</v>
-      </c>
-      <c r="G30" s="2">
+      <c r="F30" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="G30" s="3">
+        <v>1</v>
+      </c>
+      <c r="H30" s="2">
         <v>2</v>
       </c>
-      <c r="H30" s="2">
+      <c r="I30" s="2">
         <v>8</v>
       </c>
-      <c r="I30" s="2">
-        <v>1</v>
-      </c>
-      <c r="J30" s="3">
+      <c r="J30" s="2">
+        <v>1</v>
+      </c>
+      <c r="K30" s="3">
         <f t="shared" si="2"/>
         <v>2700</v>
       </c>
-      <c r="K30" s="2">
+      <c r="L30" s="2">
         <v>99</v>
       </c>
-      <c r="L30" s="2">
-        <v>0</v>
-      </c>
-      <c r="M30" s="10"/>
-      <c r="N30" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="O30" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="31" s="2" customFormat="1" customHeight="1" spans="2:15">
+      <c r="M30" s="2">
+        <v>0</v>
+      </c>
+      <c r="N30" s="10"/>
+      <c r="O30" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" customHeight="1" spans="2:16">
       <c r="B31" s="2">
         <v>10002013</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="D31" s="2">
         <v>10000009</v>
@@ -2880,42 +3074,45 @@
       <c r="E31" s="2">
         <v>3</v>
       </c>
-      <c r="F31" s="3">
-        <v>1</v>
-      </c>
-      <c r="G31" s="2">
+      <c r="F31" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="G31" s="3">
+        <v>1</v>
+      </c>
+      <c r="H31" s="2">
         <v>2</v>
       </c>
-      <c r="H31" s="2">
+      <c r="I31" s="2">
         <v>9</v>
       </c>
-      <c r="I31" s="2">
-        <v>1</v>
-      </c>
-      <c r="J31" s="3">
+      <c r="J31" s="2">
+        <v>1</v>
+      </c>
+      <c r="K31" s="3">
         <f t="shared" si="2"/>
         <v>2800</v>
       </c>
-      <c r="K31" s="2">
+      <c r="L31" s="2">
         <v>99</v>
       </c>
-      <c r="L31" s="2">
-        <v>0</v>
-      </c>
-      <c r="M31" s="10"/>
-      <c r="N31" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="O31" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="32" s="2" customFormat="1" customHeight="1" spans="2:15">
+      <c r="M31" s="2">
+        <v>0</v>
+      </c>
+      <c r="N31" s="10"/>
+      <c r="O31" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="2:16">
       <c r="B32" s="2">
         <v>10003001</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="D32" s="2">
         <v>10003001</v>
@@ -2923,36 +3120,39 @@
       <c r="E32" s="2">
         <v>1</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="G32" s="3">
         <v>25</v>
       </c>
-      <c r="G32" s="2">
+      <c r="H32" s="2">
         <v>3</v>
       </c>
-      <c r="H32" s="2">
+      <c r="I32" s="2">
         <v>3001</v>
       </c>
-      <c r="I32" s="2">
-        <v>1</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="J32" s="2">
+        <v>1</v>
+      </c>
+      <c r="K32" s="3">
         <v>2800</v>
       </c>
-      <c r="K32" s="2">
-        <v>1</v>
-      </c>
       <c r="L32" s="2">
+        <v>1</v>
+      </c>
+      <c r="M32" s="2">
         <v>12000001</v>
       </c>
-      <c r="M32" s="10"/>
       <c r="N32" s="10"/>
-    </row>
-    <row r="33" s="2" customFormat="1" customHeight="1" spans="2:15">
+      <c r="O32" s="10"/>
+    </row>
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="2:16">
       <c r="B33" s="2">
         <v>10003002</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="D33" s="2">
         <v>10003002</v>
@@ -2960,37 +3160,40 @@
       <c r="E33" s="2">
         <v>2</v>
       </c>
-      <c r="F33" s="3">
+      <c r="F33" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="G33" s="3">
         <v>26</v>
       </c>
-      <c r="G33" s="2">
+      <c r="H33" s="2">
         <v>3</v>
       </c>
-      <c r="H33" s="2">
+      <c r="I33" s="2">
         <v>3002</v>
       </c>
-      <c r="I33" s="2">
-        <v>1</v>
-      </c>
-      <c r="J33" s="3">
-        <f t="shared" ref="J33:J38" si="3">J32+100</f>
+      <c r="J33" s="2">
+        <v>1</v>
+      </c>
+      <c r="K33" s="3">
+        <f t="shared" ref="K33:K38" si="3">K32+100</f>
         <v>2900</v>
       </c>
-      <c r="K33" s="2">
-        <v>1</v>
-      </c>
       <c r="L33" s="2">
+        <v>1</v>
+      </c>
+      <c r="M33" s="2">
         <v>12000002</v>
       </c>
-      <c r="M33" s="10"/>
       <c r="N33" s="10"/>
-    </row>
-    <row r="34" s="2" customFormat="1" customHeight="1" spans="2:15">
+      <c r="O33" s="10"/>
+    </row>
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="2:16">
       <c r="B34" s="2">
         <v>10003003</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="D34" s="2">
         <v>10003003</v>
@@ -2998,40 +3201,43 @@
       <c r="E34" s="2">
         <v>3</v>
       </c>
-      <c r="F34" s="3">
+      <c r="F34" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="G34" s="3">
         <v>27</v>
       </c>
-      <c r="G34" s="2">
+      <c r="H34" s="2">
         <v>3</v>
       </c>
-      <c r="H34" s="2">
+      <c r="I34" s="2">
         <v>3003</v>
       </c>
-      <c r="I34" s="2">
-        <v>1</v>
-      </c>
-      <c r="J34" s="3">
+      <c r="J34" s="2">
+        <v>1</v>
+      </c>
+      <c r="K34" s="3">
         <f t="shared" si="3"/>
         <v>3000</v>
       </c>
-      <c r="K34" s="2">
-        <v>1</v>
-      </c>
       <c r="L34" s="2">
+        <v>1</v>
+      </c>
+      <c r="M34" s="2">
         <v>12000003</v>
       </c>
-      <c r="M34" s="10"/>
       <c r="N34" s="10"/>
-      <c r="O34" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="35" s="2" customFormat="1" customHeight="1" spans="2:15">
+      <c r="O34" s="10"/>
+      <c r="P34" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="2:16">
       <c r="B35" s="2">
         <v>10003004</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="D35" s="2">
         <v>10003004</v>
@@ -3039,40 +3245,43 @@
       <c r="E35" s="2">
         <v>4</v>
       </c>
-      <c r="F35" s="3">
+      <c r="F35" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="G35" s="3">
         <v>28</v>
       </c>
-      <c r="G35" s="2">
+      <c r="H35" s="2">
         <v>3</v>
       </c>
-      <c r="H35" s="2">
+      <c r="I35" s="2">
         <v>3004</v>
       </c>
-      <c r="I35" s="2">
-        <v>1</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="J35" s="2">
+        <v>1</v>
+      </c>
+      <c r="K35" s="3">
         <f t="shared" si="3"/>
         <v>3100</v>
       </c>
-      <c r="K35" s="2">
-        <v>1</v>
-      </c>
       <c r="L35" s="2">
+        <v>1</v>
+      </c>
+      <c r="M35" s="2">
         <v>12000004</v>
       </c>
-      <c r="M35" s="10"/>
       <c r="N35" s="10"/>
-      <c r="O35" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="36" s="2" customFormat="1" customHeight="1" spans="2:15">
+      <c r="O35" s="10"/>
+      <c r="P35" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="2:16">
       <c r="B36" s="2">
         <v>10003005</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="D36" s="2">
         <v>10003005</v>
@@ -3080,40 +3289,43 @@
       <c r="E36" s="2">
         <v>5</v>
       </c>
-      <c r="F36" s="3">
+      <c r="F36" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="G36" s="3">
         <v>29</v>
       </c>
-      <c r="G36" s="2">
+      <c r="H36" s="2">
         <v>3</v>
       </c>
-      <c r="H36" s="2">
+      <c r="I36" s="2">
         <v>3005</v>
       </c>
-      <c r="I36" s="2">
-        <v>1</v>
-      </c>
-      <c r="J36" s="3">
+      <c r="J36" s="2">
+        <v>1</v>
+      </c>
+      <c r="K36" s="3">
         <f t="shared" si="3"/>
         <v>3200</v>
       </c>
-      <c r="K36" s="2">
-        <v>1</v>
-      </c>
       <c r="L36" s="2">
+        <v>1</v>
+      </c>
+      <c r="M36" s="2">
         <v>12000005</v>
       </c>
-      <c r="M36" s="10"/>
       <c r="N36" s="10"/>
-      <c r="O36" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="37" s="2" customFormat="1" customHeight="1" spans="2:15">
+      <c r="O36" s="10"/>
+      <c r="P36" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="37" s="2" customFormat="1" customHeight="1" spans="2:16">
       <c r="B37" s="2">
         <v>10003006</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="D37" s="2">
         <v>10003006</v>
@@ -3121,40 +3333,43 @@
       <c r="E37" s="2">
         <v>6</v>
       </c>
-      <c r="F37" s="3">
+      <c r="F37" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="G37" s="3">
         <v>30</v>
       </c>
-      <c r="G37" s="2">
+      <c r="H37" s="2">
         <v>3</v>
       </c>
-      <c r="H37" s="2">
+      <c r="I37" s="2">
         <v>3006</v>
       </c>
-      <c r="I37" s="2">
-        <v>1</v>
-      </c>
-      <c r="J37" s="3">
+      <c r="J37" s="2">
+        <v>1</v>
+      </c>
+      <c r="K37" s="3">
         <f t="shared" si="3"/>
         <v>3300</v>
       </c>
-      <c r="K37" s="2">
-        <v>1</v>
-      </c>
       <c r="L37" s="2">
+        <v>1</v>
+      </c>
+      <c r="M37" s="2">
         <v>12000006</v>
       </c>
-      <c r="M37" s="10"/>
       <c r="N37" s="10"/>
-      <c r="O37" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="38" s="2" customFormat="1" customHeight="1" spans="2:15">
+      <c r="O37" s="10"/>
+      <c r="P37" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="38" s="2" customFormat="1" customHeight="1" spans="2:16">
       <c r="B38" s="2">
         <v>10003011</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="D38" s="2">
         <v>10003001</v>
@@ -3162,32 +3377,35 @@
       <c r="E38" s="2">
         <v>3</v>
       </c>
-      <c r="F38" s="3">
+      <c r="F38" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="G38" s="3">
         <v>25</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>3</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>3001</v>
       </c>
-      <c r="I38" s="2">
-        <v>1</v>
-      </c>
-      <c r="J38" s="3">
+      <c r="J38" s="2">
+        <v>1</v>
+      </c>
+      <c r="K38" s="3">
         <f t="shared" si="3"/>
         <v>3400</v>
       </c>
-      <c r="K38" s="2">
-        <v>1</v>
-      </c>
       <c r="L38" s="2">
+        <v>1</v>
+      </c>
+      <c r="M38" s="2">
         <v>12000011</v>
       </c>
-      <c r="M38" s="10"/>
       <c r="N38" s="10"/>
-      <c r="O38" s="2" t="s">
-        <v>105</v>
+      <c r="O38" s="10"/>
+      <c r="P38" s="2" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>
